--- a/artifacts/reports/architecture/ARCH-HOST-01_タブレットPOS_デバイスコネクタ基本設計書/ARCH-HOST-01_タブレットPOS_デバイスコネクタ基本設計書.xlsx
+++ b/artifacts/reports/architecture/ARCH-HOST-01_タブレットPOS_デバイスコネクタ基本設計書/ARCH-HOST-01_タブレットPOS_デバイスコネクタ基本設計書.xlsx
@@ -29,7 +29,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -82,6 +82,12 @@
       <b val="1"/>
       <color rgb="FF000000"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Meiryo UI"/>
+      <b val="1"/>
+      <color rgb="FF404040"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Meiryo UI"/>
@@ -183,7 +189,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="150">
+  <borders count="158">
     <border>
       <left/>
       <right/>
@@ -1213,6 +1219,98 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FFBF9000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFBF9000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBF9000"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFBF9000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBF9000"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFBF9000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBF9000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBF9000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBF9000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBF9000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBF9000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBF9000"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFBF9000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFBF9000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBF9000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFBF9000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBF9000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFBF9000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBF9000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBF9000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FFF4CCCC"/>
       </left>
       <right/>
@@ -1859,7 +1957,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="100">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1997,12 +2095,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="92" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="93" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="97" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="97" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="100" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="101" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="105" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="105" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="108" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -2032,10 +2130,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="148" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="149" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="153" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="156" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="157" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2546,7 +2649,7 @@
       <c r="X2" s="15" t="n"/>
       <c r="Y2" s="17" t="inlineStr">
         <is>
-          <t>2026/07/12</t>
+          <t>2026/07/13</t>
         </is>
       </c>
       <c r="Z2" s="18" t="n"/>
@@ -2739,7 +2842,7 @@
       <c r="G10" s="29" t="n"/>
       <c r="H10" s="32" t="inlineStr">
         <is>
-          <t>0.3.0</t>
+          <t>0.3.2</t>
         </is>
       </c>
       <c r="I10" s="28" t="n"/>
@@ -3201,7 +3304,7 @@
       <c r="X2" s="15" t="n"/>
       <c r="Y2" s="17" t="inlineStr">
         <is>
-          <t>2026/07/12</t>
+          <t>2026/07/13</t>
         </is>
       </c>
       <c r="Z2" s="18" t="n"/>
@@ -3374,7 +3477,7 @@
       <c r="S12" s="29" t="n"/>
       <c r="T12" s="32" t="inlineStr">
         <is>
-          <t>デバイスアクセス、コマンド受付、順序制御、コマンド実行、デバイス管理。</t>
+          <t>デバイス制御層、コマンド受付、順序制御、コマンド実行、デバイス管理。</t>
         </is>
       </c>
       <c r="U12" s="28" t="n"/>
@@ -3536,7 +3639,7 @@
     <row r="27" ht="18" customHeight="1">
       <c r="C27" s="24" t="inlineStr">
         <is>
-          <t>① アプリケーション層はデバイス操作をデバイスアクセスへ依頼する。</t>
+          <t>① アプリケーション層はデバイス操作をデバイス制御層へ依頼する。</t>
         </is>
       </c>
     </row>
@@ -3599,7 +3702,7 @@
     <row r="37" ht="28" customHeight="1">
       <c r="C37" s="24" t="inlineStr">
         <is>
-          <t>② イベント配信はイベント通知用パイプを通じてデバイスアクセスへ通知する。結果・イベント連携はイベントJSONをアプリ内形式へ変換し、アプリケーション層の購読処理へ通知する。</t>
+          <t>② イベント配信はイベント通知用パイプを通じてデバイス制御層へ通知する。結果・イベント連携はイベントJSONをアプリ内形式へ変換し、アプリケーション層の購読処理へ通知する。</t>
         </is>
       </c>
     </row>
@@ -3903,7 +4006,7 @@
       <c r="X2" s="15" t="n"/>
       <c r="Y2" s="17" t="inlineStr">
         <is>
-          <t>2026/07/12</t>
+          <t>2026/07/13</t>
         </is>
       </c>
       <c r="Z2" s="18" t="n"/>
@@ -4177,7 +4280,7 @@
       <c r="U12" s="34" t="n"/>
       <c r="V12" s="34" t="n"/>
       <c r="W12" s="35" t="n"/>
-      <c r="X12" s="94" t="inlineStr">
+      <c r="X12" s="97" t="inlineStr">
         <is>
           <t>F-HOST-004</t>
         </is>
@@ -4365,7 +4468,7 @@
       <c r="Z19" s="30" t="n"/>
     </row>
     <row r="20" ht="72" customHeight="1">
-      <c r="B20" s="95" t="inlineStr">
+      <c r="B20" s="98" t="inlineStr">
         <is>
           <t>F-HOST-011</t>
         </is>
@@ -4592,7 +4695,7 @@
       <c r="Z26" s="30" t="n"/>
     </row>
     <row r="27" ht="54" customHeight="1">
-      <c r="B27" s="95" t="inlineStr">
+      <c r="B27" s="98" t="inlineStr">
         <is>
           <t>F-HOST-010</t>
         </is>
@@ -4991,7 +5094,7 @@
       <c r="Z39" s="9" t="n"/>
     </row>
     <row r="40" ht="72" customHeight="1">
-      <c r="B40" s="95" t="inlineStr">
+      <c r="B40" s="98" t="inlineStr">
         <is>
           <t>F-HOST-004</t>
         </is>
@@ -5347,7 +5450,7 @@
       <c r="X2" s="15" t="n"/>
       <c r="Y2" s="17" t="inlineStr">
         <is>
-          <t>2026/07/12</t>
+          <t>2026/07/13</t>
         </is>
       </c>
       <c r="Z2" s="18" t="n"/>
@@ -5668,7 +5771,7 @@
       </c>
     </row>
     <row r="18" ht="165" customHeight="1">
-      <c r="B18" s="96" t="inlineStr">
+      <c r="B18" s="99" t="inlineStr">
         <is>
           <t>{
   "RequestId": "00000001",
@@ -6332,7 +6435,7 @@
       <c r="Z38" s="37" t="n"/>
     </row>
     <row r="40" ht="24" customHeight="1">
-      <c r="B40" s="96" t="inlineStr">
+      <c r="B40" s="99" t="inlineStr">
         <is>
           <t>Message\tDeviceMethod\tTabletDeviceId\tCustomerDisplay\tMethodId\tDisplayText\tHandle\t12345\tData\tTOTAL 1,000</t>
         </is>
@@ -6353,7 +6456,7 @@
       </c>
     </row>
     <row r="45" ht="150" customHeight="1">
-      <c r="B45" s="96" t="inlineStr">
+      <c r="B45" s="99" t="inlineStr">
         <is>
           <t>{
   "RequestId": "00000001",
@@ -6727,7 +6830,7 @@
       </c>
     </row>
     <row r="60" ht="195" customHeight="1">
-      <c r="B60" s="96" t="inlineStr">
+      <c r="B60" s="99" t="inlineStr">
         <is>
           <t>{
   "EventId": "a1b2c3",
@@ -8118,7 +8221,7 @@
       <c r="X2" s="15" t="n"/>
       <c r="Y2" s="17" t="inlineStr">
         <is>
-          <t>2026/07/12</t>
+          <t>2026/07/13</t>
         </is>
       </c>
       <c r="Z2" s="18" t="n"/>
@@ -8154,7 +8257,7 @@
     <row r="5" ht="18" customHeight="1">
       <c r="B5" s="24" t="inlineStr">
         <is>
-          <t>デバイスアクセスとデバイスコネクタが参照する設定の責務、および対象デバイス固有の実行条件を定義する。</t>
+          <t>デバイス制御層とデバイスコネクタが参照する設定の責務、および対象デバイス固有の実行条件を定義する。</t>
         </is>
       </c>
     </row>
@@ -8185,13 +8288,13 @@
       <c r="J8" s="5" t="n"/>
       <c r="K8" s="5" t="n"/>
       <c r="L8" s="5" t="n"/>
-      <c r="M8" s="6" t="n"/>
-      <c r="N8" s="26" t="inlineStr">
+      <c r="M8" s="5" t="n"/>
+      <c r="N8" s="6" t="n"/>
+      <c r="O8" s="26" t="inlineStr">
         <is>
           <t>読込主体</t>
         </is>
       </c>
-      <c r="O8" s="5" t="n"/>
       <c r="P8" s="5" t="n"/>
       <c r="Q8" s="5" t="n"/>
       <c r="R8" s="5" t="n"/>
@@ -8228,13 +8331,13 @@
       <c r="J9" s="28" t="n"/>
       <c r="K9" s="28" t="n"/>
       <c r="L9" s="28" t="n"/>
-      <c r="M9" s="29" t="n"/>
-      <c r="N9" s="16" t="inlineStr">
-        <is>
-          <t>タブレットPOS端末アプリ / デバイスアクセス</t>
-        </is>
-      </c>
-      <c r="O9" s="28" t="n"/>
+      <c r="M9" s="28" t="n"/>
+      <c r="N9" s="29" t="n"/>
+      <c r="O9" s="16" t="inlineStr">
+        <is>
+          <t>タブレットPOS端末アプリ / デバイス制御層</t>
+        </is>
+      </c>
       <c r="P9" s="28" t="n"/>
       <c r="Q9" s="28" t="n"/>
       <c r="R9" s="28" t="n"/>
@@ -8271,13 +8374,13 @@
       <c r="J10" s="34" t="n"/>
       <c r="K10" s="34" t="n"/>
       <c r="L10" s="34" t="n"/>
-      <c r="M10" s="35" t="n"/>
-      <c r="N10" s="44" t="inlineStr">
+      <c r="M10" s="34" t="n"/>
+      <c r="N10" s="35" t="n"/>
+      <c r="O10" s="44" t="inlineStr">
         <is>
           <t>デバイスコネクタ / デバイス管理</t>
         </is>
       </c>
-      <c r="O10" s="34" t="n"/>
       <c r="P10" s="34" t="n"/>
       <c r="Q10" s="34" t="n"/>
       <c r="R10" s="34" t="n"/>
@@ -9758,17 +9861,14 @@
   <mergeCells count="179">
     <mergeCell ref="Q14:S14"/>
     <mergeCell ref="F27:I27"/>
-    <mergeCell ref="E10:M10"/>
     <mergeCell ref="S21:T21"/>
     <mergeCell ref="C31:E31"/>
     <mergeCell ref="C21:E21"/>
-    <mergeCell ref="N8:S8"/>
     <mergeCell ref="V48:Z48"/>
     <mergeCell ref="O23:R23"/>
     <mergeCell ref="Q41:Z41"/>
     <mergeCell ref="Q15:S15"/>
     <mergeCell ref="C23:E23"/>
-    <mergeCell ref="N10:S10"/>
     <mergeCell ref="B42:F42"/>
     <mergeCell ref="W1:X1"/>
     <mergeCell ref="K14:P14"/>
@@ -9810,11 +9910,13 @@
     <mergeCell ref="S22:T22"/>
     <mergeCell ref="O27:R27"/>
     <mergeCell ref="J48:N48"/>
+    <mergeCell ref="O10:S10"/>
     <mergeCell ref="J29:N29"/>
     <mergeCell ref="U25:Z25"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="C22:E22"/>
     <mergeCell ref="E48:F48"/>
+    <mergeCell ref="O9:S9"/>
     <mergeCell ref="B6:Z6"/>
     <mergeCell ref="B10:D10"/>
     <mergeCell ref="H2:Q3"/>
@@ -9833,6 +9935,7 @@
     <mergeCell ref="J26:N26"/>
     <mergeCell ref="U20:Z20"/>
     <mergeCell ref="A1:D3"/>
+    <mergeCell ref="E8:N8"/>
     <mergeCell ref="U23:Z23"/>
     <mergeCell ref="F30:I30"/>
     <mergeCell ref="S24:T24"/>
@@ -9843,11 +9946,13 @@
     <mergeCell ref="F20:I20"/>
     <mergeCell ref="Q16:S16"/>
     <mergeCell ref="U22:Z22"/>
+    <mergeCell ref="E10:N10"/>
     <mergeCell ref="F33:I33"/>
     <mergeCell ref="C24:E24"/>
     <mergeCell ref="K15:P15"/>
     <mergeCell ref="C33:E33"/>
     <mergeCell ref="O31:R31"/>
+    <mergeCell ref="E9:N9"/>
     <mergeCell ref="O21:R21"/>
     <mergeCell ref="C26:E26"/>
     <mergeCell ref="R1:S1"/>
@@ -9894,7 +9999,6 @@
     <mergeCell ref="O48:R48"/>
     <mergeCell ref="T16:Z16"/>
     <mergeCell ref="G49:I49"/>
-    <mergeCell ref="E9:M9"/>
     <mergeCell ref="W2:X3"/>
     <mergeCell ref="S27:T27"/>
     <mergeCell ref="S49:U49"/>
@@ -9902,7 +10006,6 @@
     <mergeCell ref="C27:E27"/>
     <mergeCell ref="B5:Z5"/>
     <mergeCell ref="B45:Z45"/>
-    <mergeCell ref="N9:S9"/>
     <mergeCell ref="O24:R24"/>
     <mergeCell ref="O33:R33"/>
     <mergeCell ref="Q37:Z37"/>
@@ -9921,15 +10024,15 @@
     <mergeCell ref="K16:P16"/>
     <mergeCell ref="S47:U47"/>
     <mergeCell ref="F32:I32"/>
+    <mergeCell ref="O8:S8"/>
     <mergeCell ref="F26:I26"/>
     <mergeCell ref="J21:N21"/>
     <mergeCell ref="S29:T29"/>
     <mergeCell ref="U27:Z27"/>
     <mergeCell ref="G48:I48"/>
-    <mergeCell ref="E8:M8"/>
+    <mergeCell ref="O50:R50"/>
     <mergeCell ref="C29:E29"/>
     <mergeCell ref="U30:Z30"/>
-    <mergeCell ref="O50:R50"/>
     <mergeCell ref="V47:Z47"/>
     <mergeCell ref="J23:N23"/>
     <mergeCell ref="B41:F41"/>
@@ -10090,7 +10193,7 @@
       <c r="X2" s="15" t="n"/>
       <c r="Y2" s="17" t="inlineStr">
         <is>
-          <t>2026/07/12</t>
+          <t>2026/07/13</t>
         </is>
       </c>
       <c r="Z2" s="18" t="n"/>
@@ -12957,7 +13060,7 @@
       <c r="X2" s="15" t="n"/>
       <c r="Y2" s="17" t="inlineStr">
         <is>
-          <t>2026/07/12</t>
+          <t>2026/07/13</t>
         </is>
       </c>
       <c r="Z2" s="18" t="n"/>
@@ -14132,7 +14235,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Z17"/>
+  <dimension ref="A1:Z19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -14266,7 +14369,7 @@
       <c r="X2" s="15" t="n"/>
       <c r="Y2" s="17" t="inlineStr">
         <is>
-          <t>2026/07/12</t>
+          <t>2026/07/13</t>
         </is>
       </c>
       <c r="Z2" s="18" t="n"/>
@@ -14356,19 +14459,19 @@
     <row r="7" ht="36" customHeight="1">
       <c r="B7" s="27" t="inlineStr">
         <is>
-          <t>0.3.0</t>
+          <t>0.3.2</t>
         </is>
       </c>
       <c r="C7" s="29" t="n"/>
       <c r="D7" s="16" t="inlineStr">
         <is>
-          <t>2026/07/12</t>
+          <t>2026/07/13</t>
         </is>
       </c>
       <c r="E7" s="29" t="n"/>
       <c r="F7" s="16" t="inlineStr">
         <is>
-          <t>システム全体、責務グループ、構成要素、機能の順に理解できる構成へ再設計。3つの図と本文の役割を整理し、重複していた処理説明を各設計章へ集約。</t>
+          <t>補足コメントの色指定と透過率の記載を分離し、淡い黄色の背景、黄土色の枠線、および濃い灰色の文字で表示する規約を明確化。</t>
         </is>
       </c>
       <c r="G7" s="28" t="n"/>
@@ -14403,19 +14506,19 @@
     <row r="8" ht="36" customHeight="1">
       <c r="B8" s="31" t="inlineStr">
         <is>
-          <t>0.2.29</t>
+          <t>0.3.1</t>
         </is>
       </c>
       <c r="C8" s="29" t="n"/>
       <c r="D8" s="32" t="inlineStr">
         <is>
-          <t>2026/07/11</t>
+          <t>2026/07/13</t>
         </is>
       </c>
       <c r="E8" s="29" t="n"/>
       <c r="F8" s="32" t="inlineStr">
         <is>
-          <t>対象デバイスを対象範囲へ統合し、単独のデバイス別設計を廃止。機能詳細の手順表示と各一覧の番号付けを整理。</t>
+          <t>図の関係について、矢印の向きと色・線種の役割を分離し、主処理、コマンド通信、実機制御、非同期イベント、設定参照、および異常経路の表示規約を明確化。</t>
         </is>
       </c>
       <c r="G8" s="28" t="n"/>
@@ -14450,19 +14553,19 @@
     <row r="9" ht="36" customHeight="1">
       <c r="B9" s="27" t="inlineStr">
         <is>
-          <t>0.2.28</t>
+          <t>0.3.0</t>
         </is>
       </c>
       <c r="C9" s="29" t="n"/>
       <c r="D9" s="16" t="inlineStr">
         <is>
-          <t>2026/07/11</t>
+          <t>2026/07/12</t>
         </is>
       </c>
       <c r="E9" s="29" t="n"/>
       <c r="F9" s="16" t="inlineStr">
         <is>
-          <t>通常運用フローと重複していたライフサイクル設計を統合し、管理責務および保守・デバッグ時の扱いを通常運用説明へ集約。</t>
+          <t>システム全体、責務グループ、構成要素、機能の順に理解できる構成へ再設計。3つの図と本文の役割を整理し、重複していた処理説明を各設計章へ集約。</t>
         </is>
       </c>
       <c r="G9" s="28" t="n"/>
@@ -14494,10 +14597,10 @@
       <c r="Y9" s="28" t="n"/>
       <c r="Z9" s="30" t="n"/>
     </row>
-    <row r="10" ht="24" customHeight="1">
+    <row r="10" ht="36" customHeight="1">
       <c r="B10" s="31" t="inlineStr">
         <is>
-          <t>0.2.27</t>
+          <t>0.2.29</t>
         </is>
       </c>
       <c r="C10" s="29" t="n"/>
@@ -14509,7 +14612,7 @@
       <c r="E10" s="29" t="n"/>
       <c r="F10" s="32" t="inlineStr">
         <is>
-          <t>理解しにくい構成要素だけに表示する補足コメントの表示規約を汎用へ追加。</t>
+          <t>対象デバイスを対象範囲へ統合し、単独のデバイス別設計を廃止。機能詳細の手順表示と各一覧の番号付けを整理。</t>
         </is>
       </c>
       <c r="G10" s="28" t="n"/>
@@ -14544,7 +14647,7 @@
     <row r="11" ht="36" customHeight="1">
       <c r="B11" s="27" t="inlineStr">
         <is>
-          <t>0.2.26</t>
+          <t>0.2.28</t>
         </is>
       </c>
       <c r="C11" s="29" t="n"/>
@@ -14556,7 +14659,7 @@
       <c r="E11" s="29" t="n"/>
       <c r="F11" s="16" t="inlineStr">
         <is>
-          <t>デバイス操作要求処理とライフサイクルを通常運用フローへ統合し、起動・操作・終了および主要異常経路を1図で確認できる構成へ変更。</t>
+          <t>通常運用フローと重複していたライフサイクル設計を統合し、管理責務および保守・デバッグ時の扱いを通常運用説明へ集約。</t>
         </is>
       </c>
       <c r="G11" s="28" t="n"/>
@@ -14588,10 +14691,10 @@
       <c r="Y11" s="28" t="n"/>
       <c r="Z11" s="30" t="n"/>
     </row>
-    <row r="12" ht="36" customHeight="1">
+    <row r="12" ht="24" customHeight="1">
       <c r="B12" s="31" t="inlineStr">
         <is>
-          <t>0.2.25</t>
+          <t>0.2.27</t>
         </is>
       </c>
       <c r="C12" s="29" t="n"/>
@@ -14603,7 +14706,7 @@
       <c r="E12" s="29" t="n"/>
       <c r="F12" s="32" t="inlineStr">
         <is>
-          <t>通信再試行、再送禁止、イベント再接続、異常種別、および稼働確認の時間条件を各処理図へ反映。</t>
+          <t>理解しにくい構成要素だけに表示する補足コメントの表示規約を汎用へ追加。</t>
         </is>
       </c>
       <c r="G12" s="28" t="n"/>
@@ -14635,10 +14738,10 @@
       <c r="Y12" s="28" t="n"/>
       <c r="Z12" s="30" t="n"/>
     </row>
-    <row r="13" ht="54" customHeight="1">
+    <row r="13" ht="36" customHeight="1">
       <c r="B13" s="27" t="inlineStr">
         <is>
-          <t>0.2.24</t>
+          <t>0.2.26</t>
         </is>
       </c>
       <c r="C13" s="29" t="n"/>
@@ -14650,7 +14753,7 @@
       <c r="E13" s="29" t="n"/>
       <c r="F13" s="16" t="inlineStr">
         <is>
-          <t>プロセス起動準備確認、所有プロセスの停止、非同期イベント受信、通信再試行、設定読込、エラー処理、およびログを設計方針として確定。全体構成とライフサイクルを更新。</t>
+          <t>デバイス操作要求処理とライフサイクルを通常運用フローへ統合し、起動・操作・終了および主要異常経路を1図で確認できる構成へ変更。</t>
         </is>
       </c>
       <c r="G13" s="28" t="n"/>
@@ -14685,7 +14788,7 @@
     <row r="14" ht="36" customHeight="1">
       <c r="B14" s="31" t="inlineStr">
         <is>
-          <t>0.2.23</t>
+          <t>0.2.25</t>
         </is>
       </c>
       <c r="C14" s="29" t="n"/>
@@ -14697,7 +14800,7 @@
       <c r="E14" s="29" t="n"/>
       <c r="F14" s="32" t="inlineStr">
         <is>
-          <t>同期応答経路とプロセス終了確認を明確化し、デバイス操作失敗と通信失敗を分離。通常の停止制御と対象外デバイス記載をエラー一覧から整理。</t>
+          <t>通信再試行、再送禁止、イベント再接続、異常種別、および稼働確認の時間条件を各処理図へ反映。</t>
         </is>
       </c>
       <c r="G14" s="28" t="n"/>
@@ -14729,22 +14832,22 @@
       <c r="Y14" s="28" t="n"/>
       <c r="Z14" s="30" t="n"/>
     </row>
-    <row r="15" ht="36" customHeight="1">
+    <row r="15" ht="54" customHeight="1">
       <c r="B15" s="27" t="inlineStr">
         <is>
-          <t>0.2.21</t>
+          <t>0.2.24</t>
         </is>
       </c>
       <c r="C15" s="29" t="n"/>
       <c r="D15" s="16" t="inlineStr">
         <is>
-          <t>2026/07/10</t>
+          <t>2026/07/11</t>
         </is>
       </c>
       <c r="E15" s="29" t="n"/>
       <c r="F15" s="16" t="inlineStr">
         <is>
-          <t>全体構成を、3つの責務領域と主経路を示す全体概要図、および詳細構成図の2段構成へ変更。</t>
+          <t>プロセス起動準備確認、所有プロセスの停止、非同期イベント受信、通信再試行、設定読込、エラー処理、およびログを設計方針として確定。全体構成とライフサイクルを更新。</t>
         </is>
       </c>
       <c r="G15" s="28" t="n"/>
@@ -14776,22 +14879,22 @@
       <c r="Y15" s="28" t="n"/>
       <c r="Z15" s="30" t="n"/>
     </row>
-    <row r="16" ht="24" customHeight="1">
+    <row r="16" ht="36" customHeight="1">
       <c r="B16" s="31" t="inlineStr">
         <is>
-          <t>0.2.16</t>
+          <t>0.2.23</t>
         </is>
       </c>
       <c r="C16" s="29" t="n"/>
       <c r="D16" s="32" t="inlineStr">
         <is>
-          <t>2026/07/10</t>
+          <t>2026/07/11</t>
         </is>
       </c>
       <c r="E16" s="29" t="n"/>
       <c r="F16" s="32" t="inlineStr">
         <is>
-          <t>本文と図の論理名称を日本語へ統一し、物理識別子の記載箇所を整理。</t>
+          <t>同期応答経路とプロセス終了確認を明確化し、デバイス操作失敗と通信失敗を分離。通常の停止制御と対象外デバイス記載をエラー一覧から整理。</t>
         </is>
       </c>
       <c r="G16" s="28" t="n"/>
@@ -14823,129 +14926,233 @@
       <c r="Y16" s="28" t="n"/>
       <c r="Z16" s="30" t="n"/>
     </row>
-    <row r="17" ht="24" customHeight="1">
-      <c r="B17" s="33" t="inlineStr">
+    <row r="17" ht="36" customHeight="1">
+      <c r="B17" s="27" t="inlineStr">
+        <is>
+          <t>0.2.21</t>
+        </is>
+      </c>
+      <c r="C17" s="29" t="n"/>
+      <c r="D17" s="16" t="inlineStr">
+        <is>
+          <t>2026/07/10</t>
+        </is>
+      </c>
+      <c r="E17" s="29" t="n"/>
+      <c r="F17" s="16" t="inlineStr">
+        <is>
+          <t>全体構成を、3つの責務領域と主経路を示す全体概要図、および詳細構成図の2段構成へ変更。</t>
+        </is>
+      </c>
+      <c r="G17" s="28" t="n"/>
+      <c r="H17" s="28" t="n"/>
+      <c r="I17" s="28" t="n"/>
+      <c r="J17" s="28" t="n"/>
+      <c r="K17" s="28" t="n"/>
+      <c r="L17" s="28" t="n"/>
+      <c r="M17" s="28" t="n"/>
+      <c r="N17" s="28" t="n"/>
+      <c r="O17" s="28" t="n"/>
+      <c r="P17" s="28" t="n"/>
+      <c r="Q17" s="28" t="n"/>
+      <c r="R17" s="29" t="n"/>
+      <c r="S17" s="16" t="inlineStr">
+        <is>
+          <t>VTI サム</t>
+        </is>
+      </c>
+      <c r="T17" s="28" t="n"/>
+      <c r="U17" s="28" t="n"/>
+      <c r="V17" s="29" t="n"/>
+      <c r="W17" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X17" s="28" t="n"/>
+      <c r="Y17" s="28" t="n"/>
+      <c r="Z17" s="30" t="n"/>
+    </row>
+    <row r="18" ht="24" customHeight="1">
+      <c r="B18" s="31" t="inlineStr">
+        <is>
+          <t>0.2.16</t>
+        </is>
+      </c>
+      <c r="C18" s="29" t="n"/>
+      <c r="D18" s="32" t="inlineStr">
+        <is>
+          <t>2026/07/10</t>
+        </is>
+      </c>
+      <c r="E18" s="29" t="n"/>
+      <c r="F18" s="32" t="inlineStr">
+        <is>
+          <t>本文と図の論理名称を日本語へ統一し、物理識別子の記載箇所を整理。</t>
+        </is>
+      </c>
+      <c r="G18" s="28" t="n"/>
+      <c r="H18" s="28" t="n"/>
+      <c r="I18" s="28" t="n"/>
+      <c r="J18" s="28" t="n"/>
+      <c r="K18" s="28" t="n"/>
+      <c r="L18" s="28" t="n"/>
+      <c r="M18" s="28" t="n"/>
+      <c r="N18" s="28" t="n"/>
+      <c r="O18" s="28" t="n"/>
+      <c r="P18" s="28" t="n"/>
+      <c r="Q18" s="28" t="n"/>
+      <c r="R18" s="29" t="n"/>
+      <c r="S18" s="32" t="inlineStr">
+        <is>
+          <t>VTI サム</t>
+        </is>
+      </c>
+      <c r="T18" s="28" t="n"/>
+      <c r="U18" s="28" t="n"/>
+      <c r="V18" s="29" t="n"/>
+      <c r="W18" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X18" s="28" t="n"/>
+      <c r="Y18" s="28" t="n"/>
+      <c r="Z18" s="30" t="n"/>
+    </row>
+    <row r="19" ht="24" customHeight="1">
+      <c r="B19" s="33" t="inlineStr">
         <is>
           <t>0.2.8</t>
         </is>
       </c>
-      <c r="C17" s="35" t="n"/>
-      <c r="D17" s="36" t="inlineStr">
+      <c r="C19" s="35" t="n"/>
+      <c r="D19" s="36" t="inlineStr">
         <is>
           <t>2026/07/08</t>
         </is>
       </c>
-      <c r="E17" s="35" t="n"/>
-      <c r="F17" s="36" t="inlineStr">
+      <c r="E19" s="35" t="n"/>
+      <c r="F19" s="36" t="inlineStr">
         <is>
           <t>デバイスコネクタの基本設計書として新規作成。</t>
         </is>
       </c>
-      <c r="G17" s="34" t="n"/>
-      <c r="H17" s="34" t="n"/>
-      <c r="I17" s="34" t="n"/>
-      <c r="J17" s="34" t="n"/>
-      <c r="K17" s="34" t="n"/>
-      <c r="L17" s="34" t="n"/>
-      <c r="M17" s="34" t="n"/>
-      <c r="N17" s="34" t="n"/>
-      <c r="O17" s="34" t="n"/>
-      <c r="P17" s="34" t="n"/>
-      <c r="Q17" s="34" t="n"/>
-      <c r="R17" s="35" t="n"/>
-      <c r="S17" s="36" t="inlineStr">
+      <c r="G19" s="34" t="n"/>
+      <c r="H19" s="34" t="n"/>
+      <c r="I19" s="34" t="n"/>
+      <c r="J19" s="34" t="n"/>
+      <c r="K19" s="34" t="n"/>
+      <c r="L19" s="34" t="n"/>
+      <c r="M19" s="34" t="n"/>
+      <c r="N19" s="34" t="n"/>
+      <c r="O19" s="34" t="n"/>
+      <c r="P19" s="34" t="n"/>
+      <c r="Q19" s="34" t="n"/>
+      <c r="R19" s="35" t="n"/>
+      <c r="S19" s="36" t="inlineStr">
         <is>
           <t>VTI サム</t>
         </is>
       </c>
-      <c r="T17" s="34" t="n"/>
-      <c r="U17" s="34" t="n"/>
-      <c r="V17" s="35" t="n"/>
-      <c r="W17" s="36" t="inlineStr">
+      <c r="T19" s="34" t="n"/>
+      <c r="U19" s="34" t="n"/>
+      <c r="V19" s="35" t="n"/>
+      <c r="W19" s="36" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="X17" s="34" t="n"/>
-      <c r="Y17" s="34" t="n"/>
-      <c r="Z17" s="37" t="n"/>
+      <c r="X19" s="34" t="n"/>
+      <c r="Y19" s="34" t="n"/>
+      <c r="Z19" s="37" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="74">
+  <mergeCells count="84">
+    <mergeCell ref="W9:Z9"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="W13:Z13"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="W1:X1"/>
+    <mergeCell ref="Y1:Z1"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="F11:R11"/>
+    <mergeCell ref="W15:Z15"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="S7:V7"/>
+    <mergeCell ref="F15:R15"/>
+    <mergeCell ref="E2:G3"/>
+    <mergeCell ref="Y2:Z3"/>
+    <mergeCell ref="S19:V19"/>
     <mergeCell ref="S9:V9"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="D10:E10"/>
+    <mergeCell ref="F13:R13"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="W14:Z14"/>
+    <mergeCell ref="H2:Q3"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="S12:V12"/>
+    <mergeCell ref="W6:Z6"/>
+    <mergeCell ref="F19:R19"/>
+    <mergeCell ref="F16:R16"/>
+    <mergeCell ref="F6:R6"/>
+    <mergeCell ref="A1:D3"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="F17:R17"/>
+    <mergeCell ref="W16:Z16"/>
+    <mergeCell ref="S10:V10"/>
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="W18:Z18"/>
     <mergeCell ref="B7:C7"/>
-    <mergeCell ref="W9:Z9"/>
-    <mergeCell ref="F13:R13"/>
     <mergeCell ref="F9:R9"/>
     <mergeCell ref="W8:Z8"/>
     <mergeCell ref="W17:Z17"/>
     <mergeCell ref="W11:Z11"/>
-    <mergeCell ref="W2:X3"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="W14:Z14"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="H2:Q3"/>
-    <mergeCell ref="F14:R14"/>
     <mergeCell ref="T1:V1"/>
-    <mergeCell ref="W13:Z13"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B5:Z5"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="W1:X1"/>
-    <mergeCell ref="S16:V16"/>
-    <mergeCell ref="Y1:Z1"/>
+    <mergeCell ref="W19:Z19"/>
     <mergeCell ref="R2:S3"/>
-    <mergeCell ref="W10:Z10"/>
-    <mergeCell ref="B14:C14"/>
     <mergeCell ref="B17:C17"/>
-    <mergeCell ref="S12:V12"/>
     <mergeCell ref="H1:Q1"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="F11:R11"/>
-    <mergeCell ref="W6:Z6"/>
-    <mergeCell ref="W15:Z15"/>
     <mergeCell ref="D17:E17"/>
     <mergeCell ref="F10:R10"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="F16:R16"/>
-    <mergeCell ref="F6:R6"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="F7:R7"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="S14:V14"/>
+    <mergeCell ref="T2:V3"/>
+    <mergeCell ref="F18:R18"/>
+    <mergeCell ref="S13:V13"/>
+    <mergeCell ref="F8:R8"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="W7:Z7"/>
+    <mergeCell ref="S6:V6"/>
+    <mergeCell ref="S15:V15"/>
+    <mergeCell ref="W2:X3"/>
+    <mergeCell ref="F14:R14"/>
+    <mergeCell ref="B5:Z5"/>
+    <mergeCell ref="S16:V16"/>
+    <mergeCell ref="W10:Z10"/>
+    <mergeCell ref="B8:C8"/>
     <mergeCell ref="D16:E16"/>
-    <mergeCell ref="A1:D3"/>
-    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="S18:V18"/>
     <mergeCell ref="S8:V8"/>
-    <mergeCell ref="F7:R7"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="S17:V17"/>
     <mergeCell ref="S11:V11"/>
     <mergeCell ref="F12:R12"/>
-    <mergeCell ref="S7:V7"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="F15:R15"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="S14:V14"/>
+    <mergeCell ref="D18:E18"/>
     <mergeCell ref="D8:E8"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="T2:V3"/>
-    <mergeCell ref="E2:G3"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="S13:V13"/>
-    <mergeCell ref="F17:R17"/>
-    <mergeCell ref="Y2:Z3"/>
-    <mergeCell ref="F8:R8"/>
-    <mergeCell ref="W16:Z16"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="W7:Z7"/>
-    <mergeCell ref="S10:V10"/>
     <mergeCell ref="W12:Z12"/>
-    <mergeCell ref="S6:V6"/>
-    <mergeCell ref="R1:S1"/>
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="S15:V15"/>
   </mergeCells>
   <printOptions gridLines="0"/>
   <pageMargins left="0.35" right="0.35" top="0.45" bottom="0.35" header="0.5" footer="0.5"/>
@@ -15101,7 +15308,7 @@
       <c r="X2" s="15" t="n"/>
       <c r="Y2" s="17" t="inlineStr">
         <is>
-          <t>2026/07/12</t>
+          <t>2026/07/13</t>
         </is>
       </c>
       <c r="Z2" s="18" t="n"/>
@@ -15977,7 +16184,7 @@
       <c r="X2" s="15" t="n"/>
       <c r="Y2" s="17" t="inlineStr">
         <is>
-          <t>2026/07/12</t>
+          <t>2026/07/13</t>
         </is>
       </c>
       <c r="Z2" s="18" t="n"/>
@@ -16034,7 +16241,7 @@
     <row r="9" ht="42" customHeight="1">
       <c r="B9" s="24" t="inlineStr">
         <is>
-          <t>アプリケーション層は業務上必要なデバイス操作をデバイス制御へ依頼する。デバイス制御は要求と結果をアプリ内の形式へ変換し、名前付きパイプを介してデバイスコネクタと通信する。デバイスコネクタは要求順序の保証、対象デバイスの選択、既存資源を利用した実機制御、および非同期イベント配信を担当する。この境界により、アプリケーション層はデバイスコネクタ内部や個別デバイス実装を直接呼び出さない。</t>
+          <t>アプリケーション層は業務上必要なデバイス操作をデバイス制御層へ依頼する。デバイス制御層は要求と結果をアプリ内の形式へ変換し、名前付きパイプを介してデバイスコネクタと通信する。デバイスコネクタは要求順序の保証、対象デバイスの選択、既存資源を利用した実機制御、および非同期イベント配信を担当する。この境界により、アプリケーション層はデバイスコネクタ内部や個別デバイス実装を直接呼び出さない。</t>
         </is>
       </c>
     </row>
@@ -16779,7 +16986,7 @@
       <c r="X2" s="15" t="n"/>
       <c r="Y2" s="17" t="inlineStr">
         <is>
-          <t>2026/07/12</t>
+          <t>2026/07/13</t>
         </is>
       </c>
       <c r="Z2" s="18" t="n"/>
@@ -17298,7 +17505,7 @@
       <c r="X2" s="15" t="n"/>
       <c r="Y2" s="17" t="inlineStr">
         <is>
-          <t>2026/07/12</t>
+          <t>2026/07/13</t>
         </is>
       </c>
       <c r="Z2" s="18" t="n"/>
@@ -18005,7 +18212,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Z114"/>
+  <dimension ref="A1:Z116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -18139,7 +18346,7 @@
       <c r="X2" s="15" t="n"/>
       <c r="Y2" s="17" t="inlineStr">
         <is>
-          <t>2026/07/12</t>
+          <t>2026/07/13</t>
         </is>
       </c>
       <c r="Z2" s="18" t="n"/>
@@ -18200,124 +18407,112 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="B10" s="52" t="inlineStr">
+    <row r="10" ht="28" customHeight="1">
+      <c r="B10" s="24" t="inlineStr">
+        <is>
+          <t>矢印の向きは関係の方向を示し、色と線種は関係の意味を示す。要求と同期応答、または実機制御と結果を1つの通信経路で送受信する関係のみを双方向で示し、その他の処理順、制御、通知、参照、および異常分岐は一方向で示す。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="B11" s="52" t="inlineStr">
         <is>
           <t>（1）タブレットPOS端末アプリ</t>
         </is>
       </c>
-      <c r="C10" s="53" t="n"/>
-      <c r="D10" s="53" t="n"/>
-      <c r="E10" s="53" t="n"/>
-      <c r="F10" s="53" t="n"/>
-      <c r="G10" s="53" t="n"/>
-      <c r="H10" s="53" t="n"/>
-      <c r="I10" s="54" t="n"/>
-      <c r="J10" s="55" t="inlineStr">
+      <c r="C11" s="53" t="n"/>
+      <c r="D11" s="53" t="n"/>
+      <c r="E11" s="53" t="n"/>
+      <c r="F11" s="53" t="n"/>
+      <c r="G11" s="53" t="n"/>
+      <c r="H11" s="53" t="n"/>
+      <c r="I11" s="54" t="n"/>
+      <c r="J11" s="55" t="inlineStr">
         <is>
           <t>アプリケーション層とデバイス制御を含むアプリプロセスの責務境界を示す。</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="B11" s="56" t="inlineStr">
+    <row r="12" ht="20" customHeight="1">
+      <c r="B12" s="56" t="inlineStr">
         <is>
           <t>（2）デバイスコネクタ</t>
         </is>
       </c>
-      <c r="C11" s="57" t="n"/>
-      <c r="D11" s="57" t="n"/>
-      <c r="E11" s="57" t="n"/>
-      <c r="F11" s="57" t="n"/>
-      <c r="G11" s="57" t="n"/>
-      <c r="H11" s="57" t="n"/>
-      <c r="I11" s="58" t="n"/>
-      <c r="J11" s="55" t="inlineStr">
+      <c r="C12" s="57" t="n"/>
+      <c r="D12" s="57" t="n"/>
+      <c r="E12" s="57" t="n"/>
+      <c r="F12" s="57" t="n"/>
+      <c r="G12" s="57" t="n"/>
+      <c r="H12" s="57" t="n"/>
+      <c r="I12" s="58" t="n"/>
+      <c r="J12" s="55" t="inlineStr">
         <is>
           <t>通信、コマンド実行、デバイス管理、および実機制御を担当する独立プロセスを示す。</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="B12" s="59" t="inlineStr">
+    <row r="13" ht="20" customHeight="1">
+      <c r="B13" s="59" t="inlineStr">
         <is>
           <t>（3）周辺機器</t>
         </is>
       </c>
-      <c r="C12" s="60" t="n"/>
-      <c r="D12" s="60" t="n"/>
-      <c r="E12" s="60" t="n"/>
-      <c r="F12" s="60" t="n"/>
-      <c r="G12" s="60" t="n"/>
-      <c r="H12" s="60" t="n"/>
-      <c r="I12" s="61" t="n"/>
-      <c r="J12" s="55" t="inlineStr">
+      <c r="C13" s="60" t="n"/>
+      <c r="D13" s="60" t="n"/>
+      <c r="E13" s="60" t="n"/>
+      <c r="F13" s="60" t="n"/>
+      <c r="G13" s="60" t="n"/>
+      <c r="H13" s="60" t="n"/>
+      <c r="I13" s="61" t="n"/>
+      <c r="J13" s="55" t="inlineStr">
         <is>
           <t>デバイスコネクタから制御される実機を示す。</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="B13" s="62" t="inlineStr">
+    <row r="14" ht="20" customHeight="1">
+      <c r="B14" s="62" t="inlineStr">
         <is>
           <t>責務グループ</t>
         </is>
       </c>
-      <c r="C13" s="63" t="n"/>
-      <c r="D13" s="63" t="n"/>
-      <c r="E13" s="63" t="n"/>
-      <c r="F13" s="63" t="n"/>
-      <c r="G13" s="63" t="n"/>
-      <c r="H13" s="63" t="n"/>
-      <c r="I13" s="64" t="n"/>
-      <c r="J13" s="55" t="inlineStr">
+      <c r="C14" s="63" t="n"/>
+      <c r="D14" s="63" t="n"/>
+      <c r="E14" s="63" t="n"/>
+      <c r="F14" s="63" t="n"/>
+      <c r="G14" s="63" t="n"/>
+      <c r="H14" s="63" t="n"/>
+      <c r="I14" s="64" t="n"/>
+      <c r="J14" s="55" t="inlineStr">
         <is>
           <t>同じ目的を持つ論理構成要素のまとまりを示す。</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="B14" s="65" t="inlineStr">
+    <row r="15" ht="20" customHeight="1">
+      <c r="B15" s="65" t="inlineStr">
         <is>
           <t>角丸ブロック</t>
         </is>
       </c>
-      <c r="C14" s="66" t="n"/>
-      <c r="D14" s="66" t="n"/>
-      <c r="E14" s="66" t="n"/>
-      <c r="F14" s="66" t="n"/>
-      <c r="G14" s="66" t="n"/>
-      <c r="H14" s="66" t="n"/>
-      <c r="I14" s="67" t="n"/>
-      <c r="J14" s="55" t="inlineStr">
+      <c r="C15" s="66" t="n"/>
+      <c r="D15" s="66" t="n"/>
+      <c r="E15" s="66" t="n"/>
+      <c r="F15" s="66" t="n"/>
+      <c r="G15" s="66" t="n"/>
+      <c r="H15" s="66" t="n"/>
+      <c r="I15" s="67" t="n"/>
+      <c r="J15" s="55" t="inlineStr">
         <is>
           <t>論理構成要素、処理、または対象デバイスを示す。</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="B15" s="68" t="inlineStr">
-        <is>
-          <t>◇</t>
-        </is>
-      </c>
-      <c r="C15" s="69" t="n"/>
-      <c r="D15" s="69" t="n"/>
-      <c r="E15" s="69" t="n"/>
-      <c r="F15" s="69" t="n"/>
-      <c r="G15" s="69" t="n"/>
-      <c r="H15" s="69" t="n"/>
-      <c r="I15" s="70" t="n"/>
-      <c r="J15" s="55" t="inlineStr">
-        <is>
-          <t>次の処理を決める判定を示す。</t>
         </is>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="B16" s="68" t="inlineStr">
         <is>
-          <t>補足コメント（角丸）</t>
+          <t>◇</t>
         </is>
       </c>
       <c r="C16" s="69" t="n"/>
@@ -18329,14 +18524,14 @@
       <c r="I16" s="70" t="n"/>
       <c r="J16" s="55" t="inlineStr">
         <is>
-          <t>図だけでは誤解しやすい制約がある場合に、対象要素の近くへ補足を表示する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="20" customHeight="1">
+          <t>次の処理を決める判定を示す。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="28" customHeight="1">
       <c r="B17" s="71" t="inlineStr">
         <is>
-          <t>異常処理</t>
+          <t>補足コメント（吹き出し・半透明）</t>
         </is>
       </c>
       <c r="C17" s="72" t="n"/>
@@ -18348,52 +18543,52 @@
       <c r="I17" s="73" t="n"/>
       <c r="J17" s="55" t="inlineStr">
         <is>
+          <t>70%透過の吹き出しで対象要素を指し示し、図だけでは判断しにくい設計意図、運用条件、または制約を補足する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="B18" s="74" t="inlineStr">
+        <is>
+          <t>異常処理</t>
+        </is>
+      </c>
+      <c r="C18" s="75" t="n"/>
+      <c r="D18" s="75" t="n"/>
+      <c r="E18" s="75" t="n"/>
+      <c r="F18" s="75" t="n"/>
+      <c r="G18" s="75" t="n"/>
+      <c r="H18" s="75" t="n"/>
+      <c r="I18" s="76" t="n"/>
+      <c r="J18" s="55" t="inlineStr">
+        <is>
           <t>起動中止、通信失敗、または強制終了などの主要な異常結果を示す。</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="B18" s="62" t="inlineStr">
+    <row r="19" ht="20" customHeight="1">
+      <c r="B19" s="62" t="inlineStr">
         <is>
           <t>運用フェーズ</t>
         </is>
       </c>
-      <c r="C18" s="63" t="n"/>
-      <c r="D18" s="63" t="n"/>
-      <c r="E18" s="63" t="n"/>
-      <c r="F18" s="63" t="n"/>
-      <c r="G18" s="63" t="n"/>
-      <c r="H18" s="63" t="n"/>
-      <c r="I18" s="64" t="n"/>
-      <c r="J18" s="55" t="inlineStr">
+      <c r="C19" s="63" t="n"/>
+      <c r="D19" s="63" t="n"/>
+      <c r="E19" s="63" t="n"/>
+      <c r="F19" s="63" t="n"/>
+      <c r="G19" s="63" t="n"/>
+      <c r="H19" s="63" t="n"/>
+      <c r="I19" s="64" t="n"/>
+      <c r="J19" s="55" t="inlineStr">
         <is>
           <t>起動、デバイス操作、および終了の区切りを示す。</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="20" customHeight="1">
-      <c r="B19" s="74" t="inlineStr">
-        <is>
-          <t>━━▶ 主処理</t>
-        </is>
-      </c>
-      <c r="C19" s="75" t="n"/>
-      <c r="D19" s="75" t="n"/>
-      <c r="E19" s="75" t="n"/>
-      <c r="F19" s="75" t="n"/>
-      <c r="G19" s="75" t="n"/>
-      <c r="H19" s="75" t="n"/>
-      <c r="I19" s="76" t="n"/>
-      <c r="J19" s="55" t="inlineStr">
-        <is>
-          <t>要求、同期応答、または通常の処理順を示す。</t>
         </is>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="B20" s="77" t="inlineStr">
         <is>
-          <t>━━▶ ライフサイクル</t>
+          <t>━━▶ 主処理</t>
         </is>
       </c>
       <c r="C20" s="78" t="n"/>
@@ -18405,95 +18600,131 @@
       <c r="I20" s="79" t="n"/>
       <c r="J20" s="55" t="inlineStr">
         <is>
+          <t>通常の処理順または一方向の要求を示す。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="B21" s="77" t="inlineStr">
+        <is>
+          <t>◀━━▶ コマンド通信</t>
+        </is>
+      </c>
+      <c r="C21" s="78" t="n"/>
+      <c r="D21" s="78" t="n"/>
+      <c r="E21" s="78" t="n"/>
+      <c r="F21" s="78" t="n"/>
+      <c r="G21" s="78" t="n"/>
+      <c r="H21" s="78" t="n"/>
+      <c r="I21" s="79" t="n"/>
+      <c r="J21" s="55" t="inlineStr">
+        <is>
+          <t>アプリからの要求とデバイスコネクタからの同期応答を同じ通信経路で送受信する関係を示す。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="B22" s="80" t="inlineStr">
+        <is>
+          <t>━━▶ ライフサイクル</t>
+        </is>
+      </c>
+      <c r="C22" s="81" t="n"/>
+      <c r="D22" s="81" t="n"/>
+      <c r="E22" s="81" t="n"/>
+      <c r="F22" s="81" t="n"/>
+      <c r="G22" s="81" t="n"/>
+      <c r="H22" s="81" t="n"/>
+      <c r="I22" s="82" t="n"/>
+      <c r="J22" s="55" t="inlineStr">
+        <is>
           <t>プロセスの起動、停止、および終了監視を示す。</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="B21" s="80" t="inlineStr">
+    <row r="23" ht="20" customHeight="1">
+      <c r="B23" s="83" t="inlineStr">
         <is>
           <t>◀━━▶ 実機制御</t>
         </is>
       </c>
-      <c r="C21" s="81" t="n"/>
-      <c r="D21" s="81" t="n"/>
-      <c r="E21" s="81" t="n"/>
-      <c r="F21" s="81" t="n"/>
-      <c r="G21" s="81" t="n"/>
-      <c r="H21" s="81" t="n"/>
-      <c r="I21" s="82" t="n"/>
-      <c r="J21" s="55" t="inlineStr">
+      <c r="C23" s="84" t="n"/>
+      <c r="D23" s="84" t="n"/>
+      <c r="E23" s="84" t="n"/>
+      <c r="F23" s="84" t="n"/>
+      <c r="G23" s="84" t="n"/>
+      <c r="H23" s="84" t="n"/>
+      <c r="I23" s="85" t="n"/>
+      <c r="J23" s="55" t="inlineStr">
         <is>
           <t>デバイスコネクタと周辺機器間の制御と結果を示す。</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="20" customHeight="1">
-      <c r="B22" s="83" t="inlineStr">
+    <row r="24" ht="20" customHeight="1">
+      <c r="B24" s="86" t="inlineStr">
         <is>
           <t>┄┄▶ 非同期イベント</t>
         </is>
       </c>
-      <c r="C22" s="84" t="n"/>
-      <c r="D22" s="84" t="n"/>
-      <c r="E22" s="84" t="n"/>
-      <c r="F22" s="84" t="n"/>
-      <c r="G22" s="84" t="n"/>
-      <c r="H22" s="84" t="n"/>
-      <c r="I22" s="85" t="n"/>
-      <c r="J22" s="55" t="inlineStr">
+      <c r="C24" s="87" t="n"/>
+      <c r="D24" s="87" t="n"/>
+      <c r="E24" s="87" t="n"/>
+      <c r="F24" s="87" t="n"/>
+      <c r="G24" s="87" t="n"/>
+      <c r="H24" s="87" t="n"/>
+      <c r="I24" s="88" t="n"/>
+      <c r="J24" s="55" t="inlineStr">
         <is>
           <t>同期応答とは別に通知されるデバイス処理結果を示す。</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="20" customHeight="1">
-      <c r="B23" s="86" t="inlineStr">
+    <row r="25" ht="20" customHeight="1">
+      <c r="B25" s="89" t="inlineStr">
         <is>
           <t>┈┈▶ 設定参照</t>
         </is>
       </c>
-      <c r="C23" s="87" t="n"/>
-      <c r="D23" s="87" t="n"/>
-      <c r="E23" s="87" t="n"/>
-      <c r="F23" s="87" t="n"/>
-      <c r="G23" s="87" t="n"/>
-      <c r="H23" s="87" t="n"/>
-      <c r="I23" s="88" t="n"/>
-      <c r="J23" s="55" t="inlineStr">
+      <c r="C25" s="90" t="n"/>
+      <c r="D25" s="90" t="n"/>
+      <c r="E25" s="90" t="n"/>
+      <c r="F25" s="90" t="n"/>
+      <c r="G25" s="90" t="n"/>
+      <c r="H25" s="90" t="n"/>
+      <c r="I25" s="91" t="n"/>
+      <c r="J25" s="55" t="inlineStr">
         <is>
           <t>設定情報を参照する関係を示す。</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="20" customHeight="1">
-      <c r="B24" s="89" t="inlineStr">
+    <row r="26" ht="20" customHeight="1">
+      <c r="B26" s="92" t="inlineStr">
         <is>
           <t>┄┄▶ 異常経路</t>
         </is>
       </c>
-      <c r="C24" s="90" t="n"/>
-      <c r="D24" s="90" t="n"/>
-      <c r="E24" s="90" t="n"/>
-      <c r="F24" s="90" t="n"/>
-      <c r="G24" s="90" t="n"/>
-      <c r="H24" s="90" t="n"/>
-      <c r="I24" s="91" t="n"/>
-      <c r="J24" s="55" t="inlineStr">
+      <c r="C26" s="93" t="n"/>
+      <c r="D26" s="93" t="n"/>
+      <c r="E26" s="93" t="n"/>
+      <c r="F26" s="93" t="n"/>
+      <c r="G26" s="93" t="n"/>
+      <c r="H26" s="93" t="n"/>
+      <c r="I26" s="94" t="n"/>
+      <c r="J26" s="55" t="inlineStr">
         <is>
           <t>通常経路から異常結果または復旧処理へ分岐する経路を示す。</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="B25" s="45" t="inlineStr">
+    <row r="27" ht="18" customHeight="1">
+      <c r="B27" s="45" t="inlineStr">
         <is>
           <t>■5.1.1 システムコンテキスト図</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="18" customHeight="1"/>
-    <row r="28" ht="18" customHeight="1"/>
     <row r="29" ht="18" customHeight="1"/>
     <row r="30" ht="18" customHeight="1"/>
     <row r="31" ht="18" customHeight="1"/>
@@ -18532,15 +18763,15 @@
     <row r="64" ht="18" customHeight="1"/>
     <row r="65" ht="18" customHeight="1"/>
     <row r="66" ht="18" customHeight="1"/>
-    <row r="67" ht="18" customHeight="1">
-      <c r="B67" s="45" t="inlineStr">
+    <row r="67" ht="18" customHeight="1"/>
+    <row r="68" ht="18" customHeight="1"/>
+    <row r="69" ht="18" customHeight="1">
+      <c r="B69" s="45" t="inlineStr">
         <is>
           <t>■5.1.2 論理構成図</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="18" customHeight="1"/>
-    <row r="70" ht="18" customHeight="1"/>
     <row r="71" ht="18" customHeight="1"/>
     <row r="72" ht="18" customHeight="1"/>
     <row r="73" ht="18" customHeight="1"/>
@@ -18579,59 +18810,63 @@
     <row r="106" ht="18" customHeight="1"/>
     <row r="107" ht="18" customHeight="1"/>
     <row r="108" ht="18" customHeight="1"/>
-    <row r="109" ht="18" customHeight="1">
-      <c r="B109" s="45" t="inlineStr">
+    <row r="109" ht="18" customHeight="1"/>
+    <row r="110" ht="18" customHeight="1"/>
+    <row r="111" ht="18" customHeight="1">
+      <c r="B111" s="45" t="inlineStr">
         <is>
           <t>■図の補足</t>
-        </is>
-      </c>
-    </row>
-    <row r="110" ht="18" customHeight="1">
-      <c r="B110" s="55" t="inlineStr">
-        <is>
-          <t>- システムコンテキスト図は、3つの責務領域、プロセス境界、および領域間の通信だけを示す。</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="18" customHeight="1">
-      <c r="B111" s="55" t="inlineStr">
-        <is>
-          <t>- 論理構成図は、各責務領域を責務グループと論理構成要素へ分解する。番号は5.3と対応する。</t>
         </is>
       </c>
     </row>
     <row r="112" ht="18" customHeight="1">
       <c r="B112" s="55" t="inlineStr">
         <is>
-          <t>- タブレットPOS端末アプリとデバイスコネクタは同一Windows端末上の別プロセスであり、要求、応答、およびイベント通知には名前付きパイプを使用する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" ht="28" customHeight="1">
+          <t>- システムコンテキスト図は、3つの責務領域、プロセス境界、および領域間の通信だけを示す。</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="18" customHeight="1">
       <c r="B113" s="55" t="inlineStr">
         <is>
-          <t>- アプリケーション層はデバイスコネクタ内部を直接呼び出さない。デバイス操作はデバイスアクセスを経由し、プロセスの起動・停止はデバイスコネクタプロセス管理が担当する。</t>
+          <t>- 論理構成図は、各責務領域を責務グループと論理構成要素へ分解する。番号は5.3と対応する。</t>
         </is>
       </c>
     </row>
     <row r="114" ht="18" customHeight="1">
       <c r="B114" s="55" t="inlineStr">
         <is>
+          <t>- タブレットPOS端末アプリとデバイスコネクタは同一Windows端末上の別プロセスであり、要求、応答、およびイベント通知には名前付きパイプを使用する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="28" customHeight="1">
+      <c r="B115" s="55" t="inlineStr">
+        <is>
+          <t>- アプリケーション層はデバイスコネクタ内部を直接呼び出さない。デバイス操作はデバイス制御層を経由し、プロセスの起動・停止はデバイスコネクタプロセス管理が担当する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="18" customHeight="1">
+      <c r="B116" s="55" t="inlineStr">
+        <is>
           <t>- 再試行、タイムアウト、所有プロセス、および異常分岐は静的構成ではなく、06_運用シナリオで示す。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="55">
+  <mergeCells count="58">
+    <mergeCell ref="B69:Z69"/>
     <mergeCell ref="J23:Z23"/>
+    <mergeCell ref="B10:Z10"/>
     <mergeCell ref="B112:Z112"/>
+    <mergeCell ref="B25:I25"/>
     <mergeCell ref="J17:Z17"/>
     <mergeCell ref="B16:I16"/>
     <mergeCell ref="B9:Z9"/>
     <mergeCell ref="B22:I22"/>
     <mergeCell ref="W2:X3"/>
     <mergeCell ref="J14:Z14"/>
-    <mergeCell ref="J10:Z10"/>
     <mergeCell ref="B6:Z6"/>
     <mergeCell ref="J18:Z18"/>
     <mergeCell ref="J13:Z13"/>
@@ -18645,7 +18880,6 @@
     <mergeCell ref="B5:Z5"/>
     <mergeCell ref="B114:Z114"/>
     <mergeCell ref="W1:X1"/>
-    <mergeCell ref="B110:Z110"/>
     <mergeCell ref="Y1:Z1"/>
     <mergeCell ref="R2:S3"/>
     <mergeCell ref="B14:I14"/>
@@ -18656,13 +18890,15 @@
     <mergeCell ref="H1:Q1"/>
     <mergeCell ref="B17:I17"/>
     <mergeCell ref="B13:I13"/>
-    <mergeCell ref="B25:Z25"/>
-    <mergeCell ref="B109:Z109"/>
     <mergeCell ref="A1:D3"/>
+    <mergeCell ref="B116:Z116"/>
     <mergeCell ref="J20:Z20"/>
-    <mergeCell ref="B10:I10"/>
+    <mergeCell ref="J26:Z26"/>
+    <mergeCell ref="B115:Z115"/>
+    <mergeCell ref="B27:Z27"/>
     <mergeCell ref="J11:Z11"/>
     <mergeCell ref="B19:I19"/>
+    <mergeCell ref="J25:Z25"/>
     <mergeCell ref="J16:Z16"/>
     <mergeCell ref="J22:Z22"/>
     <mergeCell ref="T2:V3"/>
@@ -18672,12 +18908,12 @@
     <mergeCell ref="B24:I24"/>
     <mergeCell ref="J12:Z12"/>
     <mergeCell ref="B20:I20"/>
-    <mergeCell ref="B67:Z67"/>
     <mergeCell ref="Y2:Z3"/>
     <mergeCell ref="J21:Z21"/>
     <mergeCell ref="B8:Z8"/>
     <mergeCell ref="R1:S1"/>
     <mergeCell ref="E1:G1"/>
+    <mergeCell ref="B26:I26"/>
   </mergeCells>
   <printOptions gridLines="0"/>
   <pageMargins left="0.35" right="0.35" top="0.45" bottom="0.35" header="0.5" footer="0.5"/>
@@ -18833,7 +19069,7 @@
       <c r="X2" s="15" t="n"/>
       <c r="Y2" s="17" t="inlineStr">
         <is>
-          <t>2026/07/12</t>
+          <t>2026/07/13</t>
         </is>
       </c>
       <c r="Z2" s="18" t="n"/>
@@ -19053,47 +19289,47 @@
     <row r="16" ht="18" customHeight="1">
       <c r="C16" s="24" t="inlineStr">
         <is>
-          <t>① 業務・プロセス管理は、業務上のデバイス利用とデバイスコネクタプロセスのライフサイクルを管理する。</t>
+          <t>① アプリケーション層（業務・プロセス管理）は、業務上のデバイス利用とデバイスコネクタプロセスのライフサイクルを管理する。</t>
         </is>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="C17" s="92" t="inlineStr">
+      <c r="C17" s="95" t="inlineStr">
         <is>
           <t>①-1 画面・業務処理は、必要なデバイス操作を依頼し、同期結果または非同期イベントを業務処理へ反映する。</t>
         </is>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="C18" s="93" t="inlineStr">
+      <c r="C18" s="96" t="inlineStr">
         <is>
           <t>関連シート: 06_運用シナリオ_02、07_機能設計</t>
         </is>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="C19" s="92" t="inlineStr">
+      <c r="C19" s="95" t="inlineStr">
         <is>
           <t>①-2 アプリライフサイクルは、アプリの起動、再開、停止、および破棄をプロセス管理へ通知する。</t>
         </is>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="C20" s="93" t="inlineStr">
+      <c r="C20" s="96" t="inlineStr">
         <is>
           <t>関連シート: 06_運用シナリオ_02</t>
         </is>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="C21" s="92" t="inlineStr">
+      <c r="C21" s="95" t="inlineStr">
         <is>
           <t>①-3 デバイスコネクタプロセス管理は、存在確認、起動、稼働確認、停止要求、および所有プロセスの終了監視を行う。</t>
         </is>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="C22" s="93" t="inlineStr">
+      <c r="C22" s="96" t="inlineStr">
         <is>
           <t>関連シート: 06_運用シナリオ_02、07_機能設計、10_異常・運用設計</t>
         </is>
@@ -19102,47 +19338,47 @@
     <row r="23" ht="18" customHeight="1">
       <c r="C23" s="24" t="inlineStr">
         <is>
-          <t>② デバイスアクセスは、アプリ内の要求をプロセス間通信へ変換し、結果をアプリケーション層へ戻す。</t>
+          <t>② デバイス制御層は、アプリ内の要求をプロセス間通信へ変換し、結果をアプリケーション層へ戻す。</t>
         </is>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
-      <c r="C24" s="92" t="inlineStr">
+      <c r="C24" s="95" t="inlineStr">
         <is>
           <t>②-1 設定・制御方式選択は、読み込み済み設定から有効デバイスとデバイスコネクタ経由の制御方式を選択する。</t>
         </is>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
-      <c r="C25" s="93" t="inlineStr">
+      <c r="C25" s="96" t="inlineStr">
         <is>
           <t>関連シート: 07_機能設計、09_設定・デバイス設計</t>
         </is>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
-      <c r="C26" s="92" t="inlineStr">
+      <c r="C26" s="95" t="inlineStr">
         <is>
           <t>②-2 コマンド通信は、要求を生成し、コマンド通信用パイプで送信して同期応答を受信する。</t>
         </is>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
-      <c r="C27" s="93" t="inlineStr">
+      <c r="C27" s="96" t="inlineStr">
         <is>
           <t>関連シート: 07_機能設計、08_通信・データ設計</t>
         </is>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
-      <c r="C28" s="92" t="inlineStr">
+      <c r="C28" s="95" t="inlineStr">
         <is>
           <t>②-3 結果・イベント連携は、同期応答と非同期イベントをアプリ内の結果形式へ変換して通知する。</t>
         </is>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
-      <c r="C29" s="93" t="inlineStr">
+      <c r="C29" s="96" t="inlineStr">
         <is>
           <t>関連シート: 07_機能設計、08_通信・データ設計、10_異常・運用設計</t>
         </is>
@@ -19163,42 +19399,42 @@
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
-      <c r="C32" s="92" t="inlineStr">
+      <c r="C32" s="95" t="inlineStr">
         <is>
           <t>①-1 起動・停止管理は、通信サービスとデバイス管理を開始・停止し、稼働状態を管理する。</t>
         </is>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
-      <c r="C33" s="93" t="inlineStr">
+      <c r="C33" s="96" t="inlineStr">
         <is>
           <t>関連シート: 06_運用シナリオ_02、07_機能設計、10_異常・運用設計</t>
         </is>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
-      <c r="C34" s="92" t="inlineStr">
+      <c r="C34" s="95" t="inlineStr">
         <is>
           <t>①-2 コマンド受付は、一接続につき一要求を受け付け、同じ接続で同期応答を返す。</t>
         </is>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
-      <c r="C35" s="93" t="inlineStr">
+      <c r="C35" s="96" t="inlineStr">
         <is>
           <t>関連シート: 07_機能設計、08_通信・データ設計</t>
         </is>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
-      <c r="C36" s="92" t="inlineStr">
+      <c r="C36" s="95" t="inlineStr">
         <is>
           <t>①-3 イベント配信は、デバイス処理結果をイベント通知用パイプの接続先へ送信する。</t>
         </is>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
-      <c r="C37" s="93" t="inlineStr">
+      <c r="C37" s="96" t="inlineStr">
         <is>
           <t>関連シート: 07_機能設計、08_通信・データ設計</t>
         </is>
@@ -19212,42 +19448,42 @@
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
-      <c r="C39" s="92" t="inlineStr">
+      <c r="C39" s="95" t="inlineStr">
         <is>
           <t>②-1 デバイスID別順序制御は、同一デバイスIDの要求を投入順に処理する。</t>
         </is>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
-      <c r="C40" s="93" t="inlineStr">
+      <c r="C40" s="96" t="inlineStr">
         <is>
           <t>関連シート: 06_運用シナリオ_02、07_機能設計</t>
         </is>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
-      <c r="C41" s="92" t="inlineStr">
+      <c r="C41" s="95" t="inlineStr">
         <is>
           <t>②-2 要求変換・コマンド制御は、通信形式を内部要求へ変換し、制御要求またはデバイス操作要求として実行する。</t>
         </is>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
-      <c r="C42" s="93" t="inlineStr">
+      <c r="C42" s="96" t="inlineStr">
         <is>
           <t>関連シート: 07_機能設計、08_通信・データ設計、10_異常・運用設計</t>
         </is>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
-      <c r="C43" s="92" t="inlineStr">
+      <c r="C43" s="95" t="inlineStr">
         <is>
           <t>②-3 デバイス管理は、設定に基づくデバイス生成、保持、検索、実行、および停止を管理する。</t>
         </is>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
-      <c r="C44" s="93" t="inlineStr">
+      <c r="C44" s="96" t="inlineStr">
         <is>
           <t>関連シート: 07_機能設計、09_設定・デバイス設計、10_異常・運用設計</t>
         </is>
@@ -19261,14 +19497,14 @@
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
-      <c r="C46" s="92" t="inlineStr">
+      <c r="C46" s="95" t="inlineStr">
         <is>
           <t>③-1 個別デバイス実装は、OPOS、OCX、共有メモリ、要求／応答ファイルなどを利用して実機を制御する。</t>
         </is>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
-      <c r="C47" s="93" t="inlineStr">
+      <c r="C47" s="96" t="inlineStr">
         <is>
           <t>関連シート: 09_設定・デバイス設計、11_実装対応</t>
         </is>
@@ -19282,42 +19518,42 @@
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
-      <c r="C49" s="92" t="inlineStr">
+      <c r="C49" s="95" t="inlineStr">
         <is>
           <t>① 釣銭機（RT-300）は、入金、払出、状態確認、およびエラー確認を行う。</t>
         </is>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
-      <c r="C50" s="93" t="inlineStr">
+      <c r="C50" s="96" t="inlineStr">
         <is>
           <t>関連シート: 03_対象範囲、09_設定・デバイス設計</t>
         </is>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
-      <c r="C51" s="92" t="inlineStr">
+      <c r="C51" s="95" t="inlineStr">
         <is>
           <t>② キャッシュドロア（SHARP）は、ドロア開放を行う。</t>
         </is>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
-      <c r="C52" s="93" t="inlineStr">
+      <c r="C52" s="96" t="inlineStr">
         <is>
           <t>関連シート: 03_対象範囲、09_設定・デバイス設計</t>
         </is>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
-      <c r="C53" s="92" t="inlineStr">
+      <c r="C53" s="95" t="inlineStr">
         <is>
           <t>③ カスタマーディスプレイ（SHARP）は、表示、消去、スクロール、および位置指定表示を行う。</t>
         </is>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
-      <c r="C54" s="93" t="inlineStr">
+      <c r="C54" s="96" t="inlineStr">
         <is>
           <t>関連シート: 03_対象範囲、09_設定・デバイス設計</t>
         </is>
@@ -19548,7 +19784,7 @@
       <c r="X2" s="15" t="n"/>
       <c r="Y2" s="17" t="inlineStr">
         <is>
-          <t>2026/07/12</t>
+          <t>2026/07/13</t>
         </is>
       </c>
       <c r="Z2" s="18" t="n"/>
@@ -19642,10 +19878,10 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="18" customHeight="1">
+    <row r="49" ht="28" customHeight="1">
       <c r="B49" s="55" t="inlineStr">
         <is>
-          <t>- 起動フェーズは、アプリ設定、デバイスコネクタプロセス、デバイスコネクタ内部の順に準備する。運用設定を使用できない場合だけ初期設定へ切り替える。</t>
+          <t>- 起動フェーズは、設定、デバイスコネクタプロセス、通信、およびデバイスを順に準備する。運用設定を使用できない場合だけ初期設定へ切り替え、起動準備が完了しない場合は運用を開始しない。</t>
         </is>
       </c>
     </row>
@@ -19687,7 +19923,7 @@
     <row r="55" ht="18" customHeight="1">
       <c r="B55" s="55" t="inlineStr">
         <is>
-          <t>- 停止要求、終了監視、および強制終了は所有プロセスだけを対象とする。停止要求に失敗しても最大10秒の終了監視を継続する。</t>
+          <t>- 終了フェーズは所有プロセスだけを対象とする。停止要求に失敗しても最大10秒の終了監視を継続し、終了しない場合は所有プロセスツリーを強制終了する。</t>
         </is>
       </c>
     </row>

--- a/artifacts/reports/architecture/ARCH-HOST-01_タブレットPOS_デバイスコネクタ基本設計書/ARCH-HOST-01_タブレットPOS_デバイスコネクタ基本設計書.xlsx
+++ b/artifacts/reports/architecture/ARCH-HOST-01_タブレットPOS_デバイスコネクタ基本設計書/ARCH-HOST-01_タブレットPOS_デバイスコネクタ基本設計書.xlsx
@@ -2026,6 +2026,12 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="43" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="44" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2033,12 +2039,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="45" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2649,7 +2649,7 @@
       <c r="X2" s="15" t="n"/>
       <c r="Y2" s="17" t="inlineStr">
         <is>
-          <t>2026/07/13</t>
+          <t>2026/07/14</t>
         </is>
       </c>
       <c r="Z2" s="18" t="n"/>
@@ -2842,7 +2842,7 @@
       <c r="G10" s="29" t="n"/>
       <c r="H10" s="32" t="inlineStr">
         <is>
-          <t>0.3.2</t>
+          <t>0.3.3</t>
         </is>
       </c>
       <c r="I10" s="28" t="n"/>
@@ -3004,7 +3004,7 @@
       <c r="Y14" s="28" t="n"/>
       <c r="Z14" s="30" t="n"/>
     </row>
-    <row r="15" ht="24" customHeight="1">
+    <row r="15" ht="36" customHeight="1">
       <c r="B15" s="27" t="inlineStr">
         <is>
           <t>目的</t>
@@ -3017,7 +3017,7 @@
       <c r="G15" s="29" t="n"/>
       <c r="H15" s="16" t="inlineStr">
         <is>
-          <t>デバイスコネクタの役割、機能、インターフェース、設定、エラー処理、およびログを基本設計として定義する。</t>
+          <t>タブレットPOS端末アプリから直接利用できない既存のOPOS、OCX、ActiveX、および既存DLLを別プロセスで利用するため、デバイスコネクタの役割、機能、インターフェース、設定、エラー処理、およびログを基本設計として定義する。</t>
         </is>
       </c>
       <c r="I15" s="28" t="n"/>
@@ -3052,7 +3052,7 @@
       <c r="G16" s="29" t="n"/>
       <c r="H16" s="32" t="inlineStr">
         <is>
-          <t>タブレットPOS端末アプリとデバイスコネクタの責務境界、通信契約、および運用時の処理を一貫した設計としてレビューできる状態にする。</t>
+          <t>タブレットPOS端末アプリとデバイスコネクタを分ける理由、両プロセスの責務境界、通信契約、および運用時の処理を一貫した設計としてレビューできる状態にする。</t>
         </is>
       </c>
       <c r="I16" s="28" t="n"/>
@@ -3304,7 +3304,7 @@
       <c r="X2" s="15" t="n"/>
       <c r="Y2" s="17" t="inlineStr">
         <is>
-          <t>2026/07/13</t>
+          <t>2026/07/14</t>
         </is>
       </c>
       <c r="Z2" s="18" t="n"/>
@@ -3345,7 +3345,7 @@
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="B6" s="42" t="inlineStr">
+      <c r="B6" s="44" t="inlineStr">
         <is>
           <t>■6.2 運用シナリオ</t>
         </is>
@@ -3520,7 +3520,7 @@
       <c r="S13" s="29" t="n"/>
       <c r="T13" s="16" t="inlineStr">
         <is>
-          <t>個別デバイス実装、デバイス管理、イベント配信、結果・イベント連携。</t>
+          <t>ホスト内部実装、デバイス管理、イベント配信、結果・イベント連携。</t>
         </is>
       </c>
       <c r="U13" s="28" t="n"/>
@@ -3531,14 +3531,14 @@
       <c r="Z13" s="30" t="n"/>
     </row>
     <row r="14" ht="36" customHeight="1">
-      <c r="B14" s="43" t="inlineStr">
+      <c r="B14" s="38" t="inlineStr">
         <is>
           <t>終了</t>
         </is>
       </c>
       <c r="C14" s="34" t="n"/>
       <c r="D14" s="35" t="n"/>
-      <c r="E14" s="44" t="inlineStr">
+      <c r="E14" s="39" t="inlineStr">
         <is>
           <t>アプリを停止または破棄する。</t>
         </is>
@@ -3548,7 +3548,7 @@
       <c r="H14" s="34" t="n"/>
       <c r="I14" s="34" t="n"/>
       <c r="J14" s="35" t="n"/>
-      <c r="K14" s="44" t="inlineStr">
+      <c r="K14" s="39" t="inlineStr">
         <is>
           <t>所有プロセスの終了確認または強制終了を完了する。</t>
         </is>
@@ -3561,7 +3561,7 @@
       <c r="Q14" s="34" t="n"/>
       <c r="R14" s="34" t="n"/>
       <c r="S14" s="35" t="n"/>
-      <c r="T14" s="44" t="inlineStr">
+      <c r="T14" s="39" t="inlineStr">
         <is>
           <t>デバイスコネクタプロセス管理、デバイスコネクタ起動・停止管理。</t>
         </is>
@@ -3590,7 +3590,7 @@
     <row r="19" ht="28" customHeight="1">
       <c r="C19" s="24" t="inlineStr">
         <is>
-          <t>② デバイスコネクタプロセス管理は同名プロセスの存在を確認する。未起動の場合だけデバイスコネクタ起動プログラムを別プロセスとして起動し、所有プロセスとして保持する。</t>
+          <t>② デバイスコネクタプロセス管理は同名プロセスの存在を確認する。未起動の場合だけデバイスコネクタ起動プログラムをWindows別プロセスとして起動し、所有プロセスとして保持する。通常時は画面を表示せず、バックグラウンドで動作させる。</t>
         </is>
       </c>
     </row>
@@ -3660,14 +3660,14 @@
     <row r="30" ht="28" customHeight="1">
       <c r="C30" s="24" t="inlineStr">
         <is>
-          <t>④ デバイスコネクタは要求を受け付け、同一デバイスIDの要求を投入順に処理する。要求を内部形式へ変換し、対象デバイスを検索して個別デバイス実装へ処理を渡す。</t>
+          <t>④ デバイスコネクタは要求を受け付け、同一デバイスIDの要求を投入順に処理する。要求を内部形式へ変換し、対象デバイスを検索してホスト内部実装へ処理を渡す。</t>
         </is>
       </c>
     </row>
     <row r="31" ht="28" customHeight="1">
       <c r="C31" s="24" t="inlineStr">
         <is>
-          <t>⑤ 個別デバイス実装の結果は、要求と同じコマンド通信用パイプ接続で同期応答として返す。入力不備、未登録デバイス、またはデバイス処理失敗を判定できた場合は失敗応答を返す。</t>
+          <t>⑤ ホスト内部実装の結果は、要求と同じコマンド通信用パイプ接続で同期応答として返す。入力不備、未登録デバイス、またはデバイス処理失敗を判定できた場合は失敗応答を返す。</t>
         </is>
       </c>
     </row>
@@ -3695,7 +3695,7 @@
     <row r="36" ht="18" customHeight="1">
       <c r="C36" s="24" t="inlineStr">
         <is>
-          <t>① 個別デバイス実装でデバイス処理結果通知が発生した場合、デバイス管理は通知データをイベント配信へ渡す。</t>
+          <t>① ホスト内部実装でデバイス処理結果通知が発生した場合、デバイス管理は通知データをイベント配信へ渡す。</t>
         </is>
       </c>
     </row>
@@ -3737,7 +3737,7 @@
     <row r="43" ht="18" customHeight="1">
       <c r="C43" s="24" t="inlineStr">
         <is>
-          <t>② 所有プロセスにはコマンド通信用パイプでHost停止要求を送信する。接続失敗または応答タイムアウトの場合も終了監視を継続する。</t>
+          <t>② 所有プロセスにはコマンド通信用パイプでデバイスコネクタ停止要求を送信する。接続失敗または応答タイムアウトの場合も終了監視を継続する。</t>
         </is>
       </c>
     </row>
@@ -3776,10 +3776,10 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="28" customHeight="1">
+    <row r="50" ht="42" customHeight="1">
       <c r="B50" s="24" t="inlineStr">
         <is>
-          <t>デバッグ引数（DEBUG）付きで起動した場合だけ、デバイスコネクタを直接開始・停止する画面を表示する。保守用停止要求送信ツールはアプリとは独立してHost停止要求を送信し、Host再起動要求は保守操作に限定する。これらの操作は通常の店舗運用シナリオに含めない。</t>
+          <t>通常運用時は画面を表示せず、デバイスコネクタをバックグラウンドで動作させる。デバッグ引数（DEBUG）付きで起動した場合だけ、デバイスコネクタを直接開始・停止する画面を表示する。保守用停止要求送信ツールはアプリとは独立してデバイスコネクタ停止要求を送信し、デバイスコネクタ再起動要求は保守操作に限定する。これらの操作は通常の店舗運用シナリオに含めない。</t>
         </is>
       </c>
     </row>
@@ -4006,7 +4006,7 @@
       <c r="X2" s="15" t="n"/>
       <c r="Y2" s="17" t="inlineStr">
         <is>
-          <t>2026/07/13</t>
+          <t>2026/07/14</t>
         </is>
       </c>
       <c r="Z2" s="18" t="n"/>
@@ -4047,7 +4047,7 @@
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="B6" s="42" t="inlineStr">
+      <c r="B6" s="44" t="inlineStr">
         <is>
           <t>■7.1 機能構成</t>
         </is>
@@ -4220,7 +4220,7 @@
       <c r="L11" s="29" t="n"/>
       <c r="M11" s="16" t="inlineStr">
         <is>
-          <t>（2）② コマンド実行、（2）③ デバイスアダプター</t>
+          <t>（2）② コマンド実行、（2）③ 既存デバイス資源呼出し</t>
         </is>
       </c>
       <c r="N11" s="28" t="n"/>
@@ -4242,12 +4242,12 @@
       <c r="Z11" s="30" t="n"/>
     </row>
     <row r="12" ht="24" customHeight="1">
-      <c r="B12" s="43" t="inlineStr">
+      <c r="B12" s="38" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="C12" s="44" t="inlineStr">
+      <c r="C12" s="39" t="inlineStr">
         <is>
           <t>非同期通知</t>
         </is>
@@ -4256,7 +4256,7 @@
       <c r="E12" s="34" t="n"/>
       <c r="F12" s="34" t="n"/>
       <c r="G12" s="35" t="n"/>
-      <c r="H12" s="44" t="inlineStr">
+      <c r="H12" s="39" t="inlineStr">
         <is>
           <t>非同期イベント</t>
         </is>
@@ -4265,7 +4265,7 @@
       <c r="J12" s="34" t="n"/>
       <c r="K12" s="34" t="n"/>
       <c r="L12" s="35" t="n"/>
-      <c r="M12" s="44" t="inlineStr">
+      <c r="M12" s="39" t="inlineStr">
         <is>
           <t>（2）①-3 イベント配信、（1）②-3 結果・イベント連携</t>
         </is>
@@ -4296,7 +4296,7 @@
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="B15" s="42" t="inlineStr">
+      <c r="B15" s="44" t="inlineStr">
         <is>
           <t>■7.2 プロセスライフサイクル機能</t>
         </is>
@@ -4340,21 +4340,21 @@
         </is>
       </c>
       <c r="R17" s="5" t="n"/>
-      <c r="S17" s="6" t="n"/>
-      <c r="T17" s="26" t="inlineStr">
+      <c r="S17" s="5" t="n"/>
+      <c r="T17" s="6" t="n"/>
+      <c r="U17" s="26" t="inlineStr">
         <is>
           <t>異常時</t>
         </is>
       </c>
-      <c r="U17" s="5" t="n"/>
       <c r="V17" s="5" t="n"/>
-      <c r="W17" s="6" t="n"/>
-      <c r="X17" s="26" t="inlineStr">
+      <c r="W17" s="5" t="n"/>
+      <c r="X17" s="6" t="n"/>
+      <c r="Y17" s="26" t="inlineStr">
         <is>
           <t>主な構成要素</t>
         </is>
       </c>
-      <c r="Y17" s="5" t="n"/>
       <c r="Z17" s="9" t="n"/>
     </row>
     <row r="18" ht="54" customHeight="1">
@@ -4395,21 +4395,21 @@
         </is>
       </c>
       <c r="R18" s="28" t="n"/>
-      <c r="S18" s="29" t="n"/>
-      <c r="T18" s="16" t="inlineStr">
+      <c r="S18" s="28" t="n"/>
+      <c r="T18" s="29" t="n"/>
+      <c r="U18" s="16" t="inlineStr">
         <is>
           <t>10秒以内に確認できない場合は起動失敗とする。</t>
         </is>
       </c>
-      <c r="U18" s="28" t="n"/>
       <c r="V18" s="28" t="n"/>
-      <c r="W18" s="29" t="n"/>
-      <c r="X18" s="16" t="inlineStr">
+      <c r="W18" s="28" t="n"/>
+      <c r="X18" s="29" t="n"/>
+      <c r="Y18" s="16" t="inlineStr">
         <is>
           <t>（1）①-3、（2）①-1、（2）①-2</t>
         </is>
       </c>
-      <c r="Y18" s="28" t="n"/>
       <c r="Z18" s="30" t="n"/>
     </row>
     <row r="19" ht="54" customHeight="1">
@@ -4450,21 +4450,21 @@
         </is>
       </c>
       <c r="R19" s="28" t="n"/>
-      <c r="S19" s="29" t="n"/>
-      <c r="T19" s="32" t="inlineStr">
+      <c r="S19" s="28" t="n"/>
+      <c r="T19" s="29" t="n"/>
+      <c r="U19" s="32" t="inlineStr">
         <is>
           <t>実行ファイル未検出または起動例外時は運用を開始しない。</t>
         </is>
       </c>
-      <c r="U19" s="28" t="n"/>
       <c r="V19" s="28" t="n"/>
-      <c r="W19" s="29" t="n"/>
-      <c r="X19" s="32" t="inlineStr">
+      <c r="W19" s="28" t="n"/>
+      <c r="X19" s="29" t="n"/>
+      <c r="Y19" s="32" t="inlineStr">
         <is>
           <t>（1）①-3</t>
         </is>
       </c>
-      <c r="Y19" s="28" t="n"/>
       <c r="Z19" s="30" t="n"/>
     </row>
     <row r="20" ht="72" customHeight="1">
@@ -4501,29 +4501,29 @@
       <c r="P20" s="35" t="n"/>
       <c r="Q20" s="36" t="inlineStr">
         <is>
-          <t>Host停止要求後、最大10秒で終了を確認する。</t>
+          <t>デバイスコネクタ停止要求後、最大10秒で終了を確認する。</t>
         </is>
       </c>
       <c r="R20" s="34" t="n"/>
-      <c r="S20" s="35" t="n"/>
-      <c r="T20" s="36" t="inlineStr">
+      <c r="S20" s="34" t="n"/>
+      <c r="T20" s="35" t="n"/>
+      <c r="U20" s="36" t="inlineStr">
         <is>
           <t>非所有プロセスは停止しない。10秒以内に終了しない所有プロセスだけを強制終了する。</t>
         </is>
       </c>
-      <c r="U20" s="34" t="n"/>
       <c r="V20" s="34" t="n"/>
-      <c r="W20" s="35" t="n"/>
-      <c r="X20" s="36" t="inlineStr">
+      <c r="W20" s="34" t="n"/>
+      <c r="X20" s="35" t="n"/>
+      <c r="Y20" s="36" t="inlineStr">
         <is>
           <t>（1）①-3、（2）①-1</t>
         </is>
       </c>
-      <c r="Y20" s="34" t="n"/>
       <c r="Z20" s="37" t="n"/>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="B22" s="42" t="inlineStr">
+      <c r="B22" s="44" t="inlineStr">
         <is>
           <t>■7.3 コマンド通信機能</t>
         </is>
@@ -4609,7 +4609,7 @@
       <c r="K25" s="29" t="n"/>
       <c r="L25" s="16" t="inlineStr">
         <is>
-          <t>入力: JSONまたは既存互換形式／出力: 内部要求、JSON応答</t>
+          <t>入力: JSON要求／出力: 内部要求、JSON応答</t>
         </is>
       </c>
       <c r="M25" s="28" t="n"/>
@@ -4626,7 +4626,7 @@
       <c r="T25" s="29" t="n"/>
       <c r="U25" s="16" t="inlineStr">
         <is>
-          <t>空行、形式不正は失敗応答とする。待受失敗時は200ミリ秒後に待受を再開する。</t>
+          <t>空行、JSON形式不正は失敗応答とする。待受失敗時は200ミリ秒後に待受を再開する。</t>
         </is>
       </c>
       <c r="V25" s="28" t="n"/>
@@ -4656,7 +4656,7 @@
       <c r="G26" s="29" t="n"/>
       <c r="H26" s="32" t="inlineStr">
         <is>
-          <t>外部通信形式と内部コマンド形式を相互変換する。</t>
+          <t>JSON通信形式と内部コマンド形式を相互変換する。</t>
         </is>
       </c>
       <c r="I26" s="28" t="n"/>
@@ -4664,7 +4664,7 @@
       <c r="K26" s="29" t="n"/>
       <c r="L26" s="32" t="inlineStr">
         <is>
-          <t>入力: JSON、既存互換形式、処理結果／出力: 内部要求、JSON応答</t>
+          <t>入力: JSON要求、処理結果／出力: 内部要求、JSON応答</t>
         </is>
       </c>
       <c r="M26" s="28" t="n"/>
@@ -4750,7 +4750,7 @@
       <c r="Z27" s="37" t="n"/>
     </row>
     <row r="29" ht="18" customHeight="1">
-      <c r="B29" s="42" t="inlineStr">
+      <c r="B29" s="44" t="inlineStr">
         <is>
           <t>■7.4 コマンド・デバイス実行機能</t>
         </is>
@@ -4866,7 +4866,7 @@
       </c>
       <c r="Z32" s="30" t="n"/>
     </row>
-    <row r="33" ht="54" customHeight="1">
+    <row r="33" ht="72" customHeight="1">
       <c r="B33" s="50" t="inlineStr">
         <is>
           <t>F-HOST-007</t>
@@ -4883,7 +4883,7 @@
       <c r="G33" s="29" t="n"/>
       <c r="H33" s="32" t="inlineStr">
         <is>
-          <t>稼働確認、Host停止要求、保守用Host再起動要求を処理する。</t>
+          <t>稼働確認、デバイスコネクタ停止要求、保守用デバイスコネクタ再起動要求を処理する。</t>
         </is>
       </c>
       <c r="I33" s="28" t="n"/>
@@ -4921,7 +4921,7 @@
       </c>
       <c r="Z33" s="30" t="n"/>
     </row>
-    <row r="34" ht="54" customHeight="1">
+    <row r="34" ht="72" customHeight="1">
       <c r="B34" s="49" t="inlineStr">
         <is>
           <t>F-HOST-008</t>
@@ -4955,7 +4955,7 @@
       <c r="P34" s="29" t="n"/>
       <c r="Q34" s="16" t="inlineStr">
         <is>
-          <t>起動済みデバイスを検索し、個別デバイス実装へ処理を渡す。</t>
+          <t>起動済みデバイスを検索し、既存デバイス資源を呼び出すホスト内部実装へ処理を渡す。</t>
         </is>
       </c>
       <c r="R34" s="28" t="n"/>
@@ -4984,14 +4984,14 @@
       </c>
       <c r="C35" s="34" t="n"/>
       <c r="D35" s="35" t="n"/>
-      <c r="E35" s="44" t="inlineStr">
+      <c r="E35" s="39" t="inlineStr">
         <is>
           <t>デバイス管理</t>
         </is>
       </c>
       <c r="F35" s="34" t="n"/>
       <c r="G35" s="35" t="n"/>
-      <c r="H35" s="44" t="inlineStr">
+      <c r="H35" s="39" t="inlineStr">
         <is>
           <t>設定に基づいて対象デバイスを生成、保持、検索、停止する。</t>
         </is>
@@ -4999,7 +4999,7 @@
       <c r="I35" s="34" t="n"/>
       <c r="J35" s="34" t="n"/>
       <c r="K35" s="35" t="n"/>
-      <c r="L35" s="44" t="inlineStr">
+      <c r="L35" s="39" t="inlineStr">
         <is>
           <t>入力: host_device_config.json／出力: 起動済みデバイス、準備状態</t>
         </is>
@@ -5008,7 +5008,7 @@
       <c r="N35" s="34" t="n"/>
       <c r="O35" s="34" t="n"/>
       <c r="P35" s="35" t="n"/>
-      <c r="Q35" s="44" t="inlineStr">
+      <c r="Q35" s="39" t="inlineStr">
         <is>
           <t>デバイス開始を50ミリ秒間隔で最大3回試行する。</t>
         </is>
@@ -5016,7 +5016,7 @@
       <c r="R35" s="34" t="n"/>
       <c r="S35" s="34" t="n"/>
       <c r="T35" s="35" t="n"/>
-      <c r="U35" s="44" t="inlineStr">
+      <c r="U35" s="39" t="inlineStr">
         <is>
           <t>最終失敗したデバイスは登録しない。必須設定異常時はプロセスを終了する。</t>
         </is>
@@ -5024,7 +5024,7 @@
       <c r="V35" s="34" t="n"/>
       <c r="W35" s="34" t="n"/>
       <c r="X35" s="35" t="n"/>
-      <c r="Y35" s="44" t="inlineStr">
+      <c r="Y35" s="39" t="inlineStr">
         <is>
           <t>（2）②-3、（2）③-1</t>
         </is>
@@ -5032,7 +5032,7 @@
       <c r="Z35" s="37" t="n"/>
     </row>
     <row r="37" ht="18" customHeight="1">
-      <c r="B37" s="42" t="inlineStr">
+      <c r="B37" s="44" t="inlineStr">
         <is>
           <t>■7.5 非同期通知機能</t>
         </is>
@@ -5152,14 +5152,12 @@
   <mergeCells count="145">
     <mergeCell ref="H27:K27"/>
     <mergeCell ref="U39:X39"/>
-    <mergeCell ref="X18:Z18"/>
     <mergeCell ref="E31:G31"/>
     <mergeCell ref="E40:G40"/>
     <mergeCell ref="H24:K24"/>
     <mergeCell ref="Y24:Z24"/>
     <mergeCell ref="H33:K33"/>
     <mergeCell ref="B34:D34"/>
-    <mergeCell ref="T18:W18"/>
     <mergeCell ref="H26:K26"/>
     <mergeCell ref="U31:X31"/>
     <mergeCell ref="L33:P33"/>
@@ -5179,6 +5177,7 @@
     <mergeCell ref="L25:P25"/>
     <mergeCell ref="E18:G18"/>
     <mergeCell ref="X12:Z12"/>
+    <mergeCell ref="Y18:Z18"/>
     <mergeCell ref="U25:X25"/>
     <mergeCell ref="Q26:T26"/>
     <mergeCell ref="E2:G3"/>
@@ -5190,9 +5189,10 @@
     <mergeCell ref="E20:G20"/>
     <mergeCell ref="B29:Z29"/>
     <mergeCell ref="Q27:T27"/>
-    <mergeCell ref="Q19:S19"/>
     <mergeCell ref="B17:D17"/>
+    <mergeCell ref="Q17:T17"/>
     <mergeCell ref="L32:P32"/>
+    <mergeCell ref="U20:X20"/>
     <mergeCell ref="B6:Z6"/>
     <mergeCell ref="B15:Z15"/>
     <mergeCell ref="H18:K18"/>
@@ -5220,25 +5220,26 @@
     <mergeCell ref="H17:K17"/>
     <mergeCell ref="Q31:T31"/>
     <mergeCell ref="Q40:T40"/>
-    <mergeCell ref="Q18:S18"/>
     <mergeCell ref="Y33:Z33"/>
     <mergeCell ref="E17:G17"/>
     <mergeCell ref="B39:D39"/>
     <mergeCell ref="R1:S1"/>
     <mergeCell ref="H19:K19"/>
+    <mergeCell ref="E1:G1"/>
     <mergeCell ref="U24:X24"/>
-    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="U18:X18"/>
     <mergeCell ref="U33:X33"/>
     <mergeCell ref="E19:G19"/>
     <mergeCell ref="B37:Z37"/>
     <mergeCell ref="E34:G34"/>
     <mergeCell ref="M9:W9"/>
     <mergeCell ref="Y39:Z39"/>
+    <mergeCell ref="U19:X19"/>
     <mergeCell ref="T1:V1"/>
     <mergeCell ref="C10:G10"/>
+    <mergeCell ref="Y20:Z20"/>
     <mergeCell ref="M11:W11"/>
     <mergeCell ref="R2:S3"/>
-    <mergeCell ref="Q17:S17"/>
     <mergeCell ref="H1:Q1"/>
     <mergeCell ref="C9:G9"/>
     <mergeCell ref="X10:Z10"/>
@@ -5248,21 +5249,17 @@
     <mergeCell ref="M12:W12"/>
     <mergeCell ref="B35:D35"/>
     <mergeCell ref="C11:G11"/>
+    <mergeCell ref="Q20:T20"/>
     <mergeCell ref="B25:D25"/>
     <mergeCell ref="T2:V3"/>
-    <mergeCell ref="X17:Z17"/>
     <mergeCell ref="L27:P27"/>
     <mergeCell ref="H8:L8"/>
-    <mergeCell ref="X19:Z19"/>
     <mergeCell ref="L17:P17"/>
-    <mergeCell ref="T17:W17"/>
     <mergeCell ref="H10:L10"/>
     <mergeCell ref="W2:X3"/>
     <mergeCell ref="L19:P19"/>
-    <mergeCell ref="T19:W19"/>
     <mergeCell ref="Q32:T32"/>
     <mergeCell ref="H9:L9"/>
-    <mergeCell ref="X20:Z20"/>
     <mergeCell ref="U26:X26"/>
     <mergeCell ref="Y35:Z35"/>
     <mergeCell ref="E27:G27"/>
@@ -5271,21 +5268,25 @@
     <mergeCell ref="Q25:T25"/>
     <mergeCell ref="H20:K20"/>
     <mergeCell ref="B40:D40"/>
+    <mergeCell ref="Y19:Z19"/>
     <mergeCell ref="U34:X34"/>
-    <mergeCell ref="T20:W20"/>
     <mergeCell ref="B24:D24"/>
     <mergeCell ref="Q24:T24"/>
     <mergeCell ref="E25:G25"/>
-    <mergeCell ref="L39:P39"/>
+    <mergeCell ref="Y17:Z17"/>
+    <mergeCell ref="Q18:T18"/>
     <mergeCell ref="B33:D33"/>
     <mergeCell ref="Q33:T33"/>
+    <mergeCell ref="L39:P39"/>
     <mergeCell ref="U27:X27"/>
     <mergeCell ref="H31:K31"/>
     <mergeCell ref="B22:Z22"/>
     <mergeCell ref="B32:D32"/>
     <mergeCell ref="B26:D26"/>
+    <mergeCell ref="U17:X17"/>
     <mergeCell ref="C8:G8"/>
     <mergeCell ref="L31:P31"/>
+    <mergeCell ref="Q19:T19"/>
     <mergeCell ref="L40:P40"/>
     <mergeCell ref="B14:Z14"/>
     <mergeCell ref="E39:G39"/>
@@ -5294,7 +5295,6 @@
     <mergeCell ref="B27:D27"/>
     <mergeCell ref="H32:K32"/>
     <mergeCell ref="Y32:Z32"/>
-    <mergeCell ref="Q20:S20"/>
   </mergeCells>
   <printOptions gridLines="0"/>
   <pageMargins left="0.35" right="0.35" top="0.45" bottom="0.35" header="0.5" footer="0.5"/>
@@ -5316,7 +5316,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Z83"/>
+  <dimension ref="A1:Z72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -5450,7 +5450,7 @@
       <c r="X2" s="15" t="n"/>
       <c r="Y2" s="17" t="inlineStr">
         <is>
-          <t>2026/07/13</t>
+          <t>2026/07/14</t>
         </is>
       </c>
       <c r="Z2" s="18" t="n"/>
@@ -5491,7 +5491,7 @@
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="B6" s="42" t="inlineStr">
+      <c r="B6" s="44" t="inlineStr">
         <is>
           <t>■8.1 通信モデル</t>
         </is>
@@ -5604,7 +5604,7 @@
       <c r="O10" s="29" t="n"/>
       <c r="P10" s="16" t="inlineStr">
         <is>
-          <t>JSONまたは既存互換形式</t>
+          <t>JSON</t>
         </is>
       </c>
       <c r="Q10" s="29" t="n"/>
@@ -5757,7 +5757,7 @@
       <c r="Z12" s="37" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="B14" s="42" t="inlineStr">
+      <c r="B14" s="44" t="inlineStr">
         <is>
           <t>■8.2 コマンド要求</t>
         </is>
@@ -6011,7 +6011,7 @@
       <c r="S25" s="29" t="n"/>
       <c r="T25" s="16" t="inlineStr">
         <is>
-          <t>Host停止要求とHost再起動要求では未指定可。</t>
+          <t>デバイスコネクタ停止要求とデバイスコネクタ再起動要求では未指定可。</t>
         </is>
       </c>
       <c r="U25" s="28" t="n"/>
@@ -6103,7 +6103,7 @@
       <c r="I27" s="29" t="n"/>
       <c r="J27" s="16" t="inlineStr">
         <is>
-          <t>呼出元を識別する既存互換用ハンドル。</t>
+          <t>呼出元を識別するハンドル。</t>
         </is>
       </c>
       <c r="K27" s="28" t="n"/>
@@ -6132,31 +6132,31 @@
       <c r="Z27" s="30" t="n"/>
     </row>
     <row r="28" ht="36" customHeight="1">
-      <c r="B28" s="43" t="inlineStr">
+      <c r="B28" s="38" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="C28" s="44" t="inlineStr">
+      <c r="C28" s="39" t="inlineStr">
         <is>
           <t>付加データ（Payload）</t>
         </is>
       </c>
       <c r="D28" s="34" t="n"/>
       <c r="E28" s="35" t="n"/>
-      <c r="F28" s="44" t="inlineStr">
+      <c r="F28" s="39" t="inlineStr">
         <is>
           <t>object</t>
         </is>
       </c>
       <c r="G28" s="35" t="n"/>
-      <c r="H28" s="44" t="inlineStr">
+      <c r="H28" s="39" t="inlineStr">
         <is>
           <t>任意</t>
         </is>
       </c>
       <c r="I28" s="35" t="n"/>
-      <c r="J28" s="44" t="inlineStr">
+      <c r="J28" s="39" t="inlineStr">
         <is>
           <t>文字列キーと文字列値で構成するデバイス操作引数。</t>
         </is>
@@ -6166,7 +6166,7 @@
       <c r="M28" s="34" t="n"/>
       <c r="N28" s="34" t="n"/>
       <c r="O28" s="35" t="n"/>
-      <c r="P28" s="44" t="inlineStr">
+      <c r="P28" s="39" t="inlineStr">
         <is>
           <t>{ "Data": "TOTAL 1,000", "Attribute": "0" }</t>
         </is>
@@ -6174,7 +6174,7 @@
       <c r="Q28" s="34" t="n"/>
       <c r="R28" s="34" t="n"/>
       <c r="S28" s="35" t="n"/>
-      <c r="T28" s="44" t="inlineStr">
+      <c r="T28" s="39" t="inlineStr">
         <is>
           <t>内容はデバイスIDとメソッドIDにより変わる。</t>
         </is>
@@ -6187,276 +6187,21 @@
       <c r="Z28" s="37" t="n"/>
     </row>
     <row r="30" ht="18" customHeight="1">
-      <c r="B30" s="45" t="inlineStr">
-        <is>
-          <t>■8.2.3 既存互換形式</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="42" customHeight="1">
-      <c r="B32" s="24" t="inlineStr">
-        <is>
-          <t>既存互換形式は、キーと値をタブ文字で交互に並べた一行データとする。コマンド受付は、順序制御へ投入する前にメッセージ（Message）とデバイスID（TabletDeviceId）を解析する。デバイス操作要求ではデバイスIDを順序制御キーに使用し、デバイスコネクタ制御要求では共通キーを使用する。既存互換形式には要求IDがないため、コマンド受付が要求単位の追跡IDを採番し、応答へ設定する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="20" customHeight="1">
-      <c r="B33" s="25" t="inlineStr">
-        <is>
-          <t>キー</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="n"/>
-      <c r="D33" s="5" t="n"/>
-      <c r="E33" s="5" t="n"/>
-      <c r="F33" s="5" t="n"/>
-      <c r="G33" s="5" t="n"/>
-      <c r="H33" s="5" t="n"/>
-      <c r="I33" s="6" t="n"/>
-      <c r="J33" s="26" t="inlineStr">
-        <is>
-          <t>必須</t>
-        </is>
-      </c>
-      <c r="K33" s="6" t="n"/>
-      <c r="L33" s="26" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="M33" s="5" t="n"/>
-      <c r="N33" s="5" t="n"/>
-      <c r="O33" s="5" t="n"/>
-      <c r="P33" s="5" t="n"/>
-      <c r="Q33" s="5" t="n"/>
-      <c r="R33" s="5" t="n"/>
-      <c r="S33" s="5" t="n"/>
-      <c r="T33" s="5" t="n"/>
-      <c r="U33" s="5" t="n"/>
-      <c r="V33" s="5" t="n"/>
-      <c r="W33" s="5" t="n"/>
-      <c r="X33" s="5" t="n"/>
-      <c r="Y33" s="5" t="n"/>
-      <c r="Z33" s="9" t="n"/>
-    </row>
-    <row r="34" ht="24" customHeight="1">
-      <c r="B34" s="27" t="inlineStr">
-        <is>
-          <t>メッセージ（Message）</t>
-        </is>
-      </c>
-      <c r="C34" s="28" t="n"/>
-      <c r="D34" s="28" t="n"/>
-      <c r="E34" s="28" t="n"/>
-      <c r="F34" s="28" t="n"/>
-      <c r="G34" s="28" t="n"/>
-      <c r="H34" s="28" t="n"/>
-      <c r="I34" s="29" t="n"/>
-      <c r="J34" s="16" t="inlineStr">
-        <is>
-          <t>必須</t>
-        </is>
-      </c>
-      <c r="K34" s="29" t="n"/>
-      <c r="L34" s="16" t="inlineStr">
-        <is>
-          <t>メッセージ種別。</t>
-        </is>
-      </c>
-      <c r="M34" s="28" t="n"/>
-      <c r="N34" s="28" t="n"/>
-      <c r="O34" s="28" t="n"/>
-      <c r="P34" s="28" t="n"/>
-      <c r="Q34" s="28" t="n"/>
-      <c r="R34" s="28" t="n"/>
-      <c r="S34" s="28" t="n"/>
-      <c r="T34" s="28" t="n"/>
-      <c r="U34" s="28" t="n"/>
-      <c r="V34" s="28" t="n"/>
-      <c r="W34" s="28" t="n"/>
-      <c r="X34" s="28" t="n"/>
-      <c r="Y34" s="28" t="n"/>
-      <c r="Z34" s="30" t="n"/>
-    </row>
-    <row r="35" ht="36" customHeight="1">
-      <c r="B35" s="31" t="inlineStr">
-        <is>
-          <t>TabletDeviceId</t>
-        </is>
-      </c>
-      <c r="C35" s="28" t="n"/>
-      <c r="D35" s="28" t="n"/>
-      <c r="E35" s="28" t="n"/>
-      <c r="F35" s="28" t="n"/>
-      <c r="G35" s="28" t="n"/>
-      <c r="H35" s="28" t="n"/>
-      <c r="I35" s="29" t="n"/>
-      <c r="J35" s="32" t="inlineStr">
-        <is>
-          <t>条件付き必須</t>
-        </is>
-      </c>
-      <c r="K35" s="29" t="n"/>
-      <c r="L35" s="32" t="inlineStr">
-        <is>
-          <t>デバイス操作要求の対象デバイスID。</t>
-        </is>
-      </c>
-      <c r="M35" s="28" t="n"/>
-      <c r="N35" s="28" t="n"/>
-      <c r="O35" s="28" t="n"/>
-      <c r="P35" s="28" t="n"/>
-      <c r="Q35" s="28" t="n"/>
-      <c r="R35" s="28" t="n"/>
-      <c r="S35" s="28" t="n"/>
-      <c r="T35" s="28" t="n"/>
-      <c r="U35" s="28" t="n"/>
-      <c r="V35" s="28" t="n"/>
-      <c r="W35" s="28" t="n"/>
-      <c r="X35" s="28" t="n"/>
-      <c r="Y35" s="28" t="n"/>
-      <c r="Z35" s="30" t="n"/>
-    </row>
-    <row r="36" ht="36" customHeight="1">
-      <c r="B36" s="27" t="inlineStr">
-        <is>
-          <t>メソッドID（MethodId）</t>
-        </is>
-      </c>
-      <c r="C36" s="28" t="n"/>
-      <c r="D36" s="28" t="n"/>
-      <c r="E36" s="28" t="n"/>
-      <c r="F36" s="28" t="n"/>
-      <c r="G36" s="28" t="n"/>
-      <c r="H36" s="28" t="n"/>
-      <c r="I36" s="29" t="n"/>
-      <c r="J36" s="16" t="inlineStr">
-        <is>
-          <t>条件付き必須</t>
-        </is>
-      </c>
-      <c r="K36" s="29" t="n"/>
-      <c r="L36" s="16" t="inlineStr">
-        <is>
-          <t>デバイスメソッド実行の対象メソッドID。</t>
-        </is>
-      </c>
-      <c r="M36" s="28" t="n"/>
-      <c r="N36" s="28" t="n"/>
-      <c r="O36" s="28" t="n"/>
-      <c r="P36" s="28" t="n"/>
-      <c r="Q36" s="28" t="n"/>
-      <c r="R36" s="28" t="n"/>
-      <c r="S36" s="28" t="n"/>
-      <c r="T36" s="28" t="n"/>
-      <c r="U36" s="28" t="n"/>
-      <c r="V36" s="28" t="n"/>
-      <c r="W36" s="28" t="n"/>
-      <c r="X36" s="28" t="n"/>
-      <c r="Y36" s="28" t="n"/>
-      <c r="Z36" s="30" t="n"/>
-    </row>
-    <row r="37" ht="24" customHeight="1">
-      <c r="B37" s="31" t="inlineStr">
-        <is>
-          <t>ハンドル（Handle）</t>
-        </is>
-      </c>
-      <c r="C37" s="28" t="n"/>
-      <c r="D37" s="28" t="n"/>
-      <c r="E37" s="28" t="n"/>
-      <c r="F37" s="28" t="n"/>
-      <c r="G37" s="28" t="n"/>
-      <c r="H37" s="28" t="n"/>
-      <c r="I37" s="29" t="n"/>
-      <c r="J37" s="32" t="inlineStr">
-        <is>
-          <t>任意</t>
-        </is>
-      </c>
-      <c r="K37" s="29" t="n"/>
-      <c r="L37" s="32" t="inlineStr">
-        <is>
-          <t>呼出元ハンドル。未指定時は0として扱う。</t>
-        </is>
-      </c>
-      <c r="M37" s="28" t="n"/>
-      <c r="N37" s="28" t="n"/>
-      <c r="O37" s="28" t="n"/>
-      <c r="P37" s="28" t="n"/>
-      <c r="Q37" s="28" t="n"/>
-      <c r="R37" s="28" t="n"/>
-      <c r="S37" s="28" t="n"/>
-      <c r="T37" s="28" t="n"/>
-      <c r="U37" s="28" t="n"/>
-      <c r="V37" s="28" t="n"/>
-      <c r="W37" s="28" t="n"/>
-      <c r="X37" s="28" t="n"/>
-      <c r="Y37" s="28" t="n"/>
-      <c r="Z37" s="30" t="n"/>
-    </row>
-    <row r="38" ht="24" customHeight="1">
-      <c r="B38" s="33" t="inlineStr">
-        <is>
-          <t>上記以外</t>
-        </is>
-      </c>
-      <c r="C38" s="34" t="n"/>
-      <c r="D38" s="34" t="n"/>
-      <c r="E38" s="34" t="n"/>
-      <c r="F38" s="34" t="n"/>
-      <c r="G38" s="34" t="n"/>
-      <c r="H38" s="34" t="n"/>
-      <c r="I38" s="35" t="n"/>
-      <c r="J38" s="36" t="inlineStr">
-        <is>
-          <t>任意</t>
-        </is>
-      </c>
-      <c r="K38" s="35" t="n"/>
-      <c r="L38" s="36" t="inlineStr">
-        <is>
-          <t>個別デバイス操作の付加データ。</t>
-        </is>
-      </c>
-      <c r="M38" s="34" t="n"/>
-      <c r="N38" s="34" t="n"/>
-      <c r="O38" s="34" t="n"/>
-      <c r="P38" s="34" t="n"/>
-      <c r="Q38" s="34" t="n"/>
-      <c r="R38" s="34" t="n"/>
-      <c r="S38" s="34" t="n"/>
-      <c r="T38" s="34" t="n"/>
-      <c r="U38" s="34" t="n"/>
-      <c r="V38" s="34" t="n"/>
-      <c r="W38" s="34" t="n"/>
-      <c r="X38" s="34" t="n"/>
-      <c r="Y38" s="34" t="n"/>
-      <c r="Z38" s="37" t="n"/>
-    </row>
-    <row r="40" ht="24" customHeight="1">
-      <c r="B40" s="99" t="inlineStr">
-        <is>
-          <t>Message\tDeviceMethod\tTabletDeviceId\tCustomerDisplay\tMethodId\tDisplayText\tHandle\t12345\tData\tTOTAL 1,000</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="18" customHeight="1">
-      <c r="B41" s="42" t="inlineStr">
+      <c r="B30" s="44" t="inlineStr">
         <is>
           <t>■8.3 コマンド応答</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="18" customHeight="1">
-      <c r="B43" s="45" t="inlineStr">
+    <row r="32" ht="18" customHeight="1">
+      <c r="B32" s="45" t="inlineStr">
         <is>
           <t>■8.3.1 コマンド応答JSON例</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="150" customHeight="1">
-      <c r="B45" s="99" t="inlineStr">
+    <row r="34" ht="150" customHeight="1">
+      <c r="B34" s="99" t="inlineStr">
         <is>
           <t>{
   "RequestId": "00000001",
@@ -6471,366 +6216,366 @@
         </is>
       </c>
     </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="B35" s="45" t="inlineStr">
+        <is>
+          <t>■8.3.2 コマンド応答項目</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="B37" s="25" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="C37" s="26" t="inlineStr">
+        <is>
+          <t>項目名</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="n"/>
+      <c r="E37" s="6" t="n"/>
+      <c r="F37" s="26" t="inlineStr">
+        <is>
+          <t>型</t>
+        </is>
+      </c>
+      <c r="G37" s="6" t="n"/>
+      <c r="H37" s="26" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="I37" s="6" t="n"/>
+      <c r="J37" s="26" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="n"/>
+      <c r="L37" s="5" t="n"/>
+      <c r="M37" s="5" t="n"/>
+      <c r="N37" s="6" t="n"/>
+      <c r="O37" s="26" t="inlineStr">
+        <is>
+          <t>正常時</t>
+        </is>
+      </c>
+      <c r="P37" s="5" t="n"/>
+      <c r="Q37" s="5" t="n"/>
+      <c r="R37" s="5" t="n"/>
+      <c r="S37" s="5" t="n"/>
+      <c r="T37" s="6" t="n"/>
+      <c r="U37" s="26" t="inlineStr">
+        <is>
+          <t>異常時</t>
+        </is>
+      </c>
+      <c r="V37" s="5" t="n"/>
+      <c r="W37" s="5" t="n"/>
+      <c r="X37" s="5" t="n"/>
+      <c r="Y37" s="5" t="n"/>
+      <c r="Z37" s="9" t="n"/>
+    </row>
+    <row r="38" ht="36" customHeight="1">
+      <c r="B38" s="27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C38" s="16" t="inlineStr">
+        <is>
+          <t>要求ID（RequestId）</t>
+        </is>
+      </c>
+      <c r="D38" s="28" t="n"/>
+      <c r="E38" s="29" t="n"/>
+      <c r="F38" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="G38" s="29" t="n"/>
+      <c r="H38" s="16" t="inlineStr">
+        <is>
+          <t>任意</t>
+        </is>
+      </c>
+      <c r="I38" s="29" t="n"/>
+      <c r="J38" s="16" t="inlineStr">
+        <is>
+          <t>要求ID。</t>
+        </is>
+      </c>
+      <c r="K38" s="28" t="n"/>
+      <c r="L38" s="28" t="n"/>
+      <c r="M38" s="28" t="n"/>
+      <c r="N38" s="29" t="n"/>
+      <c r="O38" s="16" t="inlineStr">
+        <is>
+          <t>要求から引き継ぐ。</t>
+        </is>
+      </c>
+      <c r="P38" s="28" t="n"/>
+      <c r="Q38" s="28" t="n"/>
+      <c r="R38" s="28" t="n"/>
+      <c r="S38" s="28" t="n"/>
+      <c r="T38" s="29" t="n"/>
+      <c r="U38" s="16" t="inlineStr">
+        <is>
+          <t>要求を解析できた場合に引き継ぐ。</t>
+        </is>
+      </c>
+      <c r="V38" s="28" t="n"/>
+      <c r="W38" s="28" t="n"/>
+      <c r="X38" s="28" t="n"/>
+      <c r="Y38" s="28" t="n"/>
+      <c r="Z38" s="30" t="n"/>
+    </row>
+    <row r="39" ht="36" customHeight="1">
+      <c r="B39" s="31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C39" s="32" t="inlineStr">
+        <is>
+          <t>成功フラグ（Success）</t>
+        </is>
+      </c>
+      <c r="D39" s="28" t="n"/>
+      <c r="E39" s="29" t="n"/>
+      <c r="F39" s="32" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="G39" s="29" t="n"/>
+      <c r="H39" s="32" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="I39" s="29" t="n"/>
+      <c r="J39" s="32" t="inlineStr">
+        <is>
+          <t>処理成否。</t>
+        </is>
+      </c>
+      <c r="K39" s="28" t="n"/>
+      <c r="L39" s="28" t="n"/>
+      <c r="M39" s="28" t="n"/>
+      <c r="N39" s="29" t="n"/>
+      <c r="O39" s="32" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="P39" s="28" t="n"/>
+      <c r="Q39" s="28" t="n"/>
+      <c r="R39" s="28" t="n"/>
+      <c r="S39" s="28" t="n"/>
+      <c r="T39" s="29" t="n"/>
+      <c r="U39" s="32" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="V39" s="28" t="n"/>
+      <c r="W39" s="28" t="n"/>
+      <c r="X39" s="28" t="n"/>
+      <c r="Y39" s="28" t="n"/>
+      <c r="Z39" s="30" t="n"/>
+    </row>
+    <row r="40" ht="36" customHeight="1">
+      <c r="B40" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C40" s="16" t="inlineStr">
+        <is>
+          <t>結果コード（ResultCode）</t>
+        </is>
+      </c>
+      <c r="D40" s="28" t="n"/>
+      <c r="E40" s="29" t="n"/>
+      <c r="F40" s="16" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="G40" s="29" t="n"/>
+      <c r="H40" s="16" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="I40" s="29" t="n"/>
+      <c r="J40" s="16" t="inlineStr">
+        <is>
+          <t>結果コード。</t>
+        </is>
+      </c>
+      <c r="K40" s="28" t="n"/>
+      <c r="L40" s="28" t="n"/>
+      <c r="M40" s="28" t="n"/>
+      <c r="N40" s="29" t="n"/>
+      <c r="O40" s="16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P40" s="28" t="n"/>
+      <c r="Q40" s="28" t="n"/>
+      <c r="R40" s="28" t="n"/>
+      <c r="S40" s="28" t="n"/>
+      <c r="T40" s="29" t="n"/>
+      <c r="U40" s="16" t="inlineStr">
+        <is>
+          <t>-1またはデバイス結果コード。</t>
+        </is>
+      </c>
+      <c r="V40" s="28" t="n"/>
+      <c r="W40" s="28" t="n"/>
+      <c r="X40" s="28" t="n"/>
+      <c r="Y40" s="28" t="n"/>
+      <c r="Z40" s="30" t="n"/>
+    </row>
+    <row r="41" ht="36" customHeight="1">
+      <c r="B41" s="31" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C41" s="32" t="inlineStr">
+        <is>
+          <t>メッセージ（Message）</t>
+        </is>
+      </c>
+      <c r="D41" s="28" t="n"/>
+      <c r="E41" s="29" t="n"/>
+      <c r="F41" s="32" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="G41" s="29" t="n"/>
+      <c r="H41" s="32" t="inlineStr">
+        <is>
+          <t>任意</t>
+        </is>
+      </c>
+      <c r="I41" s="29" t="n"/>
+      <c r="J41" s="32" t="inlineStr">
+        <is>
+          <t>処理結果または異常内容。</t>
+        </is>
+      </c>
+      <c r="K41" s="28" t="n"/>
+      <c r="L41" s="28" t="n"/>
+      <c r="M41" s="28" t="n"/>
+      <c r="N41" s="29" t="n"/>
+      <c r="O41" s="32" t="inlineStr">
+        <is>
+          <t>空文字または受付結果。</t>
+        </is>
+      </c>
+      <c r="P41" s="28" t="n"/>
+      <c r="Q41" s="28" t="n"/>
+      <c r="R41" s="28" t="n"/>
+      <c r="S41" s="28" t="n"/>
+      <c r="T41" s="29" t="n"/>
+      <c r="U41" s="32" t="inlineStr">
+        <is>
+          <t>例外内容または入力不備の内容。</t>
+        </is>
+      </c>
+      <c r="V41" s="28" t="n"/>
+      <c r="W41" s="28" t="n"/>
+      <c r="X41" s="28" t="n"/>
+      <c r="Y41" s="28" t="n"/>
+      <c r="Z41" s="30" t="n"/>
+    </row>
+    <row r="42" ht="90" customHeight="1">
+      <c r="B42" s="33" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C42" s="36" t="inlineStr">
+        <is>
+          <t>付加データ（Payload）</t>
+        </is>
+      </c>
+      <c r="D42" s="34" t="n"/>
+      <c r="E42" s="35" t="n"/>
+      <c r="F42" s="36" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="G42" s="35" t="n"/>
+      <c r="H42" s="36" t="inlineStr">
+        <is>
+          <t>任意</t>
+        </is>
+      </c>
+      <c r="I42" s="35" t="n"/>
+      <c r="J42" s="36" t="inlineStr">
+        <is>
+          <t>文字列キーと文字列値で構成する追加結果。</t>
+        </is>
+      </c>
+      <c r="K42" s="34" t="n"/>
+      <c r="L42" s="34" t="n"/>
+      <c r="M42" s="34" t="n"/>
+      <c r="N42" s="35" t="n"/>
+      <c r="O42" s="36" t="inlineStr">
+        <is>
+          <t>デバイス操作では結果コード（ResultCode）、戻り値（ReturnValue）を含める。</t>
+        </is>
+      </c>
+      <c r="P42" s="34" t="n"/>
+      <c r="Q42" s="34" t="n"/>
+      <c r="R42" s="34" t="n"/>
+      <c r="S42" s="34" t="n"/>
+      <c r="T42" s="35" t="n"/>
+      <c r="U42" s="36" t="inlineStr">
+        <is>
+          <t>入力検証エラーでは結果コード（ResultCode）、戻り値（ReturnValue）を含める。解析前エラーやデバイスコネクタ制御では空またはnullの場合がある。</t>
+        </is>
+      </c>
+      <c r="V42" s="34" t="n"/>
+      <c r="W42" s="34" t="n"/>
+      <c r="X42" s="34" t="n"/>
+      <c r="Y42" s="34" t="n"/>
+      <c r="Z42" s="37" t="n"/>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="B44" s="44" t="inlineStr">
+        <is>
+          <t>■8.4 イベント通知</t>
+        </is>
+      </c>
+    </row>
     <row r="46" ht="18" customHeight="1">
       <c r="B46" s="45" t="inlineStr">
         <is>
-          <t>■8.3.2 コマンド応答項目</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="20" customHeight="1">
-      <c r="B48" s="25" t="inlineStr">
-        <is>
-          <t>No.</t>
-        </is>
-      </c>
-      <c r="C48" s="26" t="inlineStr">
-        <is>
-          <t>項目名</t>
-        </is>
-      </c>
-      <c r="D48" s="5" t="n"/>
-      <c r="E48" s="6" t="n"/>
-      <c r="F48" s="26" t="inlineStr">
-        <is>
-          <t>型</t>
-        </is>
-      </c>
-      <c r="G48" s="6" t="n"/>
-      <c r="H48" s="26" t="inlineStr">
-        <is>
-          <t>必須</t>
-        </is>
-      </c>
-      <c r="I48" s="6" t="n"/>
-      <c r="J48" s="26" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="K48" s="5" t="n"/>
-      <c r="L48" s="5" t="n"/>
-      <c r="M48" s="5" t="n"/>
-      <c r="N48" s="6" t="n"/>
-      <c r="O48" s="26" t="inlineStr">
-        <is>
-          <t>正常時</t>
-        </is>
-      </c>
-      <c r="P48" s="5" t="n"/>
-      <c r="Q48" s="5" t="n"/>
-      <c r="R48" s="5" t="n"/>
-      <c r="S48" s="5" t="n"/>
-      <c r="T48" s="6" t="n"/>
-      <c r="U48" s="26" t="inlineStr">
-        <is>
-          <t>異常時</t>
-        </is>
-      </c>
-      <c r="V48" s="5" t="n"/>
-      <c r="W48" s="5" t="n"/>
-      <c r="X48" s="5" t="n"/>
-      <c r="Y48" s="5" t="n"/>
-      <c r="Z48" s="9" t="n"/>
-    </row>
-    <row r="49" ht="36" customHeight="1">
-      <c r="B49" s="27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C49" s="16" t="inlineStr">
-        <is>
-          <t>要求ID（RequestId）</t>
-        </is>
-      </c>
-      <c r="D49" s="28" t="n"/>
-      <c r="E49" s="29" t="n"/>
-      <c r="F49" s="16" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="G49" s="29" t="n"/>
-      <c r="H49" s="16" t="inlineStr">
-        <is>
-          <t>任意</t>
-        </is>
-      </c>
-      <c r="I49" s="29" t="n"/>
-      <c r="J49" s="16" t="inlineStr">
-        <is>
-          <t>要求ID。</t>
-        </is>
-      </c>
-      <c r="K49" s="28" t="n"/>
-      <c r="L49" s="28" t="n"/>
-      <c r="M49" s="28" t="n"/>
-      <c r="N49" s="29" t="n"/>
-      <c r="O49" s="16" t="inlineStr">
-        <is>
-          <t>要求から引き継ぐ。</t>
-        </is>
-      </c>
-      <c r="P49" s="28" t="n"/>
-      <c r="Q49" s="28" t="n"/>
-      <c r="R49" s="28" t="n"/>
-      <c r="S49" s="28" t="n"/>
-      <c r="T49" s="29" t="n"/>
-      <c r="U49" s="16" t="inlineStr">
-        <is>
-          <t>要求を解析できた場合に引き継ぐ。</t>
-        </is>
-      </c>
-      <c r="V49" s="28" t="n"/>
-      <c r="W49" s="28" t="n"/>
-      <c r="X49" s="28" t="n"/>
-      <c r="Y49" s="28" t="n"/>
-      <c r="Z49" s="30" t="n"/>
-    </row>
-    <row r="50" ht="36" customHeight="1">
-      <c r="B50" s="31" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C50" s="32" t="inlineStr">
-        <is>
-          <t>成功フラグ（Success）</t>
-        </is>
-      </c>
-      <c r="D50" s="28" t="n"/>
-      <c r="E50" s="29" t="n"/>
-      <c r="F50" s="32" t="inlineStr">
-        <is>
-          <t>boolean</t>
-        </is>
-      </c>
-      <c r="G50" s="29" t="n"/>
-      <c r="H50" s="32" t="inlineStr">
-        <is>
-          <t>必須</t>
-        </is>
-      </c>
-      <c r="I50" s="29" t="n"/>
-      <c r="J50" s="32" t="inlineStr">
-        <is>
-          <t>処理成否。</t>
-        </is>
-      </c>
-      <c r="K50" s="28" t="n"/>
-      <c r="L50" s="28" t="n"/>
-      <c r="M50" s="28" t="n"/>
-      <c r="N50" s="29" t="n"/>
-      <c r="O50" s="32" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="P50" s="28" t="n"/>
-      <c r="Q50" s="28" t="n"/>
-      <c r="R50" s="28" t="n"/>
-      <c r="S50" s="28" t="n"/>
-      <c r="T50" s="29" t="n"/>
-      <c r="U50" s="32" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="V50" s="28" t="n"/>
-      <c r="W50" s="28" t="n"/>
-      <c r="X50" s="28" t="n"/>
-      <c r="Y50" s="28" t="n"/>
-      <c r="Z50" s="30" t="n"/>
-    </row>
-    <row r="51" ht="36" customHeight="1">
-      <c r="B51" s="27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C51" s="16" t="inlineStr">
-        <is>
-          <t>結果コード（ResultCode）</t>
-        </is>
-      </c>
-      <c r="D51" s="28" t="n"/>
-      <c r="E51" s="29" t="n"/>
-      <c r="F51" s="16" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="G51" s="29" t="n"/>
-      <c r="H51" s="16" t="inlineStr">
-        <is>
-          <t>必須</t>
-        </is>
-      </c>
-      <c r="I51" s="29" t="n"/>
-      <c r="J51" s="16" t="inlineStr">
-        <is>
-          <t>結果コード。</t>
-        </is>
-      </c>
-      <c r="K51" s="28" t="n"/>
-      <c r="L51" s="28" t="n"/>
-      <c r="M51" s="28" t="n"/>
-      <c r="N51" s="29" t="n"/>
-      <c r="O51" s="16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P51" s="28" t="n"/>
-      <c r="Q51" s="28" t="n"/>
-      <c r="R51" s="28" t="n"/>
-      <c r="S51" s="28" t="n"/>
-      <c r="T51" s="29" t="n"/>
-      <c r="U51" s="16" t="inlineStr">
-        <is>
-          <t>-1またはデバイス結果コード。</t>
-        </is>
-      </c>
-      <c r="V51" s="28" t="n"/>
-      <c r="W51" s="28" t="n"/>
-      <c r="X51" s="28" t="n"/>
-      <c r="Y51" s="28" t="n"/>
-      <c r="Z51" s="30" t="n"/>
-    </row>
-    <row r="52" ht="36" customHeight="1">
-      <c r="B52" s="31" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C52" s="32" t="inlineStr">
-        <is>
-          <t>メッセージ（Message）</t>
-        </is>
-      </c>
-      <c r="D52" s="28" t="n"/>
-      <c r="E52" s="29" t="n"/>
-      <c r="F52" s="32" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="G52" s="29" t="n"/>
-      <c r="H52" s="32" t="inlineStr">
-        <is>
-          <t>任意</t>
-        </is>
-      </c>
-      <c r="I52" s="29" t="n"/>
-      <c r="J52" s="32" t="inlineStr">
-        <is>
-          <t>処理結果または異常内容。</t>
-        </is>
-      </c>
-      <c r="K52" s="28" t="n"/>
-      <c r="L52" s="28" t="n"/>
-      <c r="M52" s="28" t="n"/>
-      <c r="N52" s="29" t="n"/>
-      <c r="O52" s="32" t="inlineStr">
-        <is>
-          <t>空文字または受付結果。</t>
-        </is>
-      </c>
-      <c r="P52" s="28" t="n"/>
-      <c r="Q52" s="28" t="n"/>
-      <c r="R52" s="28" t="n"/>
-      <c r="S52" s="28" t="n"/>
-      <c r="T52" s="29" t="n"/>
-      <c r="U52" s="32" t="inlineStr">
-        <is>
-          <t>例外内容または入力不備の内容。</t>
-        </is>
-      </c>
-      <c r="V52" s="28" t="n"/>
-      <c r="W52" s="28" t="n"/>
-      <c r="X52" s="28" t="n"/>
-      <c r="Y52" s="28" t="n"/>
-      <c r="Z52" s="30" t="n"/>
-    </row>
-    <row r="53" ht="90" customHeight="1">
-      <c r="B53" s="33" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C53" s="36" t="inlineStr">
-        <is>
-          <t>付加データ（Payload）</t>
-        </is>
-      </c>
-      <c r="D53" s="34" t="n"/>
-      <c r="E53" s="35" t="n"/>
-      <c r="F53" s="36" t="inlineStr">
-        <is>
-          <t>object</t>
-        </is>
-      </c>
-      <c r="G53" s="35" t="n"/>
-      <c r="H53" s="36" t="inlineStr">
-        <is>
-          <t>任意</t>
-        </is>
-      </c>
-      <c r="I53" s="35" t="n"/>
-      <c r="J53" s="36" t="inlineStr">
-        <is>
-          <t>文字列キーと文字列値で構成する追加結果。</t>
-        </is>
-      </c>
-      <c r="K53" s="34" t="n"/>
-      <c r="L53" s="34" t="n"/>
-      <c r="M53" s="34" t="n"/>
-      <c r="N53" s="35" t="n"/>
-      <c r="O53" s="36" t="inlineStr">
-        <is>
-          <t>デバイス操作では結果コード（ResultCode）、戻り値（ReturnValue）を含める。</t>
-        </is>
-      </c>
-      <c r="P53" s="34" t="n"/>
-      <c r="Q53" s="34" t="n"/>
-      <c r="R53" s="34" t="n"/>
-      <c r="S53" s="34" t="n"/>
-      <c r="T53" s="35" t="n"/>
-      <c r="U53" s="36" t="inlineStr">
-        <is>
-          <t>入力検証エラーでは結果コード（ResultCode）、戻り値（ReturnValue）を含める。解析前エラーやデバイスコネクタ制御では空またはnullの場合がある。</t>
-        </is>
-      </c>
-      <c r="V53" s="34" t="n"/>
-      <c r="W53" s="34" t="n"/>
-      <c r="X53" s="34" t="n"/>
-      <c r="Y53" s="34" t="n"/>
-      <c r="Z53" s="37" t="n"/>
-    </row>
-    <row r="55" ht="18" customHeight="1">
-      <c r="B55" s="42" t="inlineStr">
-        <is>
-          <t>■8.4 イベント通知</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="18" customHeight="1">
-      <c r="B57" s="45" t="inlineStr">
-        <is>
           <t>■8.4.1 イベント通知JSON例</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="42" customHeight="1">
-      <c r="B59" s="24" t="inlineStr">
+    <row r="48" ht="42" customHeight="1">
+      <c r="B48" s="24" t="inlineStr">
         <is>
           <t>デバイス処理結果通知は、個別デバイス処理が同期応答とは別に完了結果を返す場合に生成する。イベント種別（EventType）とメッセージ（Message）には、デバイス処理結果通知（ReplyDevice）を設定する。デバイス制御は受信後、デバイスID、メソッドID、ハンドル、および関連要求IDを使ってアプリケーション層の購読処理へ通知する。</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="195" customHeight="1">
-      <c r="B60" s="99" t="inlineStr">
+    <row r="49" ht="195" customHeight="1">
+      <c r="B49" s="99" t="inlineStr">
         <is>
           <t>{
   "EventId": "a1b2c3",
@@ -6848,175 +6593,554 @@
         </is>
       </c>
     </row>
-    <row r="61" ht="18" customHeight="1">
-      <c r="B61" s="45" t="inlineStr">
+    <row r="50" ht="18" customHeight="1">
+      <c r="B50" s="45" t="inlineStr">
         <is>
           <t>■8.4.2 イベント通知項目</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="20" customHeight="1">
-      <c r="B63" s="25" t="inlineStr">
+    <row r="52" ht="20" customHeight="1">
+      <c r="B52" s="25" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="C63" s="26" t="inlineStr">
+      <c r="C52" s="26" t="inlineStr">
         <is>
           <t>項目名</t>
         </is>
       </c>
-      <c r="D63" s="5" t="n"/>
-      <c r="E63" s="5" t="n"/>
-      <c r="F63" s="6" t="n"/>
-      <c r="G63" s="26" t="inlineStr">
+      <c r="D52" s="5" t="n"/>
+      <c r="E52" s="5" t="n"/>
+      <c r="F52" s="6" t="n"/>
+      <c r="G52" s="26" t="inlineStr">
         <is>
           <t>型</t>
         </is>
       </c>
-      <c r="H63" s="6" t="n"/>
-      <c r="I63" s="26" t="inlineStr">
+      <c r="H52" s="6" t="n"/>
+      <c r="I52" s="26" t="inlineStr">
         <is>
           <t>必須</t>
         </is>
       </c>
-      <c r="J63" s="6" t="n"/>
-      <c r="K63" s="26" t="inlineStr">
+      <c r="J52" s="6" t="n"/>
+      <c r="K52" s="26" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="L63" s="5" t="n"/>
-      <c r="M63" s="5" t="n"/>
-      <c r="N63" s="5" t="n"/>
-      <c r="O63" s="5" t="n"/>
-      <c r="P63" s="6" t="n"/>
-      <c r="Q63" s="26" t="inlineStr">
+      <c r="L52" s="5" t="n"/>
+      <c r="M52" s="5" t="n"/>
+      <c r="N52" s="5" t="n"/>
+      <c r="O52" s="5" t="n"/>
+      <c r="P52" s="6" t="n"/>
+      <c r="Q52" s="26" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="R63" s="5" t="n"/>
-      <c r="S63" s="5" t="n"/>
-      <c r="T63" s="5" t="n"/>
-      <c r="U63" s="5" t="n"/>
-      <c r="V63" s="5" t="n"/>
-      <c r="W63" s="5" t="n"/>
-      <c r="X63" s="5" t="n"/>
-      <c r="Y63" s="5" t="n"/>
-      <c r="Z63" s="9" t="n"/>
-    </row>
-    <row r="64" ht="24" customHeight="1">
-      <c r="B64" s="27" t="inlineStr">
+      <c r="R52" s="5" t="n"/>
+      <c r="S52" s="5" t="n"/>
+      <c r="T52" s="5" t="n"/>
+      <c r="U52" s="5" t="n"/>
+      <c r="V52" s="5" t="n"/>
+      <c r="W52" s="5" t="n"/>
+      <c r="X52" s="5" t="n"/>
+      <c r="Y52" s="5" t="n"/>
+      <c r="Z52" s="9" t="n"/>
+    </row>
+    <row r="53" ht="24" customHeight="1">
+      <c r="B53" s="27" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C64" s="16" t="inlineStr">
+      <c r="C53" s="16" t="inlineStr">
         <is>
           <t>イベントID（EventId）</t>
         </is>
       </c>
-      <c r="D64" s="28" t="n"/>
-      <c r="E64" s="28" t="n"/>
-      <c r="F64" s="29" t="n"/>
-      <c r="G64" s="16" t="inlineStr">
+      <c r="D53" s="28" t="n"/>
+      <c r="E53" s="28" t="n"/>
+      <c r="F53" s="29" t="n"/>
+      <c r="G53" s="16" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="H64" s="29" t="n"/>
-      <c r="I64" s="16" t="inlineStr">
+      <c r="H53" s="29" t="n"/>
+      <c r="I53" s="16" t="inlineStr">
         <is>
           <t>必須</t>
         </is>
       </c>
-      <c r="J64" s="29" t="n"/>
-      <c r="K64" s="16" t="inlineStr">
+      <c r="J53" s="29" t="n"/>
+      <c r="K53" s="16" t="inlineStr">
         <is>
           <t>イベント識別ID。</t>
         </is>
       </c>
-      <c r="L64" s="28" t="n"/>
-      <c r="M64" s="28" t="n"/>
-      <c r="N64" s="28" t="n"/>
-      <c r="O64" s="28" t="n"/>
-      <c r="P64" s="29" t="n"/>
-      <c r="Q64" s="16" t="inlineStr">
+      <c r="L53" s="28" t="n"/>
+      <c r="M53" s="28" t="n"/>
+      <c r="N53" s="28" t="n"/>
+      <c r="O53" s="28" t="n"/>
+      <c r="P53" s="29" t="n"/>
+      <c r="Q53" s="16" t="inlineStr">
         <is>
           <t>デバイスコネクタ側でGUID形式のIDを生成する。</t>
         </is>
       </c>
-      <c r="R64" s="28" t="n"/>
-      <c r="S64" s="28" t="n"/>
-      <c r="T64" s="28" t="n"/>
-      <c r="U64" s="28" t="n"/>
-      <c r="V64" s="28" t="n"/>
-      <c r="W64" s="28" t="n"/>
-      <c r="X64" s="28" t="n"/>
-      <c r="Y64" s="28" t="n"/>
-      <c r="Z64" s="30" t="n"/>
-    </row>
-    <row r="65" ht="36" customHeight="1">
-      <c r="B65" s="31" t="inlineStr">
+      <c r="R53" s="28" t="n"/>
+      <c r="S53" s="28" t="n"/>
+      <c r="T53" s="28" t="n"/>
+      <c r="U53" s="28" t="n"/>
+      <c r="V53" s="28" t="n"/>
+      <c r="W53" s="28" t="n"/>
+      <c r="X53" s="28" t="n"/>
+      <c r="Y53" s="28" t="n"/>
+      <c r="Z53" s="30" t="n"/>
+    </row>
+    <row r="54" ht="36" customHeight="1">
+      <c r="B54" s="31" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C65" s="32" t="inlineStr">
+      <c r="C54" s="32" t="inlineStr">
         <is>
           <t>イベント種別（EventType）</t>
         </is>
       </c>
-      <c r="D65" s="28" t="n"/>
-      <c r="E65" s="28" t="n"/>
-      <c r="F65" s="29" t="n"/>
-      <c r="G65" s="32" t="inlineStr">
+      <c r="D54" s="28" t="n"/>
+      <c r="E54" s="28" t="n"/>
+      <c r="F54" s="29" t="n"/>
+      <c r="G54" s="32" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="H65" s="29" t="n"/>
-      <c r="I65" s="32" t="inlineStr">
+      <c r="H54" s="29" t="n"/>
+      <c r="I54" s="32" t="inlineStr">
         <is>
           <t>必須</t>
         </is>
       </c>
-      <c r="J65" s="29" t="n"/>
-      <c r="K65" s="32" t="inlineStr">
+      <c r="J54" s="29" t="n"/>
+      <c r="K54" s="32" t="inlineStr">
         <is>
           <t>イベント種別。</t>
         </is>
       </c>
-      <c r="L65" s="28" t="n"/>
-      <c r="M65" s="28" t="n"/>
-      <c r="N65" s="28" t="n"/>
-      <c r="O65" s="28" t="n"/>
-      <c r="P65" s="29" t="n"/>
-      <c r="Q65" s="32" t="inlineStr">
+      <c r="L54" s="28" t="n"/>
+      <c r="M54" s="28" t="n"/>
+      <c r="N54" s="28" t="n"/>
+      <c r="O54" s="28" t="n"/>
+      <c r="P54" s="29" t="n"/>
+      <c r="Q54" s="32" t="inlineStr">
         <is>
           <t>デバイス処理結果通知（ReplyDevice）を設定する。</t>
         </is>
       </c>
-      <c r="R65" s="28" t="n"/>
-      <c r="S65" s="28" t="n"/>
-      <c r="T65" s="28" t="n"/>
-      <c r="U65" s="28" t="n"/>
-      <c r="V65" s="28" t="n"/>
-      <c r="W65" s="28" t="n"/>
-      <c r="X65" s="28" t="n"/>
-      <c r="Y65" s="28" t="n"/>
-      <c r="Z65" s="30" t="n"/>
-    </row>
-    <row r="66" ht="24" customHeight="1">
+      <c r="R54" s="28" t="n"/>
+      <c r="S54" s="28" t="n"/>
+      <c r="T54" s="28" t="n"/>
+      <c r="U54" s="28" t="n"/>
+      <c r="V54" s="28" t="n"/>
+      <c r="W54" s="28" t="n"/>
+      <c r="X54" s="28" t="n"/>
+      <c r="Y54" s="28" t="n"/>
+      <c r="Z54" s="30" t="n"/>
+    </row>
+    <row r="55" ht="24" customHeight="1">
+      <c r="B55" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C55" s="16" t="inlineStr">
+        <is>
+          <t>デバイスID（DeviceId）</t>
+        </is>
+      </c>
+      <c r="D55" s="28" t="n"/>
+      <c r="E55" s="28" t="n"/>
+      <c r="F55" s="29" t="n"/>
+      <c r="G55" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="H55" s="29" t="n"/>
+      <c r="I55" s="16" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="J55" s="29" t="n"/>
+      <c r="K55" s="16" t="inlineStr">
+        <is>
+          <t>対象デバイスID。</t>
+        </is>
+      </c>
+      <c r="L55" s="28" t="n"/>
+      <c r="M55" s="28" t="n"/>
+      <c r="N55" s="28" t="n"/>
+      <c r="O55" s="28" t="n"/>
+      <c r="P55" s="29" t="n"/>
+      <c r="Q55" s="16" t="inlineStr">
+        <is>
+          <t>応答元デバイスを示す。</t>
+        </is>
+      </c>
+      <c r="R55" s="28" t="n"/>
+      <c r="S55" s="28" t="n"/>
+      <c r="T55" s="28" t="n"/>
+      <c r="U55" s="28" t="n"/>
+      <c r="V55" s="28" t="n"/>
+      <c r="W55" s="28" t="n"/>
+      <c r="X55" s="28" t="n"/>
+      <c r="Y55" s="28" t="n"/>
+      <c r="Z55" s="30" t="n"/>
+    </row>
+    <row r="56" ht="24" customHeight="1">
+      <c r="B56" s="31" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C56" s="32" t="inlineStr">
+        <is>
+          <t>メソッドID（MethodId）</t>
+        </is>
+      </c>
+      <c r="D56" s="28" t="n"/>
+      <c r="E56" s="28" t="n"/>
+      <c r="F56" s="29" t="n"/>
+      <c r="G56" s="32" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="H56" s="29" t="n"/>
+      <c r="I56" s="32" t="inlineStr">
+        <is>
+          <t>任意</t>
+        </is>
+      </c>
+      <c r="J56" s="29" t="n"/>
+      <c r="K56" s="32" t="inlineStr">
+        <is>
+          <t>対象メソッドID。</t>
+        </is>
+      </c>
+      <c r="L56" s="28" t="n"/>
+      <c r="M56" s="28" t="n"/>
+      <c r="N56" s="28" t="n"/>
+      <c r="O56" s="28" t="n"/>
+      <c r="P56" s="29" t="n"/>
+      <c r="Q56" s="32" t="inlineStr">
+        <is>
+          <t>デバイス処理結果通知を生成したメソッドIDを設定する。</t>
+        </is>
+      </c>
+      <c r="R56" s="28" t="n"/>
+      <c r="S56" s="28" t="n"/>
+      <c r="T56" s="28" t="n"/>
+      <c r="U56" s="28" t="n"/>
+      <c r="V56" s="28" t="n"/>
+      <c r="W56" s="28" t="n"/>
+      <c r="X56" s="28" t="n"/>
+      <c r="Y56" s="28" t="n"/>
+      <c r="Z56" s="30" t="n"/>
+    </row>
+    <row r="57" ht="24" customHeight="1">
+      <c r="B57" s="27" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C57" s="16" t="inlineStr">
+        <is>
+          <t>ハンドル（Handle）</t>
+        </is>
+      </c>
+      <c r="D57" s="28" t="n"/>
+      <c r="E57" s="28" t="n"/>
+      <c r="F57" s="29" t="n"/>
+      <c r="G57" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="H57" s="29" t="n"/>
+      <c r="I57" s="16" t="inlineStr">
+        <is>
+          <t>任意</t>
+        </is>
+      </c>
+      <c r="J57" s="29" t="n"/>
+      <c r="K57" s="16" t="inlineStr">
+        <is>
+          <t>呼出元を識別するハンドル。</t>
+        </is>
+      </c>
+      <c r="L57" s="28" t="n"/>
+      <c r="M57" s="28" t="n"/>
+      <c r="N57" s="28" t="n"/>
+      <c r="O57" s="28" t="n"/>
+      <c r="P57" s="29" t="n"/>
+      <c r="Q57" s="16" t="inlineStr">
+        <is>
+          <t>呼出元のハンドルを引き継ぐ。</t>
+        </is>
+      </c>
+      <c r="R57" s="28" t="n"/>
+      <c r="S57" s="28" t="n"/>
+      <c r="T57" s="28" t="n"/>
+      <c r="U57" s="28" t="n"/>
+      <c r="V57" s="28" t="n"/>
+      <c r="W57" s="28" t="n"/>
+      <c r="X57" s="28" t="n"/>
+      <c r="Y57" s="28" t="n"/>
+      <c r="Z57" s="30" t="n"/>
+    </row>
+    <row r="58" ht="24" customHeight="1">
+      <c r="B58" s="31" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C58" s="32" t="inlineStr">
+        <is>
+          <t>メッセージ（Message）</t>
+        </is>
+      </c>
+      <c r="D58" s="28" t="n"/>
+      <c r="E58" s="28" t="n"/>
+      <c r="F58" s="29" t="n"/>
+      <c r="G58" s="32" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="H58" s="29" t="n"/>
+      <c r="I58" s="32" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="J58" s="29" t="n"/>
+      <c r="K58" s="32" t="inlineStr">
+        <is>
+          <t>通知メッセージ。</t>
+        </is>
+      </c>
+      <c r="L58" s="28" t="n"/>
+      <c r="M58" s="28" t="n"/>
+      <c r="N58" s="28" t="n"/>
+      <c r="O58" s="28" t="n"/>
+      <c r="P58" s="29" t="n"/>
+      <c r="Q58" s="32" t="inlineStr">
+        <is>
+          <t>デバイス処理結果通知（ReplyDevice）を設定する。</t>
+        </is>
+      </c>
+      <c r="R58" s="28" t="n"/>
+      <c r="S58" s="28" t="n"/>
+      <c r="T58" s="28" t="n"/>
+      <c r="U58" s="28" t="n"/>
+      <c r="V58" s="28" t="n"/>
+      <c r="W58" s="28" t="n"/>
+      <c r="X58" s="28" t="n"/>
+      <c r="Y58" s="28" t="n"/>
+      <c r="Z58" s="30" t="n"/>
+    </row>
+    <row r="59" ht="36" customHeight="1">
+      <c r="B59" s="27" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C59" s="16" t="inlineStr">
+        <is>
+          <t>付加データ（Payload）</t>
+        </is>
+      </c>
+      <c r="D59" s="28" t="n"/>
+      <c r="E59" s="28" t="n"/>
+      <c r="F59" s="29" t="n"/>
+      <c r="G59" s="16" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="H59" s="29" t="n"/>
+      <c r="I59" s="16" t="inlineStr">
+        <is>
+          <t>任意</t>
+        </is>
+      </c>
+      <c r="J59" s="29" t="n"/>
+      <c r="K59" s="16" t="inlineStr">
+        <is>
+          <t>文字列キーと文字列値で構成する戻りデータ。</t>
+        </is>
+      </c>
+      <c r="L59" s="28" t="n"/>
+      <c r="M59" s="28" t="n"/>
+      <c r="N59" s="28" t="n"/>
+      <c r="O59" s="28" t="n"/>
+      <c r="P59" s="29" t="n"/>
+      <c r="Q59" s="16" t="inlineStr">
+        <is>
+          <t>デバイス制御はイベントデータとしてアプリケーション層へ渡す。</t>
+        </is>
+      </c>
+      <c r="R59" s="28" t="n"/>
+      <c r="S59" s="28" t="n"/>
+      <c r="T59" s="28" t="n"/>
+      <c r="U59" s="28" t="n"/>
+      <c r="V59" s="28" t="n"/>
+      <c r="W59" s="28" t="n"/>
+      <c r="X59" s="28" t="n"/>
+      <c r="Y59" s="28" t="n"/>
+      <c r="Z59" s="30" t="n"/>
+    </row>
+    <row r="60" ht="36" customHeight="1">
+      <c r="B60" s="38" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C60" s="39" t="inlineStr">
+        <is>
+          <t>関連要求ID（RelatedRequestId）</t>
+        </is>
+      </c>
+      <c r="D60" s="34" t="n"/>
+      <c r="E60" s="34" t="n"/>
+      <c r="F60" s="35" t="n"/>
+      <c r="G60" s="39" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="H60" s="35" t="n"/>
+      <c r="I60" s="39" t="inlineStr">
+        <is>
+          <t>任意</t>
+        </is>
+      </c>
+      <c r="J60" s="35" t="n"/>
+      <c r="K60" s="39" t="inlineStr">
+        <is>
+          <t>関連するコマンド要求ID。</t>
+        </is>
+      </c>
+      <c r="L60" s="34" t="n"/>
+      <c r="M60" s="34" t="n"/>
+      <c r="N60" s="34" t="n"/>
+      <c r="O60" s="34" t="n"/>
+      <c r="P60" s="35" t="n"/>
+      <c r="Q60" s="39" t="inlineStr">
+        <is>
+          <t>要求との対応を特定できる場合は要求IDを設定する。デバイス起点で対応要求を特定できない場合はnullとする。</t>
+        </is>
+      </c>
+      <c r="R60" s="34" t="n"/>
+      <c r="S60" s="34" t="n"/>
+      <c r="T60" s="34" t="n"/>
+      <c r="U60" s="34" t="n"/>
+      <c r="V60" s="34" t="n"/>
+      <c r="W60" s="34" t="n"/>
+      <c r="X60" s="34" t="n"/>
+      <c r="Y60" s="34" t="n"/>
+      <c r="Z60" s="37" t="n"/>
+    </row>
+    <row r="62" ht="18" customHeight="1">
+      <c r="B62" s="44" t="inlineStr">
+        <is>
+          <t>■8.5 メッセージ定義</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="18" customHeight="1">
+      <c r="B64" s="24" t="inlineStr">
+        <is>
+          <t>メッセージ識別値欄には、処理内容の日本語論理名と通信で使用する識別値を併記する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="20" customHeight="1">
+      <c r="B65" s="25" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="C65" s="26" t="inlineStr">
+        <is>
+          <t>メッセージ識別値</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="n"/>
+      <c r="E65" s="5" t="n"/>
+      <c r="F65" s="6" t="n"/>
+      <c r="G65" s="26" t="inlineStr">
+        <is>
+          <t>分類</t>
+        </is>
+      </c>
+      <c r="H65" s="6" t="n"/>
+      <c r="I65" s="26" t="inlineStr">
+        <is>
+          <t>デバイスID（DeviceId）</t>
+        </is>
+      </c>
+      <c r="J65" s="5" t="n"/>
+      <c r="K65" s="6" t="n"/>
+      <c r="L65" s="26" t="inlineStr">
+        <is>
+          <t>メソッドID（MethodId）</t>
+        </is>
+      </c>
+      <c r="M65" s="5" t="n"/>
+      <c r="N65" s="6" t="n"/>
+      <c r="O65" s="26" t="inlineStr">
+        <is>
+          <t>主な用途</t>
+        </is>
+      </c>
+      <c r="P65" s="5" t="n"/>
+      <c r="Q65" s="5" t="n"/>
+      <c r="R65" s="6" t="n"/>
+      <c r="S65" s="26" t="inlineStr">
+        <is>
+          <t>正常時の扱い</t>
+        </is>
+      </c>
+      <c r="T65" s="5" t="n"/>
+      <c r="U65" s="5" t="n"/>
+      <c r="V65" s="6" t="n"/>
+      <c r="W65" s="26" t="inlineStr">
+        <is>
+          <t>異常時の扱い</t>
+        </is>
+      </c>
+      <c r="X65" s="5" t="n"/>
+      <c r="Y65" s="5" t="n"/>
+      <c r="Z65" s="9" t="n"/>
+    </row>
+    <row r="66" ht="36" customHeight="1">
       <c r="B66" s="27" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C66" s="16" t="inlineStr">
         <is>
-          <t>デバイスID（DeviceId）</t>
+          <t>デバイス使用開始（DeviceUse）</t>
         </is>
       </c>
       <c r="D66" s="28" t="n"/>
@@ -7024,7 +7148,7 @@
       <c r="F66" s="29" t="n"/>
       <c r="G66" s="16" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>デバイス操作</t>
         </is>
       </c>
       <c r="H66" s="29" t="n"/>
@@ -7033,41 +7157,49 @@
           <t>必須</t>
         </is>
       </c>
-      <c r="J66" s="29" t="n"/>
-      <c r="K66" s="16" t="inlineStr">
-        <is>
-          <t>対象デバイスID。</t>
-        </is>
-      </c>
-      <c r="L66" s="28" t="n"/>
+      <c r="J66" s="28" t="n"/>
+      <c r="K66" s="29" t="n"/>
+      <c r="L66" s="16" t="inlineStr">
+        <is>
+          <t>任意</t>
+        </is>
+      </c>
       <c r="M66" s="28" t="n"/>
-      <c r="N66" s="28" t="n"/>
-      <c r="O66" s="28" t="n"/>
-      <c r="P66" s="29" t="n"/>
-      <c r="Q66" s="16" t="inlineStr">
-        <is>
-          <t>応答元デバイスを示す。</t>
-        </is>
-      </c>
-      <c r="R66" s="28" t="n"/>
-      <c r="S66" s="28" t="n"/>
+      <c r="N66" s="29" t="n"/>
+      <c r="O66" s="16" t="inlineStr">
+        <is>
+          <t>デバイス使用開始。</t>
+        </is>
+      </c>
+      <c r="P66" s="28" t="n"/>
+      <c r="Q66" s="28" t="n"/>
+      <c r="R66" s="29" t="n"/>
+      <c r="S66" s="16" t="inlineStr">
+        <is>
+          <t>対象デバイスの使用開始処理を呼ぶ。</t>
+        </is>
+      </c>
       <c r="T66" s="28" t="n"/>
       <c r="U66" s="28" t="n"/>
-      <c r="V66" s="28" t="n"/>
-      <c r="W66" s="28" t="n"/>
+      <c r="V66" s="29" t="n"/>
+      <c r="W66" s="16" t="inlineStr">
+        <is>
+          <t>デバイスID未指定または未登録時は失敗応答。</t>
+        </is>
+      </c>
       <c r="X66" s="28" t="n"/>
       <c r="Y66" s="28" t="n"/>
       <c r="Z66" s="30" t="n"/>
     </row>
-    <row r="67" ht="24" customHeight="1">
+    <row r="67" ht="36" customHeight="1">
       <c r="B67" s="31" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C67" s="32" t="inlineStr">
         <is>
-          <t>メソッドID（MethodId）</t>
+          <t>デバイス使用終了（DeviceUnUse）</t>
         </is>
       </c>
       <c r="D67" s="28" t="n"/>
@@ -7075,50 +7207,58 @@
       <c r="F67" s="29" t="n"/>
       <c r="G67" s="32" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>デバイス操作</t>
         </is>
       </c>
       <c r="H67" s="29" t="n"/>
       <c r="I67" s="32" t="inlineStr">
         <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="J67" s="28" t="n"/>
+      <c r="K67" s="29" t="n"/>
+      <c r="L67" s="32" t="inlineStr">
+        <is>
           <t>任意</t>
         </is>
       </c>
-      <c r="J67" s="29" t="n"/>
-      <c r="K67" s="32" t="inlineStr">
-        <is>
-          <t>対象メソッドID。</t>
-        </is>
-      </c>
-      <c r="L67" s="28" t="n"/>
       <c r="M67" s="28" t="n"/>
-      <c r="N67" s="28" t="n"/>
-      <c r="O67" s="28" t="n"/>
-      <c r="P67" s="29" t="n"/>
-      <c r="Q67" s="32" t="inlineStr">
-        <is>
-          <t>デバイス処理結果通知を生成したメソッドIDを設定する。</t>
-        </is>
-      </c>
-      <c r="R67" s="28" t="n"/>
-      <c r="S67" s="28" t="n"/>
+      <c r="N67" s="29" t="n"/>
+      <c r="O67" s="32" t="inlineStr">
+        <is>
+          <t>デバイス使用終了。</t>
+        </is>
+      </c>
+      <c r="P67" s="28" t="n"/>
+      <c r="Q67" s="28" t="n"/>
+      <c r="R67" s="29" t="n"/>
+      <c r="S67" s="32" t="inlineStr">
+        <is>
+          <t>対象デバイスの使用終了処理を呼ぶ。</t>
+        </is>
+      </c>
       <c r="T67" s="28" t="n"/>
       <c r="U67" s="28" t="n"/>
-      <c r="V67" s="28" t="n"/>
-      <c r="W67" s="28" t="n"/>
+      <c r="V67" s="29" t="n"/>
+      <c r="W67" s="32" t="inlineStr">
+        <is>
+          <t>デバイスID未指定または未登録時は失敗応答。</t>
+        </is>
+      </c>
       <c r="X67" s="28" t="n"/>
       <c r="Y67" s="28" t="n"/>
       <c r="Z67" s="30" t="n"/>
     </row>
-    <row r="68" ht="24" customHeight="1">
+    <row r="68" ht="36" customHeight="1">
       <c r="B68" s="27" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C68" s="16" t="inlineStr">
         <is>
-          <t>ハンドル（Handle）</t>
+          <t>デバイス使用終了完了（DeviceUnUseComplete）</t>
         </is>
       </c>
       <c r="D68" s="28" t="n"/>
@@ -7126,50 +7266,58 @@
       <c r="F68" s="29" t="n"/>
       <c r="G68" s="16" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>デバイス操作</t>
         </is>
       </c>
       <c r="H68" s="29" t="n"/>
       <c r="I68" s="16" t="inlineStr">
         <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="J68" s="28" t="n"/>
+      <c r="K68" s="29" t="n"/>
+      <c r="L68" s="16" t="inlineStr">
+        <is>
           <t>任意</t>
         </is>
       </c>
-      <c r="J68" s="29" t="n"/>
-      <c r="K68" s="16" t="inlineStr">
-        <is>
-          <t>既存互換用のハンドル。</t>
-        </is>
-      </c>
-      <c r="L68" s="28" t="n"/>
       <c r="M68" s="28" t="n"/>
-      <c r="N68" s="28" t="n"/>
-      <c r="O68" s="28" t="n"/>
-      <c r="P68" s="29" t="n"/>
-      <c r="Q68" s="16" t="inlineStr">
-        <is>
-          <t>呼出元のハンドルを引き継ぐ。</t>
-        </is>
-      </c>
-      <c r="R68" s="28" t="n"/>
-      <c r="S68" s="28" t="n"/>
+      <c r="N68" s="29" t="n"/>
+      <c r="O68" s="16" t="inlineStr">
+        <is>
+          <t>使用完了後のプロセス情報削除。</t>
+        </is>
+      </c>
+      <c r="P68" s="28" t="n"/>
+      <c r="Q68" s="28" t="n"/>
+      <c r="R68" s="29" t="n"/>
+      <c r="S68" s="16" t="inlineStr">
+        <is>
+          <t>プロセス情報を削除し、使用終了処理を行う。</t>
+        </is>
+      </c>
       <c r="T68" s="28" t="n"/>
       <c r="U68" s="28" t="n"/>
-      <c r="V68" s="28" t="n"/>
-      <c r="W68" s="28" t="n"/>
+      <c r="V68" s="29" t="n"/>
+      <c r="W68" s="16" t="inlineStr">
+        <is>
+          <t>対象情報がない場合は結果コードで返す。</t>
+        </is>
+      </c>
       <c r="X68" s="28" t="n"/>
       <c r="Y68" s="28" t="n"/>
       <c r="Z68" s="30" t="n"/>
     </row>
-    <row r="69" ht="24" customHeight="1">
+    <row r="69" ht="54" customHeight="1">
       <c r="B69" s="31" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C69" s="32" t="inlineStr">
         <is>
-          <t>メッセージ（Message）</t>
+          <t>デバイスメソッド実行（DeviceMethod）</t>
         </is>
       </c>
       <c r="D69" s="28" t="n"/>
@@ -7177,7 +7325,7 @@
       <c r="F69" s="29" t="n"/>
       <c r="G69" s="32" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>デバイス操作</t>
         </is>
       </c>
       <c r="H69" s="29" t="n"/>
@@ -7186,41 +7334,49 @@
           <t>必須</t>
         </is>
       </c>
-      <c r="J69" s="29" t="n"/>
-      <c r="K69" s="32" t="inlineStr">
-        <is>
-          <t>通知メッセージ。</t>
-        </is>
-      </c>
-      <c r="L69" s="28" t="n"/>
+      <c r="J69" s="28" t="n"/>
+      <c r="K69" s="29" t="n"/>
+      <c r="L69" s="32" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
       <c r="M69" s="28" t="n"/>
-      <c r="N69" s="28" t="n"/>
-      <c r="O69" s="28" t="n"/>
-      <c r="P69" s="29" t="n"/>
-      <c r="Q69" s="32" t="inlineStr">
-        <is>
-          <t>デバイス処理結果通知（ReplyDevice）を設定する。</t>
-        </is>
-      </c>
-      <c r="R69" s="28" t="n"/>
-      <c r="S69" s="28" t="n"/>
+      <c r="N69" s="29" t="n"/>
+      <c r="O69" s="32" t="inlineStr">
+        <is>
+          <t>デバイス固有メソッド実行。</t>
+        </is>
+      </c>
+      <c r="P69" s="28" t="n"/>
+      <c r="Q69" s="28" t="n"/>
+      <c r="R69" s="29" t="n"/>
+      <c r="S69" s="32" t="inlineStr">
+        <is>
+          <t>対象デバイスのメソッド実行処理を呼ぶ。</t>
+        </is>
+      </c>
       <c r="T69" s="28" t="n"/>
       <c r="U69" s="28" t="n"/>
-      <c r="V69" s="28" t="n"/>
-      <c r="W69" s="28" t="n"/>
+      <c r="V69" s="29" t="n"/>
+      <c r="W69" s="32" t="inlineStr">
+        <is>
+          <t>メソッドID未指定または未登録デバイス時は失敗応答。</t>
+        </is>
+      </c>
       <c r="X69" s="28" t="n"/>
       <c r="Y69" s="28" t="n"/>
       <c r="Z69" s="30" t="n"/>
     </row>
-    <row r="70" ht="36" customHeight="1">
+    <row r="70" ht="72" customHeight="1">
       <c r="B70" s="27" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C70" s="16" t="inlineStr">
         <is>
-          <t>付加データ（Payload）</t>
+          <t>デバイスコネクタ停止要求（Kill）</t>
         </is>
       </c>
       <c r="D70" s="28" t="n"/>
@@ -7228,7 +7384,7 @@
       <c r="F70" s="29" t="n"/>
       <c r="G70" s="16" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>デバイスコネクタ制御</t>
         </is>
       </c>
       <c r="H70" s="29" t="n"/>
@@ -7237,834 +7393,402 @@
           <t>任意</t>
         </is>
       </c>
-      <c r="J70" s="29" t="n"/>
-      <c r="K70" s="16" t="inlineStr">
-        <is>
-          <t>文字列キーと文字列値で構成する戻りデータ。</t>
-        </is>
-      </c>
-      <c r="L70" s="28" t="n"/>
+      <c r="J70" s="28" t="n"/>
+      <c r="K70" s="29" t="n"/>
+      <c r="L70" s="16" t="inlineStr">
+        <is>
+          <t>任意</t>
+        </is>
+      </c>
       <c r="M70" s="28" t="n"/>
-      <c r="N70" s="28" t="n"/>
-      <c r="O70" s="28" t="n"/>
-      <c r="P70" s="29" t="n"/>
-      <c r="Q70" s="16" t="inlineStr">
-        <is>
-          <t>デバイス制御はイベントデータとしてアプリケーション層へ渡す。</t>
-        </is>
-      </c>
-      <c r="R70" s="28" t="n"/>
-      <c r="S70" s="28" t="n"/>
+      <c r="N70" s="29" t="n"/>
+      <c r="O70" s="16" t="inlineStr">
+        <is>
+          <t>デバイスコネクタ停止要求。</t>
+        </is>
+      </c>
+      <c r="P70" s="28" t="n"/>
+      <c r="Q70" s="28" t="n"/>
+      <c r="R70" s="29" t="n"/>
+      <c r="S70" s="16" t="inlineStr">
+        <is>
+          <t>停止要求受付メッセージ（Kill accepted）の書込完了後、500ミリ秒待機して停止処理へ進む。</t>
+        </is>
+      </c>
       <c r="T70" s="28" t="n"/>
       <c r="U70" s="28" t="n"/>
-      <c r="V70" s="28" t="n"/>
-      <c r="W70" s="28" t="n"/>
+      <c r="V70" s="29" t="n"/>
+      <c r="W70" s="16" t="inlineStr">
+        <is>
+          <t>停止中例外は受付応答後にデバイスコネクタ側ログへ出力する。</t>
+        </is>
+      </c>
       <c r="X70" s="28" t="n"/>
       <c r="Y70" s="28" t="n"/>
       <c r="Z70" s="30" t="n"/>
     </row>
-    <row r="71" ht="36" customHeight="1">
-      <c r="B71" s="43" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="C71" s="44" t="inlineStr">
-        <is>
-          <t>関連要求ID（RelatedRequestId）</t>
-        </is>
-      </c>
-      <c r="D71" s="34" t="n"/>
-      <c r="E71" s="34" t="n"/>
-      <c r="F71" s="35" t="n"/>
-      <c r="G71" s="44" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="H71" s="35" t="n"/>
-      <c r="I71" s="44" t="inlineStr">
+    <row r="71" ht="90" customHeight="1">
+      <c r="B71" s="31" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C71" s="32" t="inlineStr">
+        <is>
+          <t>デバイスコネクタ再起動要求／Host再起動要求（ReStart）</t>
+        </is>
+      </c>
+      <c r="D71" s="28" t="n"/>
+      <c r="E71" s="28" t="n"/>
+      <c r="F71" s="29" t="n"/>
+      <c r="G71" s="32" t="inlineStr">
+        <is>
+          <t>デバイスコネクタ制御</t>
+        </is>
+      </c>
+      <c r="H71" s="29" t="n"/>
+      <c r="I71" s="32" t="inlineStr">
         <is>
           <t>任意</t>
         </is>
       </c>
-      <c r="J71" s="35" t="n"/>
-      <c r="K71" s="44" t="inlineStr">
-        <is>
-          <t>関連するコマンド要求ID。</t>
-        </is>
-      </c>
-      <c r="L71" s="34" t="n"/>
-      <c r="M71" s="34" t="n"/>
-      <c r="N71" s="34" t="n"/>
-      <c r="O71" s="34" t="n"/>
-      <c r="P71" s="35" t="n"/>
-      <c r="Q71" s="44" t="inlineStr">
-        <is>
-          <t>要求との対応を特定できる場合は要求IDを設定する。デバイス起点で対応要求を特定できない場合はnullとする。</t>
-        </is>
-      </c>
-      <c r="R71" s="34" t="n"/>
-      <c r="S71" s="34" t="n"/>
-      <c r="T71" s="34" t="n"/>
-      <c r="U71" s="34" t="n"/>
-      <c r="V71" s="34" t="n"/>
-      <c r="W71" s="34" t="n"/>
-      <c r="X71" s="34" t="n"/>
-      <c r="Y71" s="34" t="n"/>
-      <c r="Z71" s="37" t="n"/>
-    </row>
-    <row r="73" ht="18" customHeight="1">
-      <c r="B73" s="42" t="inlineStr">
-        <is>
-          <t>■8.5 メッセージ定義</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="18" customHeight="1">
-      <c r="B75" s="24" t="inlineStr">
-        <is>
-          <t>メッセージ識別値欄には、処理内容の日本語論理名と通信で使用する識別値を併記する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="20" customHeight="1">
-      <c r="B76" s="25" t="inlineStr">
-        <is>
-          <t>No.</t>
-        </is>
-      </c>
-      <c r="C76" s="26" t="inlineStr">
-        <is>
-          <t>メッセージ識別値</t>
-        </is>
-      </c>
-      <c r="D76" s="5" t="n"/>
-      <c r="E76" s="5" t="n"/>
-      <c r="F76" s="6" t="n"/>
-      <c r="G76" s="26" t="inlineStr">
-        <is>
-          <t>分類</t>
-        </is>
-      </c>
-      <c r="H76" s="6" t="n"/>
-      <c r="I76" s="26" t="inlineStr">
-        <is>
-          <t>デバイスID（DeviceId）</t>
-        </is>
-      </c>
-      <c r="J76" s="5" t="n"/>
-      <c r="K76" s="6" t="n"/>
-      <c r="L76" s="26" t="inlineStr">
-        <is>
-          <t>メソッドID（MethodId）</t>
-        </is>
-      </c>
-      <c r="M76" s="5" t="n"/>
-      <c r="N76" s="6" t="n"/>
-      <c r="O76" s="26" t="inlineStr">
-        <is>
-          <t>主な用途</t>
-        </is>
-      </c>
-      <c r="P76" s="5" t="n"/>
-      <c r="Q76" s="5" t="n"/>
-      <c r="R76" s="6" t="n"/>
-      <c r="S76" s="26" t="inlineStr">
-        <is>
-          <t>正常時の扱い</t>
-        </is>
-      </c>
-      <c r="T76" s="5" t="n"/>
-      <c r="U76" s="5" t="n"/>
-      <c r="V76" s="6" t="n"/>
-      <c r="W76" s="26" t="inlineStr">
-        <is>
-          <t>異常時の扱い</t>
-        </is>
-      </c>
-      <c r="X76" s="5" t="n"/>
-      <c r="Y76" s="5" t="n"/>
-      <c r="Z76" s="9" t="n"/>
-    </row>
-    <row r="77" ht="36" customHeight="1">
-      <c r="B77" s="27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C77" s="16" t="inlineStr">
-        <is>
-          <t>デバイス使用開始（DeviceUse）</t>
-        </is>
-      </c>
-      <c r="D77" s="28" t="n"/>
-      <c r="E77" s="28" t="n"/>
-      <c r="F77" s="29" t="n"/>
-      <c r="G77" s="16" t="inlineStr">
-        <is>
-          <t>デバイス操作</t>
-        </is>
-      </c>
-      <c r="H77" s="29" t="n"/>
-      <c r="I77" s="16" t="inlineStr">
-        <is>
-          <t>必須</t>
-        </is>
-      </c>
-      <c r="J77" s="28" t="n"/>
-      <c r="K77" s="29" t="n"/>
-      <c r="L77" s="16" t="inlineStr">
+      <c r="J71" s="28" t="n"/>
+      <c r="K71" s="29" t="n"/>
+      <c r="L71" s="32" t="inlineStr">
         <is>
           <t>任意</t>
         </is>
       </c>
-      <c r="M77" s="28" t="n"/>
-      <c r="N77" s="29" t="n"/>
-      <c r="O77" s="16" t="inlineStr">
-        <is>
-          <t>デバイス使用開始。</t>
-        </is>
-      </c>
-      <c r="P77" s="28" t="n"/>
-      <c r="Q77" s="28" t="n"/>
-      <c r="R77" s="29" t="n"/>
-      <c r="S77" s="16" t="inlineStr">
-        <is>
-          <t>対象デバイスの使用開始処理を呼ぶ。</t>
-        </is>
-      </c>
-      <c r="T77" s="28" t="n"/>
-      <c r="U77" s="28" t="n"/>
-      <c r="V77" s="29" t="n"/>
-      <c r="W77" s="16" t="inlineStr">
-        <is>
-          <t>デバイスID未指定または未登録時は失敗応答。</t>
-        </is>
-      </c>
-      <c r="X77" s="28" t="n"/>
-      <c r="Y77" s="28" t="n"/>
-      <c r="Z77" s="30" t="n"/>
-    </row>
-    <row r="78" ht="36" customHeight="1">
-      <c r="B78" s="31" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C78" s="32" t="inlineStr">
-        <is>
-          <t>デバイス使用終了（DeviceUnUse）</t>
-        </is>
-      </c>
-      <c r="D78" s="28" t="n"/>
-      <c r="E78" s="28" t="n"/>
-      <c r="F78" s="29" t="n"/>
-      <c r="G78" s="32" t="inlineStr">
-        <is>
-          <t>デバイス操作</t>
-        </is>
-      </c>
-      <c r="H78" s="29" t="n"/>
-      <c r="I78" s="32" t="inlineStr">
-        <is>
-          <t>必須</t>
-        </is>
-      </c>
-      <c r="J78" s="28" t="n"/>
-      <c r="K78" s="29" t="n"/>
-      <c r="L78" s="32" t="inlineStr">
+      <c r="M71" s="28" t="n"/>
+      <c r="N71" s="29" t="n"/>
+      <c r="O71" s="32" t="inlineStr">
+        <is>
+          <t>デバイスコネクタ再起動要求。</t>
+        </is>
+      </c>
+      <c r="P71" s="28" t="n"/>
+      <c r="Q71" s="28" t="n"/>
+      <c r="R71" s="29" t="n"/>
+      <c r="S71" s="32" t="inlineStr">
+        <is>
+          <t>再起動要求受付メッセージ（Restart accepted）の書込完了後、500ミリ秒待機して停止・再起動する。</t>
+        </is>
+      </c>
+      <c r="T71" s="28" t="n"/>
+      <c r="U71" s="28" t="n"/>
+      <c r="V71" s="29" t="n"/>
+      <c r="W71" s="32" t="inlineStr">
+        <is>
+          <t>再起動中例外は受付応答後にデバイスコネクタ側ログへ出力する。</t>
+        </is>
+      </c>
+      <c r="X71" s="28" t="n"/>
+      <c r="Y71" s="28" t="n"/>
+      <c r="Z71" s="30" t="n"/>
+    </row>
+    <row r="72" ht="72" customHeight="1">
+      <c r="B72" s="33" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C72" s="36" t="inlineStr">
+        <is>
+          <t>デバイスコネクタ稼働確認（HealthCheck）</t>
+        </is>
+      </c>
+      <c r="D72" s="34" t="n"/>
+      <c r="E72" s="34" t="n"/>
+      <c r="F72" s="35" t="n"/>
+      <c r="G72" s="36" t="inlineStr">
+        <is>
+          <t>デバイスコネクタ制御</t>
+        </is>
+      </c>
+      <c r="H72" s="35" t="n"/>
+      <c r="I72" s="36" t="inlineStr">
         <is>
           <t>任意</t>
         </is>
       </c>
-      <c r="M78" s="28" t="n"/>
-      <c r="N78" s="29" t="n"/>
-      <c r="O78" s="32" t="inlineStr">
-        <is>
-          <t>デバイス使用終了。</t>
-        </is>
-      </c>
-      <c r="P78" s="28" t="n"/>
-      <c r="Q78" s="28" t="n"/>
-      <c r="R78" s="29" t="n"/>
-      <c r="S78" s="32" t="inlineStr">
-        <is>
-          <t>対象デバイスの使用終了処理を呼ぶ。</t>
-        </is>
-      </c>
-      <c r="T78" s="28" t="n"/>
-      <c r="U78" s="28" t="n"/>
-      <c r="V78" s="29" t="n"/>
-      <c r="W78" s="32" t="inlineStr">
-        <is>
-          <t>デバイスID未指定または未登録時は失敗応答。</t>
-        </is>
-      </c>
-      <c r="X78" s="28" t="n"/>
-      <c r="Y78" s="28" t="n"/>
-      <c r="Z78" s="30" t="n"/>
-    </row>
-    <row r="79" ht="36" customHeight="1">
-      <c r="B79" s="27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C79" s="16" t="inlineStr">
-        <is>
-          <t>デバイス使用終了完了（DeviceUnUseComplete）</t>
-        </is>
-      </c>
-      <c r="D79" s="28" t="n"/>
-      <c r="E79" s="28" t="n"/>
-      <c r="F79" s="29" t="n"/>
-      <c r="G79" s="16" t="inlineStr">
-        <is>
-          <t>デバイス操作</t>
-        </is>
-      </c>
-      <c r="H79" s="29" t="n"/>
-      <c r="I79" s="16" t="inlineStr">
-        <is>
-          <t>必須</t>
-        </is>
-      </c>
-      <c r="J79" s="28" t="n"/>
-      <c r="K79" s="29" t="n"/>
-      <c r="L79" s="16" t="inlineStr">
+      <c r="J72" s="34" t="n"/>
+      <c r="K72" s="35" t="n"/>
+      <c r="L72" s="36" t="inlineStr">
         <is>
           <t>任意</t>
         </is>
       </c>
-      <c r="M79" s="28" t="n"/>
-      <c r="N79" s="29" t="n"/>
-      <c r="O79" s="16" t="inlineStr">
-        <is>
-          <t>使用完了後のプロセス情報削除。</t>
-        </is>
-      </c>
-      <c r="P79" s="28" t="n"/>
-      <c r="Q79" s="28" t="n"/>
-      <c r="R79" s="29" t="n"/>
-      <c r="S79" s="16" t="inlineStr">
-        <is>
-          <t>プロセス情報を削除し、使用終了処理を行う。</t>
-        </is>
-      </c>
-      <c r="T79" s="28" t="n"/>
-      <c r="U79" s="28" t="n"/>
-      <c r="V79" s="29" t="n"/>
-      <c r="W79" s="16" t="inlineStr">
-        <is>
-          <t>対象情報がない場合は結果コードで返す。</t>
-        </is>
-      </c>
-      <c r="X79" s="28" t="n"/>
-      <c r="Y79" s="28" t="n"/>
-      <c r="Z79" s="30" t="n"/>
-    </row>
-    <row r="80" ht="54" customHeight="1">
-      <c r="B80" s="31" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C80" s="32" t="inlineStr">
-        <is>
-          <t>デバイスメソッド実行（DeviceMethod）</t>
-        </is>
-      </c>
-      <c r="D80" s="28" t="n"/>
-      <c r="E80" s="28" t="n"/>
-      <c r="F80" s="29" t="n"/>
-      <c r="G80" s="32" t="inlineStr">
-        <is>
-          <t>デバイス操作</t>
-        </is>
-      </c>
-      <c r="H80" s="29" t="n"/>
-      <c r="I80" s="32" t="inlineStr">
-        <is>
-          <t>必須</t>
-        </is>
-      </c>
-      <c r="J80" s="28" t="n"/>
-      <c r="K80" s="29" t="n"/>
-      <c r="L80" s="32" t="inlineStr">
-        <is>
-          <t>必須</t>
-        </is>
-      </c>
-      <c r="M80" s="28" t="n"/>
-      <c r="N80" s="29" t="n"/>
-      <c r="O80" s="32" t="inlineStr">
-        <is>
-          <t>デバイス固有メソッド実行。</t>
-        </is>
-      </c>
-      <c r="P80" s="28" t="n"/>
-      <c r="Q80" s="28" t="n"/>
-      <c r="R80" s="29" t="n"/>
-      <c r="S80" s="32" t="inlineStr">
-        <is>
-          <t>対象デバイスのメソッド実行処理を呼ぶ。</t>
-        </is>
-      </c>
-      <c r="T80" s="28" t="n"/>
-      <c r="U80" s="28" t="n"/>
-      <c r="V80" s="29" t="n"/>
-      <c r="W80" s="32" t="inlineStr">
-        <is>
-          <t>メソッドID未指定または未登録デバイス時は失敗応答。</t>
-        </is>
-      </c>
-      <c r="X80" s="28" t="n"/>
-      <c r="Y80" s="28" t="n"/>
-      <c r="Z80" s="30" t="n"/>
-    </row>
-    <row r="81" ht="72" customHeight="1">
-      <c r="B81" s="27" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C81" s="16" t="inlineStr">
-        <is>
-          <t>Host停止要求（Kill）</t>
-        </is>
-      </c>
-      <c r="D81" s="28" t="n"/>
-      <c r="E81" s="28" t="n"/>
-      <c r="F81" s="29" t="n"/>
-      <c r="G81" s="16" t="inlineStr">
-        <is>
-          <t>デバイスコネクタ制御</t>
-        </is>
-      </c>
-      <c r="H81" s="29" t="n"/>
-      <c r="I81" s="16" t="inlineStr">
-        <is>
-          <t>任意</t>
-        </is>
-      </c>
-      <c r="J81" s="28" t="n"/>
-      <c r="K81" s="29" t="n"/>
-      <c r="L81" s="16" t="inlineStr">
-        <is>
-          <t>任意</t>
-        </is>
-      </c>
-      <c r="M81" s="28" t="n"/>
-      <c r="N81" s="29" t="n"/>
-      <c r="O81" s="16" t="inlineStr">
-        <is>
-          <t>Host停止要求。</t>
-        </is>
-      </c>
-      <c r="P81" s="28" t="n"/>
-      <c r="Q81" s="28" t="n"/>
-      <c r="R81" s="29" t="n"/>
-      <c r="S81" s="16" t="inlineStr">
-        <is>
-          <t>停止要求受付メッセージ（Kill accepted）の書込完了後、500ミリ秒待機して停止処理へ進む。</t>
-        </is>
-      </c>
-      <c r="T81" s="28" t="n"/>
-      <c r="U81" s="28" t="n"/>
-      <c r="V81" s="29" t="n"/>
-      <c r="W81" s="16" t="inlineStr">
-        <is>
-          <t>停止中例外は受付応答後にデバイスコネクタ側ログへ出力する。</t>
-        </is>
-      </c>
-      <c r="X81" s="28" t="n"/>
-      <c r="Y81" s="28" t="n"/>
-      <c r="Z81" s="30" t="n"/>
-    </row>
-    <row r="82" ht="90" customHeight="1">
-      <c r="B82" s="31" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C82" s="32" t="inlineStr">
-        <is>
-          <t>Host再起動要求（ReStart）</t>
-        </is>
-      </c>
-      <c r="D82" s="28" t="n"/>
-      <c r="E82" s="28" t="n"/>
-      <c r="F82" s="29" t="n"/>
-      <c r="G82" s="32" t="inlineStr">
-        <is>
-          <t>デバイスコネクタ制御</t>
-        </is>
-      </c>
-      <c r="H82" s="29" t="n"/>
-      <c r="I82" s="32" t="inlineStr">
-        <is>
-          <t>任意</t>
-        </is>
-      </c>
-      <c r="J82" s="28" t="n"/>
-      <c r="K82" s="29" t="n"/>
-      <c r="L82" s="32" t="inlineStr">
-        <is>
-          <t>任意</t>
-        </is>
-      </c>
-      <c r="M82" s="28" t="n"/>
-      <c r="N82" s="29" t="n"/>
-      <c r="O82" s="32" t="inlineStr">
-        <is>
-          <t>Host再起動要求。</t>
-        </is>
-      </c>
-      <c r="P82" s="28" t="n"/>
-      <c r="Q82" s="28" t="n"/>
-      <c r="R82" s="29" t="n"/>
-      <c r="S82" s="32" t="inlineStr">
-        <is>
-          <t>再起動要求受付メッセージ（Restart accepted）の書込完了後、500ミリ秒待機して停止・再起動する。</t>
-        </is>
-      </c>
-      <c r="T82" s="28" t="n"/>
-      <c r="U82" s="28" t="n"/>
-      <c r="V82" s="29" t="n"/>
-      <c r="W82" s="32" t="inlineStr">
-        <is>
-          <t>再起動中例外は受付応答後にデバイスコネクタ側ログへ出力する。</t>
-        </is>
-      </c>
-      <c r="X82" s="28" t="n"/>
-      <c r="Y82" s="28" t="n"/>
-      <c r="Z82" s="30" t="n"/>
-    </row>
-    <row r="83" ht="72" customHeight="1">
-      <c r="B83" s="33" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="C83" s="36" t="inlineStr">
-        <is>
-          <t>デバイスコネクタ稼働確認（HealthCheck）</t>
-        </is>
-      </c>
-      <c r="D83" s="34" t="n"/>
-      <c r="E83" s="34" t="n"/>
-      <c r="F83" s="35" t="n"/>
-      <c r="G83" s="36" t="inlineStr">
-        <is>
-          <t>デバイスコネクタ制御</t>
-        </is>
-      </c>
-      <c r="H83" s="35" t="n"/>
-      <c r="I83" s="36" t="inlineStr">
-        <is>
-          <t>任意</t>
-        </is>
-      </c>
-      <c r="J83" s="34" t="n"/>
-      <c r="K83" s="35" t="n"/>
-      <c r="L83" s="36" t="inlineStr">
-        <is>
-          <t>任意</t>
-        </is>
-      </c>
-      <c r="M83" s="34" t="n"/>
-      <c r="N83" s="35" t="n"/>
-      <c r="O83" s="36" t="inlineStr">
+      <c r="M72" s="34" t="n"/>
+      <c r="N72" s="35" t="n"/>
+      <c r="O72" s="36" t="inlineStr">
         <is>
           <t>プロセス起動後の通信機能とデバイス管理の準備状態を確認する。</t>
         </is>
       </c>
-      <c r="P83" s="34" t="n"/>
-      <c r="Q83" s="34" t="n"/>
-      <c r="R83" s="35" t="n"/>
-      <c r="S83" s="36" t="inlineStr">
+      <c r="P72" s="34" t="n"/>
+      <c r="Q72" s="34" t="n"/>
+      <c r="R72" s="35" t="n"/>
+      <c r="S72" s="36" t="inlineStr">
         <is>
           <t>準備完了時は稼働中（Ready）を返す。</t>
         </is>
       </c>
-      <c r="T83" s="34" t="n"/>
-      <c r="U83" s="34" t="n"/>
-      <c r="V83" s="35" t="n"/>
-      <c r="W83" s="36" t="inlineStr">
+      <c r="T72" s="34" t="n"/>
+      <c r="U72" s="34" t="n"/>
+      <c r="V72" s="35" t="n"/>
+      <c r="W72" s="36" t="inlineStr">
         <is>
           <t>準備未完了時は成功フラグ（Success）=false、結果コード（ResultCode）=-1を返す。</t>
         </is>
       </c>
-      <c r="X83" s="34" t="n"/>
-      <c r="Y83" s="34" t="n"/>
-      <c r="Z83" s="37" t="n"/>
+      <c r="X72" s="34" t="n"/>
+      <c r="Y72" s="34" t="n"/>
+      <c r="Z72" s="37" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="264">
-    <mergeCell ref="O49:T49"/>
-    <mergeCell ref="H53:I53"/>
-    <mergeCell ref="G81:H81"/>
-    <mergeCell ref="O79:R79"/>
+  <mergeCells count="243">
+    <mergeCell ref="C52:F52"/>
+    <mergeCell ref="I72:K72"/>
     <mergeCell ref="F25:G25"/>
-    <mergeCell ref="Q70:Z70"/>
-    <mergeCell ref="B40:Z40"/>
+    <mergeCell ref="C40:E40"/>
+    <mergeCell ref="W70:Z70"/>
     <mergeCell ref="G71:H71"/>
-    <mergeCell ref="L83:N83"/>
-    <mergeCell ref="U53:Z53"/>
-    <mergeCell ref="C81:F81"/>
-    <mergeCell ref="C51:E51"/>
-    <mergeCell ref="O50:T50"/>
-    <mergeCell ref="L76:N76"/>
-    <mergeCell ref="S79:V79"/>
-    <mergeCell ref="C78:F78"/>
+    <mergeCell ref="C72:F72"/>
+    <mergeCell ref="B49:Z49"/>
+    <mergeCell ref="O67:R67"/>
+    <mergeCell ref="O72:R72"/>
+    <mergeCell ref="B64:Z64"/>
+    <mergeCell ref="H39:I39"/>
     <mergeCell ref="T27:Z27"/>
     <mergeCell ref="C23:E23"/>
     <mergeCell ref="V10:Z10"/>
-    <mergeCell ref="O78:R78"/>
     <mergeCell ref="W1:X1"/>
-    <mergeCell ref="B41:Z41"/>
+    <mergeCell ref="Q56:Z56"/>
+    <mergeCell ref="G57:H57"/>
     <mergeCell ref="Y1:Z1"/>
-    <mergeCell ref="K70:P70"/>
+    <mergeCell ref="L69:N69"/>
+    <mergeCell ref="B35:Z35"/>
+    <mergeCell ref="T24:Z24"/>
+    <mergeCell ref="U39:Z39"/>
+    <mergeCell ref="B50:Z50"/>
     <mergeCell ref="G66:H66"/>
-    <mergeCell ref="T24:Z24"/>
-    <mergeCell ref="O52:T52"/>
-    <mergeCell ref="J49:N49"/>
-    <mergeCell ref="I66:J66"/>
-    <mergeCell ref="I71:J71"/>
-    <mergeCell ref="I79:K79"/>
-    <mergeCell ref="H52:I52"/>
-    <mergeCell ref="S81:V81"/>
-    <mergeCell ref="I82:K82"/>
+    <mergeCell ref="S72:V72"/>
+    <mergeCell ref="I58:J58"/>
     <mergeCell ref="V9:Z9"/>
     <mergeCell ref="R12:S12"/>
-    <mergeCell ref="L34:Z34"/>
     <mergeCell ref="T12:U12"/>
     <mergeCell ref="I10:K10"/>
-    <mergeCell ref="C64:F64"/>
-    <mergeCell ref="C79:F79"/>
-    <mergeCell ref="K65:P65"/>
+    <mergeCell ref="S71:V71"/>
+    <mergeCell ref="U38:Z38"/>
+    <mergeCell ref="G68:H68"/>
     <mergeCell ref="P22:S22"/>
-    <mergeCell ref="G68:H68"/>
+    <mergeCell ref="W65:Z65"/>
     <mergeCell ref="F23:G23"/>
+    <mergeCell ref="O37:T37"/>
     <mergeCell ref="L12:O12"/>
-    <mergeCell ref="C49:E49"/>
+    <mergeCell ref="G58:H58"/>
     <mergeCell ref="V11:Z11"/>
-    <mergeCell ref="L36:Z36"/>
-    <mergeCell ref="C63:F63"/>
+    <mergeCell ref="C54:F54"/>
+    <mergeCell ref="H37:I37"/>
+    <mergeCell ref="I65:K65"/>
+    <mergeCell ref="I52:J52"/>
+    <mergeCell ref="Q58:Z58"/>
     <mergeCell ref="T25:Z25"/>
     <mergeCell ref="E10:H10"/>
-    <mergeCell ref="Q67:Z67"/>
-    <mergeCell ref="J50:N50"/>
+    <mergeCell ref="U40:Z40"/>
+    <mergeCell ref="C42:E42"/>
     <mergeCell ref="E2:G3"/>
+    <mergeCell ref="C56:F56"/>
     <mergeCell ref="J28:O28"/>
+    <mergeCell ref="Q60:Z60"/>
     <mergeCell ref="Y2:Z3"/>
-    <mergeCell ref="B61:Z61"/>
-    <mergeCell ref="Q69:Z69"/>
-    <mergeCell ref="B36:I36"/>
     <mergeCell ref="H23:I23"/>
-    <mergeCell ref="J52:N52"/>
-    <mergeCell ref="L37:Z37"/>
-    <mergeCell ref="I69:J69"/>
     <mergeCell ref="C25:E25"/>
     <mergeCell ref="V12:Z12"/>
-    <mergeCell ref="J48:N48"/>
-    <mergeCell ref="G77:H77"/>
+    <mergeCell ref="J39:N39"/>
+    <mergeCell ref="Q59:Z59"/>
+    <mergeCell ref="G59:H59"/>
+    <mergeCell ref="L71:N71"/>
     <mergeCell ref="T22:Z22"/>
-    <mergeCell ref="S83:V83"/>
-    <mergeCell ref="W77:Z77"/>
+    <mergeCell ref="O41:T41"/>
     <mergeCell ref="C22:E22"/>
     <mergeCell ref="P10:Q10"/>
+    <mergeCell ref="J38:N38"/>
     <mergeCell ref="R10:S10"/>
-    <mergeCell ref="G67:H67"/>
+    <mergeCell ref="H41:I41"/>
     <mergeCell ref="C67:F67"/>
     <mergeCell ref="I12:K12"/>
-    <mergeCell ref="H50:I50"/>
-    <mergeCell ref="O82:R82"/>
-    <mergeCell ref="S76:V76"/>
-    <mergeCell ref="K67:P67"/>
+    <mergeCell ref="G67:H67"/>
+    <mergeCell ref="G70:H70"/>
     <mergeCell ref="P24:S24"/>
     <mergeCell ref="B6:Z6"/>
     <mergeCell ref="T28:Z28"/>
-    <mergeCell ref="G70:H70"/>
-    <mergeCell ref="I70:J70"/>
+    <mergeCell ref="W67:Z67"/>
     <mergeCell ref="P9:Q9"/>
-    <mergeCell ref="B55:Z55"/>
+    <mergeCell ref="K59:P59"/>
     <mergeCell ref="H2:Q3"/>
     <mergeCell ref="H25:I25"/>
-    <mergeCell ref="L38:Z38"/>
-    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="J40:N40"/>
+    <mergeCell ref="I57:J57"/>
     <mergeCell ref="T10:U10"/>
-    <mergeCell ref="C52:E52"/>
+    <mergeCell ref="O40:T40"/>
+    <mergeCell ref="I54:J54"/>
     <mergeCell ref="C69:F69"/>
-    <mergeCell ref="C83:F83"/>
+    <mergeCell ref="U42:Z42"/>
     <mergeCell ref="E12:H12"/>
     <mergeCell ref="P26:S26"/>
-    <mergeCell ref="H49:I49"/>
-    <mergeCell ref="C48:E48"/>
-    <mergeCell ref="W78:Z78"/>
+    <mergeCell ref="C39:E39"/>
+    <mergeCell ref="W69:Z69"/>
+    <mergeCell ref="O42:T42"/>
+    <mergeCell ref="O68:R68"/>
     <mergeCell ref="P11:Q11"/>
     <mergeCell ref="B32:Z32"/>
-    <mergeCell ref="U52:Z52"/>
+    <mergeCell ref="F42:G42"/>
     <mergeCell ref="T9:U9"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="I78:K78"/>
+    <mergeCell ref="K53:P53"/>
+    <mergeCell ref="I56:J56"/>
     <mergeCell ref="P25:S25"/>
-    <mergeCell ref="Q71:Z71"/>
+    <mergeCell ref="C38:E38"/>
     <mergeCell ref="B16:Z16"/>
     <mergeCell ref="A1:D3"/>
-    <mergeCell ref="W80:Z80"/>
     <mergeCell ref="T11:U11"/>
+    <mergeCell ref="S70:V70"/>
     <mergeCell ref="G65:H65"/>
     <mergeCell ref="F28:G28"/>
-    <mergeCell ref="L77:N77"/>
     <mergeCell ref="H28:I28"/>
     <mergeCell ref="B18:Z18"/>
-    <mergeCell ref="B43:Z43"/>
-    <mergeCell ref="I81:K81"/>
     <mergeCell ref="C24:E24"/>
-    <mergeCell ref="Q63:Z63"/>
-    <mergeCell ref="F48:G48"/>
-    <mergeCell ref="B33:I33"/>
-    <mergeCell ref="H48:I48"/>
-    <mergeCell ref="O53:T53"/>
-    <mergeCell ref="G76:H76"/>
-    <mergeCell ref="B60:Z60"/>
-    <mergeCell ref="B57:Z57"/>
+    <mergeCell ref="F39:G39"/>
+    <mergeCell ref="L67:N67"/>
     <mergeCell ref="C26:E26"/>
-    <mergeCell ref="K64:P64"/>
+    <mergeCell ref="J42:N42"/>
+    <mergeCell ref="I59:J59"/>
+    <mergeCell ref="G60:H60"/>
     <mergeCell ref="C71:F71"/>
-    <mergeCell ref="L78:N78"/>
-    <mergeCell ref="B35:I35"/>
+    <mergeCell ref="I60:J60"/>
+    <mergeCell ref="B44:Z44"/>
     <mergeCell ref="R1:S1"/>
     <mergeCell ref="E1:G1"/>
-    <mergeCell ref="U48:Z48"/>
-    <mergeCell ref="C76:F76"/>
-    <mergeCell ref="I76:K76"/>
-    <mergeCell ref="C50:E50"/>
+    <mergeCell ref="O71:R71"/>
     <mergeCell ref="B19:Z19"/>
-    <mergeCell ref="K63:P63"/>
-    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="B34:Z34"/>
+    <mergeCell ref="H38:I38"/>
+    <mergeCell ref="S65:V65"/>
+    <mergeCell ref="I66:K66"/>
     <mergeCell ref="J27:O27"/>
-    <mergeCell ref="C82:F82"/>
-    <mergeCell ref="W82:Z82"/>
-    <mergeCell ref="O80:R80"/>
+    <mergeCell ref="U41:Z41"/>
+    <mergeCell ref="K56:P56"/>
+    <mergeCell ref="J37:N37"/>
+    <mergeCell ref="C57:F57"/>
+    <mergeCell ref="H40:I40"/>
     <mergeCell ref="B30:Z30"/>
+    <mergeCell ref="K58:P58"/>
     <mergeCell ref="C66:F66"/>
+    <mergeCell ref="K52:P52"/>
+    <mergeCell ref="I68:K68"/>
+    <mergeCell ref="C53:F53"/>
     <mergeCell ref="B20:Z20"/>
     <mergeCell ref="T1:V1"/>
-    <mergeCell ref="L79:N79"/>
-    <mergeCell ref="J53:N53"/>
-    <mergeCell ref="C77:F77"/>
+    <mergeCell ref="O66:R66"/>
+    <mergeCell ref="I67:K67"/>
     <mergeCell ref="J22:O22"/>
     <mergeCell ref="C68:F68"/>
     <mergeCell ref="R2:S3"/>
-    <mergeCell ref="O77:R77"/>
-    <mergeCell ref="F50:G50"/>
+    <mergeCell ref="W68:Z68"/>
     <mergeCell ref="G69:H69"/>
-    <mergeCell ref="B75:Z75"/>
     <mergeCell ref="H1:Q1"/>
-    <mergeCell ref="L81:N81"/>
-    <mergeCell ref="G78:H78"/>
+    <mergeCell ref="C58:F58"/>
+    <mergeCell ref="B62:Z62"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="J35:K35"/>
     <mergeCell ref="C28:E28"/>
-    <mergeCell ref="B59:Z59"/>
-    <mergeCell ref="O83:R83"/>
+    <mergeCell ref="L65:N65"/>
+    <mergeCell ref="C37:E37"/>
     <mergeCell ref="B46:Z46"/>
-    <mergeCell ref="B38:I38"/>
-    <mergeCell ref="S77:V77"/>
-    <mergeCell ref="G80:H80"/>
+    <mergeCell ref="Q54:Z54"/>
     <mergeCell ref="F22:G22"/>
     <mergeCell ref="J23:O23"/>
+    <mergeCell ref="J41:N41"/>
+    <mergeCell ref="H22:I22"/>
+    <mergeCell ref="Q55:Z55"/>
     <mergeCell ref="C65:F65"/>
-    <mergeCell ref="H22:I22"/>
-    <mergeCell ref="K69:P69"/>
-    <mergeCell ref="Q64:Z64"/>
-    <mergeCell ref="G64:H64"/>
-    <mergeCell ref="G79:H79"/>
-    <mergeCell ref="I64:J64"/>
-    <mergeCell ref="L82:N82"/>
+    <mergeCell ref="S67:V67"/>
+    <mergeCell ref="B48:Z48"/>
+    <mergeCell ref="O65:R65"/>
     <mergeCell ref="P27:S27"/>
-    <mergeCell ref="I80:K80"/>
     <mergeCell ref="T2:V3"/>
-    <mergeCell ref="C80:F80"/>
-    <mergeCell ref="W79:Z79"/>
     <mergeCell ref="P12:Q12"/>
-    <mergeCell ref="G63:H63"/>
-    <mergeCell ref="I63:J63"/>
-    <mergeCell ref="F49:G49"/>
-    <mergeCell ref="S78:V78"/>
+    <mergeCell ref="G54:H54"/>
+    <mergeCell ref="L66:N66"/>
+    <mergeCell ref="H42:I42"/>
+    <mergeCell ref="S69:V69"/>
+    <mergeCell ref="I70:K70"/>
+    <mergeCell ref="K54:P54"/>
     <mergeCell ref="B8:Z8"/>
     <mergeCell ref="T26:Z26"/>
+    <mergeCell ref="W72:Z72"/>
+    <mergeCell ref="K55:P55"/>
     <mergeCell ref="L10:O10"/>
     <mergeCell ref="R9:S9"/>
-    <mergeCell ref="B73:Z73"/>
-    <mergeCell ref="W81:Z81"/>
+    <mergeCell ref="C60:F60"/>
+    <mergeCell ref="G56:H56"/>
+    <mergeCell ref="L68:N68"/>
     <mergeCell ref="J24:O24"/>
-    <mergeCell ref="I65:J65"/>
     <mergeCell ref="T23:Z23"/>
     <mergeCell ref="C70:F70"/>
-    <mergeCell ref="S80:V80"/>
-    <mergeCell ref="Q65:Z65"/>
     <mergeCell ref="P28:S28"/>
+    <mergeCell ref="C41:E41"/>
+    <mergeCell ref="G52:H52"/>
     <mergeCell ref="L9:O9"/>
+    <mergeCell ref="W71:Z71"/>
+    <mergeCell ref="O70:R70"/>
     <mergeCell ref="R11:S11"/>
-    <mergeCell ref="L33:Z33"/>
-    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="G72:H72"/>
+    <mergeCell ref="I71:K71"/>
+    <mergeCell ref="U37:Z37"/>
     <mergeCell ref="J26:O26"/>
     <mergeCell ref="W2:X3"/>
-    <mergeCell ref="O81:R81"/>
-    <mergeCell ref="O76:R76"/>
+    <mergeCell ref="F40:G40"/>
     <mergeCell ref="L11:O11"/>
-    <mergeCell ref="L35:Z35"/>
-    <mergeCell ref="G82:H82"/>
     <mergeCell ref="F24:G24"/>
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="J25:O25"/>
     <mergeCell ref="C27:E27"/>
-    <mergeCell ref="K71:P71"/>
-    <mergeCell ref="O51:T51"/>
+    <mergeCell ref="Q57:Z57"/>
     <mergeCell ref="B5:Z5"/>
-    <mergeCell ref="Q66:Z66"/>
-    <mergeCell ref="F51:G51"/>
-    <mergeCell ref="B45:Z45"/>
-    <mergeCell ref="H51:I51"/>
-    <mergeCell ref="I83:K83"/>
+    <mergeCell ref="Q53:Z53"/>
+    <mergeCell ref="G53:H53"/>
+    <mergeCell ref="I53:J53"/>
     <mergeCell ref="C9:D9"/>
-    <mergeCell ref="O48:T48"/>
     <mergeCell ref="F26:G26"/>
-    <mergeCell ref="Q68:Z68"/>
-    <mergeCell ref="G83:H83"/>
-    <mergeCell ref="L80:N80"/>
-    <mergeCell ref="U51:Z51"/>
-    <mergeCell ref="I68:J68"/>
-    <mergeCell ref="C53:E53"/>
+    <mergeCell ref="F41:G41"/>
+    <mergeCell ref="L72:N72"/>
+    <mergeCell ref="O38:T38"/>
+    <mergeCell ref="F38:G38"/>
+    <mergeCell ref="K57:P57"/>
+    <mergeCell ref="Q52:Z52"/>
     <mergeCell ref="C11:D11"/>
-    <mergeCell ref="K66:P66"/>
-    <mergeCell ref="B34:I34"/>
+    <mergeCell ref="I55:J55"/>
     <mergeCell ref="I9:K9"/>
-    <mergeCell ref="W83:Z83"/>
-    <mergeCell ref="I67:J67"/>
-    <mergeCell ref="B37:I37"/>
-    <mergeCell ref="U50:Z50"/>
-    <mergeCell ref="S82:V82"/>
+    <mergeCell ref="I69:K69"/>
+    <mergeCell ref="L70:N70"/>
     <mergeCell ref="F27:G27"/>
-    <mergeCell ref="W76:Z76"/>
+    <mergeCell ref="C55:F55"/>
     <mergeCell ref="H27:I27"/>
-    <mergeCell ref="F52:G52"/>
-    <mergeCell ref="K68:P68"/>
-    <mergeCell ref="I77:K77"/>
+    <mergeCell ref="G55:H55"/>
+    <mergeCell ref="S66:V66"/>
     <mergeCell ref="I11:K11"/>
+    <mergeCell ref="F37:G37"/>
     <mergeCell ref="E9:H9"/>
     <mergeCell ref="P23:S23"/>
+    <mergeCell ref="W66:Z66"/>
+    <mergeCell ref="O69:R69"/>
     <mergeCell ref="H24:I24"/>
     <mergeCell ref="B14:Z14"/>
-    <mergeCell ref="J51:N51"/>
-    <mergeCell ref="U49:Z49"/>
-    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="C59:F59"/>
+    <mergeCell ref="S68:V68"/>
+    <mergeCell ref="O39:T39"/>
     <mergeCell ref="E11:H11"/>
-    <mergeCell ref="F53:G53"/>
+    <mergeCell ref="K60:P60"/>
     <mergeCell ref="H26:I26"/>
   </mergeCells>
   <printOptions gridLines="0"/>
@@ -8087,7 +7811,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Z50"/>
+  <dimension ref="A1:Z51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -8221,7 +7945,7 @@
       <c r="X2" s="15" t="n"/>
       <c r="Y2" s="17" t="inlineStr">
         <is>
-          <t>2026/07/13</t>
+          <t>2026/07/14</t>
         </is>
       </c>
       <c r="Z2" s="18" t="n"/>
@@ -8262,7 +7986,7 @@
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="B6" s="42" t="inlineStr">
+      <c r="B6" s="44" t="inlineStr">
         <is>
           <t>■9.1 設定責務</t>
         </is>
@@ -8355,16 +8079,16 @@
       <c r="Z9" s="30" t="n"/>
     </row>
     <row r="10" ht="36" customHeight="1">
-      <c r="B10" s="43" t="inlineStr">
+      <c r="B10" s="38" t="inlineStr">
         <is>
           <t>デバイスコネクタ側設定</t>
         </is>
       </c>
       <c r="C10" s="34" t="n"/>
       <c r="D10" s="35" t="n"/>
-      <c r="E10" s="44" t="inlineStr">
-        <is>
-          <t>起動する個別デバイス実装、その識別情報、および実装パラメータ。</t>
+      <c r="E10" s="39" t="inlineStr">
+        <is>
+          <t>起動するホスト内部実装、その識別情報、および実装パラメータ。</t>
         </is>
       </c>
       <c r="F10" s="34" t="n"/>
@@ -8376,7 +8100,7 @@
       <c r="L10" s="34" t="n"/>
       <c r="M10" s="34" t="n"/>
       <c r="N10" s="35" t="n"/>
-      <c r="O10" s="44" t="inlineStr">
+      <c r="O10" s="39" t="inlineStr">
         <is>
           <t>デバイスコネクタ / デバイス管理</t>
         </is>
@@ -8385,7 +8109,7 @@
       <c r="Q10" s="34" t="n"/>
       <c r="R10" s="34" t="n"/>
       <c r="S10" s="35" t="n"/>
-      <c r="T10" s="44" t="inlineStr">
+      <c r="T10" s="39" t="inlineStr">
         <is>
           <t>必須設定を使用できない場合は通信受付を停止し、デバイスコネクタを異常終了する。</t>
         </is>
@@ -8398,7 +8122,7 @@
       <c r="Z10" s="37" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="B12" s="42" t="inlineStr">
+      <c r="B12" s="44" t="inlineStr">
         <is>
           <t>■9.2 設定ファイル一覧</t>
         </is>
@@ -8479,7 +8203,7 @@
       <c r="J15" s="29" t="n"/>
       <c r="K15" s="16" t="inlineStr">
         <is>
-          <t>端末で使用するデバイス候補、有効デバイス、ストラテジー、名前付きパイプ設定を定義する。</t>
+          <t>端末で使用するデバイス候補、有効デバイス、アプリ側の制御方式、および名前付きパイプ設定を定義する。</t>
         </is>
       </c>
       <c r="L15" s="28" t="n"/>
@@ -8507,12 +8231,12 @@
       <c r="Z15" s="30" t="n"/>
     </row>
     <row r="16" ht="54" customHeight="1">
-      <c r="B16" s="43" t="inlineStr">
+      <c r="B16" s="38" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C16" s="44" t="inlineStr">
+      <c r="C16" s="39" t="inlineStr">
         <is>
           <t>host_device_config.json</t>
         </is>
@@ -8520,7 +8244,7 @@
       <c r="D16" s="34" t="n"/>
       <c r="E16" s="34" t="n"/>
       <c r="F16" s="35" t="n"/>
-      <c r="G16" s="44" t="inlineStr">
+      <c r="G16" s="39" t="inlineStr">
         <is>
           <t>デバイスコネクタ側</t>
         </is>
@@ -8528,9 +8252,9 @@
       <c r="H16" s="34" t="n"/>
       <c r="I16" s="34" t="n"/>
       <c r="J16" s="35" t="n"/>
-      <c r="K16" s="44" t="inlineStr">
-        <is>
-          <t>デバイスコネクタが生成、保持する既存デバイス実装を定義する。</t>
+      <c r="K16" s="39" t="inlineStr">
+        <is>
+          <t>デバイスコネクタが生成、保持するホスト内部実装を定義する。</t>
         </is>
       </c>
       <c r="L16" s="34" t="n"/>
@@ -8538,14 +8262,14 @@
       <c r="N16" s="34" t="n"/>
       <c r="O16" s="34" t="n"/>
       <c r="P16" s="35" t="n"/>
-      <c r="Q16" s="44" t="inlineStr">
+      <c r="Q16" s="39" t="inlineStr">
         <is>
           <t>デバイスコネクタ本体開始時</t>
         </is>
       </c>
       <c r="R16" s="34" t="n"/>
       <c r="S16" s="35" t="n"/>
-      <c r="T16" s="44" t="inlineStr">
+      <c r="T16" s="39" t="inlineStr">
         <is>
           <t>デバイスコネクタ実行フォルダを基準に読む。必須設定に異常がある場合は通信受付を終了し、プロセスを異常終了する。</t>
         </is>
@@ -8558,7 +8282,7 @@
       <c r="Z16" s="37" t="n"/>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="B18" s="42" t="inlineStr">
+      <c r="B18" s="44" t="inlineStr">
         <is>
           <t>■9.3 設定項目</t>
         </is>
@@ -8752,7 +8476,7 @@
       <c r="I23" s="29" t="n"/>
       <c r="J23" s="16" t="inlineStr">
         <is>
-          <t>デバイスコネクタが起動するデバイス実装一覧。</t>
+          <t>デバイスコネクタが起動するホスト内部実装一覧。</t>
         </is>
       </c>
       <c r="K23" s="28" t="n"/>
@@ -9335,7 +9059,7 @@
       <c r="Z33" s="37" t="n"/>
     </row>
     <row r="35" ht="18" customHeight="1">
-      <c r="B35" s="42" t="inlineStr">
+      <c r="B35" s="44" t="inlineStr">
         <is>
           <t>■9.4 設定ファイル対応関係</t>
         </is>
@@ -9431,7 +9155,7 @@
       <c r="F39" s="29" t="n"/>
       <c r="G39" s="32" t="inlineStr">
         <is>
-          <t>端末で使用する制御方式を選ぶ。</t>
+          <t>端末で使用するアプリ側の制御方式を選ぶ。</t>
         </is>
       </c>
       <c r="H39" s="28" t="n"/>
@@ -9445,7 +9169,7 @@
       <c r="P39" s="29" t="n"/>
       <c r="Q39" s="32" t="inlineStr">
         <is>
-          <t>デバイスコネクタで起動する既存デバイス実装を選ぶ。</t>
+          <t>デバイスコネクタ内部で呼び出すホスト内部実装を選ぶ。</t>
         </is>
       </c>
       <c r="R39" s="28" t="n"/>
@@ -9461,7 +9185,7 @@
     <row r="40" ht="36" customHeight="1">
       <c r="B40" s="27" t="inlineStr">
         <is>
-          <t>デバイスコネクタ連携</t>
+          <t>実装の位置付け</t>
         </is>
       </c>
       <c r="C40" s="28" t="n"/>
@@ -9470,7 +9194,7 @@
       <c r="F40" s="29" t="n"/>
       <c r="G40" s="16" t="inlineStr">
         <is>
-          <t>コマンド通信用／イベント通知用パイプ名、接続タイムアウト、および再接続条件を持つ。</t>
+          <t>デバイス制御層のストラテジークラスを選択する。</t>
         </is>
       </c>
       <c r="H40" s="28" t="n"/>
@@ -9484,7 +9208,7 @@
       <c r="P40" s="29" t="n"/>
       <c r="Q40" s="16" t="inlineStr">
         <is>
-          <t>デバイスコネクタ内デバイス実装を持つ。</t>
+          <t>アプリ側のストラテジークラスではなく、既存デバイス資源を呼び出すホスト内部実装を選択する。</t>
         </is>
       </c>
       <c r="R40" s="28" t="n"/>
@@ -9500,7 +9224,7 @@
     <row r="41" ht="36" customHeight="1">
       <c r="B41" s="31" t="inlineStr">
         <is>
-          <t>参照タイミング</t>
+          <t>デバイスコネクタ連携</t>
         </is>
       </c>
       <c r="C41" s="28" t="n"/>
@@ -9509,7 +9233,7 @@
       <c r="F41" s="29" t="n"/>
       <c r="G41" s="32" t="inlineStr">
         <is>
-          <t>アプリ起動時に読み込み、デバイス操作時は読み込み済み設定を参照する。</t>
+          <t>コマンド通信用／イベント通知用パイプ名、接続タイムアウト、および再接続条件を持つ。</t>
         </is>
       </c>
       <c r="H41" s="28" t="n"/>
@@ -9523,7 +9247,7 @@
       <c r="P41" s="29" t="n"/>
       <c r="Q41" s="32" t="inlineStr">
         <is>
-          <t>デバイスコネクタ起動時。</t>
+          <t>デバイスコネクタ内のホスト内部実装を持つ。</t>
         </is>
       </c>
       <c r="R41" s="28" t="n"/>
@@ -9539,7 +9263,7 @@
     <row r="42" ht="36" customHeight="1">
       <c r="B42" s="27" t="inlineStr">
         <is>
-          <t>更新方法</t>
+          <t>参照タイミング</t>
         </is>
       </c>
       <c r="C42" s="28" t="n"/>
@@ -9548,7 +9272,7 @@
       <c r="F42" s="29" t="n"/>
       <c r="G42" s="16" t="inlineStr">
         <is>
-          <t>運用設定をアプリデータ領域へ保存し、デバイス制御を再初期化する。</t>
+          <t>アプリ起動時に読み込み、デバイス操作時は読み込み済み設定を参照する。</t>
         </is>
       </c>
       <c r="H42" s="28" t="n"/>
@@ -9562,7 +9286,7 @@
       <c r="P42" s="29" t="n"/>
       <c r="Q42" s="16" t="inlineStr">
         <is>
-          <t>配置ファイルを更新し、デバイスコネクタプロセスを再起動する。</t>
+          <t>デバイスコネクタ起動時。</t>
         </is>
       </c>
       <c r="R42" s="28" t="n"/>
@@ -9575,205 +9299,185 @@
       <c r="Y42" s="28" t="n"/>
       <c r="Z42" s="30" t="n"/>
     </row>
-    <row r="43" ht="24" customHeight="1">
-      <c r="B43" s="43" t="inlineStr">
+    <row r="43" ht="36" customHeight="1">
+      <c r="B43" s="31" t="inlineStr">
+        <is>
+          <t>更新方法</t>
+        </is>
+      </c>
+      <c r="C43" s="28" t="n"/>
+      <c r="D43" s="28" t="n"/>
+      <c r="E43" s="28" t="n"/>
+      <c r="F43" s="29" t="n"/>
+      <c r="G43" s="32" t="inlineStr">
+        <is>
+          <t>運用設定をアプリデータ領域へ保存し、デバイス制御を再初期化する。</t>
+        </is>
+      </c>
+      <c r="H43" s="28" t="n"/>
+      <c r="I43" s="28" t="n"/>
+      <c r="J43" s="28" t="n"/>
+      <c r="K43" s="28" t="n"/>
+      <c r="L43" s="28" t="n"/>
+      <c r="M43" s="28" t="n"/>
+      <c r="N43" s="28" t="n"/>
+      <c r="O43" s="28" t="n"/>
+      <c r="P43" s="29" t="n"/>
+      <c r="Q43" s="32" t="inlineStr">
+        <is>
+          <t>配置ファイルを更新し、デバイスコネクタプロセスを再起動する。</t>
+        </is>
+      </c>
+      <c r="R43" s="28" t="n"/>
+      <c r="S43" s="28" t="n"/>
+      <c r="T43" s="28" t="n"/>
+      <c r="U43" s="28" t="n"/>
+      <c r="V43" s="28" t="n"/>
+      <c r="W43" s="28" t="n"/>
+      <c r="X43" s="28" t="n"/>
+      <c r="Y43" s="28" t="n"/>
+      <c r="Z43" s="30" t="n"/>
+    </row>
+    <row r="44" ht="24" customHeight="1">
+      <c r="B44" s="33" t="inlineStr">
         <is>
           <t>置換関係</t>
         </is>
       </c>
-      <c r="C43" s="34" t="n"/>
-      <c r="D43" s="34" t="n"/>
-      <c r="E43" s="34" t="n"/>
-      <c r="F43" s="35" t="n"/>
-      <c r="G43" s="44" t="inlineStr">
+      <c r="C44" s="34" t="n"/>
+      <c r="D44" s="34" t="n"/>
+      <c r="E44" s="34" t="n"/>
+      <c r="F44" s="35" t="n"/>
+      <c r="G44" s="36" t="inlineStr">
         <is>
           <t>デバイスコネクタ設定を置き換えない。</t>
         </is>
       </c>
-      <c r="H43" s="34" t="n"/>
-      <c r="I43" s="34" t="n"/>
-      <c r="J43" s="34" t="n"/>
-      <c r="K43" s="34" t="n"/>
-      <c r="L43" s="34" t="n"/>
-      <c r="M43" s="34" t="n"/>
-      <c r="N43" s="34" t="n"/>
-      <c r="O43" s="34" t="n"/>
-      <c r="P43" s="35" t="n"/>
-      <c r="Q43" s="44" t="inlineStr">
+      <c r="H44" s="34" t="n"/>
+      <c r="I44" s="34" t="n"/>
+      <c r="J44" s="34" t="n"/>
+      <c r="K44" s="34" t="n"/>
+      <c r="L44" s="34" t="n"/>
+      <c r="M44" s="34" t="n"/>
+      <c r="N44" s="34" t="n"/>
+      <c r="O44" s="34" t="n"/>
+      <c r="P44" s="35" t="n"/>
+      <c r="Q44" s="36" t="inlineStr">
         <is>
           <t>アプリ設定を置き換えない。</t>
         </is>
       </c>
-      <c r="R43" s="34" t="n"/>
-      <c r="S43" s="34" t="n"/>
-      <c r="T43" s="34" t="n"/>
-      <c r="U43" s="34" t="n"/>
-      <c r="V43" s="34" t="n"/>
-      <c r="W43" s="34" t="n"/>
-      <c r="X43" s="34" t="n"/>
-      <c r="Y43" s="34" t="n"/>
-      <c r="Z43" s="37" t="n"/>
-    </row>
-    <row r="45" ht="18" customHeight="1">
-      <c r="B45" s="42" t="inlineStr">
+      <c r="R44" s="34" t="n"/>
+      <c r="S44" s="34" t="n"/>
+      <c r="T44" s="34" t="n"/>
+      <c r="U44" s="34" t="n"/>
+      <c r="V44" s="34" t="n"/>
+      <c r="W44" s="34" t="n"/>
+      <c r="X44" s="34" t="n"/>
+      <c r="Y44" s="34" t="n"/>
+      <c r="Z44" s="37" t="n"/>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="B46" s="44" t="inlineStr">
         <is>
           <t>■9.5 デバイス別設計</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="20" customHeight="1">
-      <c r="B47" s="25" t="inlineStr">
+    <row r="48" ht="20" customHeight="1">
+      <c r="B48" s="25" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="C47" s="26" t="inlineStr">
+      <c r="C48" s="26" t="inlineStr">
         <is>
           <t>デバイス名</t>
         </is>
       </c>
-      <c r="D47" s="6" t="n"/>
-      <c r="E47" s="26" t="inlineStr">
+      <c r="D48" s="6" t="n"/>
+      <c r="E48" s="26" t="inlineStr">
         <is>
           <t>主な担当</t>
         </is>
       </c>
-      <c r="F47" s="6" t="n"/>
-      <c r="G47" s="26" t="inlineStr">
+      <c r="F48" s="6" t="n"/>
+      <c r="G48" s="26" t="inlineStr">
         <is>
           <t>主な処理</t>
         </is>
       </c>
-      <c r="H47" s="5" t="n"/>
-      <c r="I47" s="6" t="n"/>
-      <c r="J47" s="26" t="inlineStr">
+      <c r="H48" s="5" t="n"/>
+      <c r="I48" s="6" t="n"/>
+      <c r="J48" s="26" t="inlineStr">
         <is>
           <t>起動条件</t>
         </is>
       </c>
-      <c r="K47" s="5" t="n"/>
-      <c r="L47" s="5" t="n"/>
-      <c r="M47" s="5" t="n"/>
-      <c r="N47" s="6" t="n"/>
-      <c r="O47" s="26" t="inlineStr">
+      <c r="K48" s="5" t="n"/>
+      <c r="L48" s="5" t="n"/>
+      <c r="M48" s="5" t="n"/>
+      <c r="N48" s="6" t="n"/>
+      <c r="O48" s="26" t="inlineStr">
         <is>
           <t>終了条件</t>
         </is>
       </c>
-      <c r="P47" s="5" t="n"/>
-      <c r="Q47" s="5" t="n"/>
-      <c r="R47" s="6" t="n"/>
-      <c r="S47" s="26" t="inlineStr">
+      <c r="P48" s="5" t="n"/>
+      <c r="Q48" s="5" t="n"/>
+      <c r="R48" s="6" t="n"/>
+      <c r="S48" s="26" t="inlineStr">
         <is>
           <t>主な制約</t>
         </is>
       </c>
-      <c r="T47" s="5" t="n"/>
-      <c r="U47" s="6" t="n"/>
-      <c r="V47" s="26" t="inlineStr">
+      <c r="T48" s="5" t="n"/>
+      <c r="U48" s="6" t="n"/>
+      <c r="V48" s="26" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="W47" s="5" t="n"/>
-      <c r="X47" s="5" t="n"/>
-      <c r="Y47" s="5" t="n"/>
-      <c r="Z47" s="9" t="n"/>
-    </row>
-    <row r="48" ht="90" customHeight="1">
-      <c r="B48" s="27" t="inlineStr">
+      <c r="W48" s="5" t="n"/>
+      <c r="X48" s="5" t="n"/>
+      <c r="Y48" s="5" t="n"/>
+      <c r="Z48" s="9" t="n"/>
+    </row>
+    <row r="49" ht="90" customHeight="1">
+      <c r="B49" s="27" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C48" s="16" t="inlineStr">
+      <c r="C49" s="16" t="inlineStr">
         <is>
           <t>RT-300釣銭機</t>
         </is>
       </c>
-      <c r="D48" s="29" t="n"/>
-      <c r="E48" s="16" t="inlineStr">
+      <c r="D49" s="29" t="n"/>
+      <c r="E49" s="16" t="inlineStr">
         <is>
           <t>釣銭機制御部</t>
         </is>
       </c>
-      <c r="F48" s="29" t="n"/>
-      <c r="G48" s="16" t="inlineStr">
+      <c r="F49" s="29" t="n"/>
+      <c r="G49" s="16" t="inlineStr">
         <is>
           <t>入金、払出、状態確認、エラー確認。</t>
-        </is>
-      </c>
-      <c r="H48" s="28" t="n"/>
-      <c r="I48" s="29" t="n"/>
-      <c r="J48" s="16" t="inlineStr">
-        <is>
-          <t>host_device_config.jsonに釣銭機（CashChanger） / CashChanger1として定義されている。</t>
-        </is>
-      </c>
-      <c r="K48" s="28" t="n"/>
-      <c r="L48" s="28" t="n"/>
-      <c r="M48" s="28" t="n"/>
-      <c r="N48" s="29" t="n"/>
-      <c r="O48" s="16" t="inlineStr">
-        <is>
-          <t>デバイスコネクタ停止時またはデバイス停止処理時。</t>
-        </is>
-      </c>
-      <c r="P48" s="28" t="n"/>
-      <c r="Q48" s="28" t="n"/>
-      <c r="R48" s="29" t="n"/>
-      <c r="S48" s="16" t="inlineStr">
-        <is>
-          <t>デバイスコネクタ内OPOS、OCX、UIスレッド、共有メモリ、要求/応答ファイル連携。</t>
-        </is>
-      </c>
-      <c r="T48" s="28" t="n"/>
-      <c r="U48" s="29" t="n"/>
-      <c r="V48" s="16" t="inlineStr">
-        <is>
-          <t>デバイス開始は最大3回試行する。同期応答とデバイス処理結果通知を分けて扱う。</t>
-        </is>
-      </c>
-      <c r="W48" s="28" t="n"/>
-      <c r="X48" s="28" t="n"/>
-      <c r="Y48" s="28" t="n"/>
-      <c r="Z48" s="30" t="n"/>
-    </row>
-    <row r="49" ht="72" customHeight="1">
-      <c r="B49" s="31" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C49" s="32" t="inlineStr">
-        <is>
-          <t>SHARPキャッシュドロア</t>
-        </is>
-      </c>
-      <c r="D49" s="29" t="n"/>
-      <c r="E49" s="32" t="inlineStr">
-        <is>
-          <t>キャッシュドロア制御部</t>
-        </is>
-      </c>
-      <c r="F49" s="29" t="n"/>
-      <c r="G49" s="32" t="inlineStr">
-        <is>
-          <t>ドロアオープン。</t>
         </is>
       </c>
       <c r="H49" s="28" t="n"/>
       <c r="I49" s="29" t="n"/>
-      <c r="J49" s="32" t="inlineStr">
-        <is>
-          <t>host_device_config.jsonにキャッシュドロア（CashDrawer） / CashDrawer1として定義されている。</t>
+      <c r="J49" s="16" t="inlineStr">
+        <is>
+          <t>host_device_config.jsonに釣銭機（CashChanger） / CashChanger1として定義されている。</t>
         </is>
       </c>
       <c r="K49" s="28" t="n"/>
       <c r="L49" s="28" t="n"/>
       <c r="M49" s="28" t="n"/>
       <c r="N49" s="29" t="n"/>
-      <c r="O49" s="32" t="inlineStr">
+      <c r="O49" s="16" t="inlineStr">
         <is>
           <t>デバイスコネクタ停止時またはデバイス停止処理時。</t>
         </is>
@@ -9781,16 +9485,16 @@
       <c r="P49" s="28" t="n"/>
       <c r="Q49" s="28" t="n"/>
       <c r="R49" s="29" t="n"/>
-      <c r="S49" s="32" t="inlineStr">
-        <is>
-          <t>デバイスコネクタ内SHARP既存実装、OCXを保持する非表示フォーム。</t>
+      <c r="S49" s="16" t="inlineStr">
+        <is>
+          <t>デバイスコネクタ内OPOS、OCX、UIスレッド、共有メモリ、要求/応答ファイル連携。</t>
         </is>
       </c>
       <c r="T49" s="28" t="n"/>
       <c r="U49" s="29" t="n"/>
-      <c r="V49" s="32" t="inlineStr">
-        <is>
-          <t>結果コードと拡張結果コードを返す。</t>
+      <c r="V49" s="16" t="inlineStr">
+        <is>
+          <t>デバイス開始は最大3回試行する。同期応答とデバイス処理結果通知を分けて扱う。</t>
         </is>
       </c>
       <c r="W49" s="28" t="n"/>
@@ -9798,67 +9502,126 @@
       <c r="Y49" s="28" t="n"/>
       <c r="Z49" s="30" t="n"/>
     </row>
-    <row r="50" ht="90" customHeight="1">
-      <c r="B50" s="33" t="inlineStr">
+    <row r="50" ht="72" customHeight="1">
+      <c r="B50" s="31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C50" s="32" t="inlineStr">
+        <is>
+          <t>SHARPキャッシュドロア</t>
+        </is>
+      </c>
+      <c r="D50" s="29" t="n"/>
+      <c r="E50" s="32" t="inlineStr">
+        <is>
+          <t>キャッシュドロア制御部</t>
+        </is>
+      </c>
+      <c r="F50" s="29" t="n"/>
+      <c r="G50" s="32" t="inlineStr">
+        <is>
+          <t>ドロアオープン。</t>
+        </is>
+      </c>
+      <c r="H50" s="28" t="n"/>
+      <c r="I50" s="29" t="n"/>
+      <c r="J50" s="32" t="inlineStr">
+        <is>
+          <t>host_device_config.jsonにキャッシュドロア（CashDrawer） / CashDrawer1として定義されている。</t>
+        </is>
+      </c>
+      <c r="K50" s="28" t="n"/>
+      <c r="L50" s="28" t="n"/>
+      <c r="M50" s="28" t="n"/>
+      <c r="N50" s="29" t="n"/>
+      <c r="O50" s="32" t="inlineStr">
+        <is>
+          <t>デバイスコネクタ停止時またはデバイス停止処理時。</t>
+        </is>
+      </c>
+      <c r="P50" s="28" t="n"/>
+      <c r="Q50" s="28" t="n"/>
+      <c r="R50" s="29" t="n"/>
+      <c r="S50" s="32" t="inlineStr">
+        <is>
+          <t>デバイスコネクタ内SHARP既存実装、OCXを保持する非表示フォーム。</t>
+        </is>
+      </c>
+      <c r="T50" s="28" t="n"/>
+      <c r="U50" s="29" t="n"/>
+      <c r="V50" s="32" t="inlineStr">
+        <is>
+          <t>結果コードと拡張結果コードを返す。</t>
+        </is>
+      </c>
+      <c r="W50" s="28" t="n"/>
+      <c r="X50" s="28" t="n"/>
+      <c r="Y50" s="28" t="n"/>
+      <c r="Z50" s="30" t="n"/>
+    </row>
+    <row r="51" ht="90" customHeight="1">
+      <c r="B51" s="33" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C50" s="36" t="inlineStr">
+      <c r="C51" s="36" t="inlineStr">
         <is>
           <t>SHARPカスタマーディスプレイ</t>
         </is>
       </c>
-      <c r="D50" s="35" t="n"/>
-      <c r="E50" s="36" t="inlineStr">
+      <c r="D51" s="35" t="n"/>
+      <c r="E51" s="36" t="inlineStr">
         <is>
           <t>カスタマーディスプレイ制御部</t>
         </is>
       </c>
-      <c r="F50" s="35" t="n"/>
-      <c r="G50" s="36" t="inlineStr">
+      <c r="F51" s="35" t="n"/>
+      <c r="G51" s="36" t="inlineStr">
         <is>
           <t>表示、消去、スクロール、位置指定表示。</t>
         </is>
       </c>
-      <c r="H50" s="34" t="n"/>
-      <c r="I50" s="35" t="n"/>
-      <c r="J50" s="36" t="inlineStr">
+      <c r="H51" s="34" t="n"/>
+      <c r="I51" s="35" t="n"/>
+      <c r="J51" s="36" t="inlineStr">
         <is>
           <t>host_device_config.jsonにカスタマーディスプレイ（CustomerDisplay） / LineDisplay1として定義されている。</t>
         </is>
       </c>
-      <c r="K50" s="34" t="n"/>
-      <c r="L50" s="34" t="n"/>
-      <c r="M50" s="34" t="n"/>
-      <c r="N50" s="35" t="n"/>
-      <c r="O50" s="36" t="inlineStr">
+      <c r="K51" s="34" t="n"/>
+      <c r="L51" s="34" t="n"/>
+      <c r="M51" s="34" t="n"/>
+      <c r="N51" s="35" t="n"/>
+      <c r="O51" s="36" t="inlineStr">
         <is>
           <t>デバイスコネクタ停止時またはデバイス停止処理時。</t>
         </is>
       </c>
-      <c r="P50" s="34" t="n"/>
-      <c r="Q50" s="34" t="n"/>
-      <c r="R50" s="35" t="n"/>
-      <c r="S50" s="36" t="inlineStr">
+      <c r="P51" s="34" t="n"/>
+      <c r="Q51" s="34" t="n"/>
+      <c r="R51" s="35" t="n"/>
+      <c r="S51" s="36" t="inlineStr">
         <is>
           <t>デバイスコネクタ内SHARP既存実装、OPOS、OCXを保持する非表示フォーム、日本語文字列。</t>
         </is>
       </c>
-      <c r="T50" s="34" t="n"/>
-      <c r="U50" s="35" t="n"/>
-      <c r="V50" s="36" t="inlineStr">
+      <c r="T51" s="34" t="n"/>
+      <c r="U51" s="35" t="n"/>
+      <c r="V51" s="36" t="inlineStr">
         <is>
           <t>名前付きパイプはUTF-8の一行単位で送受信する。</t>
         </is>
       </c>
-      <c r="W50" s="34" t="n"/>
-      <c r="X50" s="34" t="n"/>
-      <c r="Y50" s="34" t="n"/>
-      <c r="Z50" s="37" t="n"/>
+      <c r="W51" s="34" t="n"/>
+      <c r="X51" s="34" t="n"/>
+      <c r="Y51" s="34" t="n"/>
+      <c r="Z51" s="37" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="179">
+  <mergeCells count="182">
     <mergeCell ref="Q14:S14"/>
     <mergeCell ref="F27:I27"/>
     <mergeCell ref="S21:T21"/>
@@ -9868,6 +9631,7 @@
     <mergeCell ref="O23:R23"/>
     <mergeCell ref="Q41:Z41"/>
     <mergeCell ref="Q15:S15"/>
+    <mergeCell ref="E51:F51"/>
     <mergeCell ref="C23:E23"/>
     <mergeCell ref="B42:F42"/>
     <mergeCell ref="W1:X1"/>
@@ -9882,6 +9646,7 @@
     <mergeCell ref="F25:I25"/>
     <mergeCell ref="J27:N27"/>
     <mergeCell ref="G42:P42"/>
+    <mergeCell ref="B44:F44"/>
     <mergeCell ref="U29:Z29"/>
     <mergeCell ref="G50:I50"/>
     <mergeCell ref="Q42:Z42"/>
@@ -9907,6 +9672,7 @@
     <mergeCell ref="F23:I23"/>
     <mergeCell ref="C20:E20"/>
     <mergeCell ref="C25:E25"/>
+    <mergeCell ref="Q44:Z44"/>
     <mergeCell ref="S22:T22"/>
     <mergeCell ref="O27:R27"/>
     <mergeCell ref="J48:N48"/>
@@ -9922,16 +9688,15 @@
     <mergeCell ref="H2:Q3"/>
     <mergeCell ref="G41:P41"/>
     <mergeCell ref="B43:F43"/>
-    <mergeCell ref="C47:D47"/>
     <mergeCell ref="U28:Z28"/>
     <mergeCell ref="J24:N24"/>
     <mergeCell ref="S23:T23"/>
     <mergeCell ref="B9:D9"/>
     <mergeCell ref="G43:P43"/>
     <mergeCell ref="T15:Z15"/>
+    <mergeCell ref="G51:I51"/>
     <mergeCell ref="C14:F14"/>
     <mergeCell ref="C32:E32"/>
-    <mergeCell ref="E47:F47"/>
     <mergeCell ref="J26:N26"/>
     <mergeCell ref="U20:Z20"/>
     <mergeCell ref="A1:D3"/>
@@ -9963,6 +9728,7 @@
     <mergeCell ref="U32:Z32"/>
     <mergeCell ref="J28:N28"/>
     <mergeCell ref="G16:J16"/>
+    <mergeCell ref="G44:P44"/>
     <mergeCell ref="B39:F39"/>
     <mergeCell ref="T1:V1"/>
     <mergeCell ref="J30:N30"/>
@@ -9974,15 +9740,16 @@
     <mergeCell ref="O28:R28"/>
     <mergeCell ref="H1:Q1"/>
     <mergeCell ref="T14:Z14"/>
-    <mergeCell ref="G47:I47"/>
     <mergeCell ref="C28:E28"/>
+    <mergeCell ref="B46:Z46"/>
+    <mergeCell ref="C51:D51"/>
     <mergeCell ref="O30:R30"/>
+    <mergeCell ref="V51:Z51"/>
     <mergeCell ref="J32:N32"/>
     <mergeCell ref="O20:R20"/>
     <mergeCell ref="C30:E30"/>
     <mergeCell ref="C48:D48"/>
     <mergeCell ref="Q38:Z38"/>
-    <mergeCell ref="J47:N47"/>
     <mergeCell ref="T2:V3"/>
     <mergeCell ref="O22:R22"/>
     <mergeCell ref="Q40:Z40"/>
@@ -9993,8 +9760,8 @@
     <mergeCell ref="S48:U48"/>
     <mergeCell ref="C49:D49"/>
     <mergeCell ref="F22:I22"/>
+    <mergeCell ref="O51:R51"/>
     <mergeCell ref="F31:I31"/>
-    <mergeCell ref="O47:R47"/>
     <mergeCell ref="S25:T25"/>
     <mergeCell ref="O48:R48"/>
     <mergeCell ref="T16:Z16"/>
@@ -10005,12 +9772,12 @@
     <mergeCell ref="U21:Z21"/>
     <mergeCell ref="C27:E27"/>
     <mergeCell ref="B5:Z5"/>
-    <mergeCell ref="B45:Z45"/>
     <mergeCell ref="O24:R24"/>
     <mergeCell ref="O33:R33"/>
     <mergeCell ref="Q37:Z37"/>
     <mergeCell ref="B38:F38"/>
     <mergeCell ref="G39:P39"/>
+    <mergeCell ref="S51:U51"/>
     <mergeCell ref="F24:I24"/>
     <mergeCell ref="U26:Z26"/>
     <mergeCell ref="C16:F16"/>
@@ -10022,18 +9789,17 @@
     <mergeCell ref="G38:P38"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="K16:P16"/>
-    <mergeCell ref="S47:U47"/>
     <mergeCell ref="F32:I32"/>
     <mergeCell ref="O8:S8"/>
     <mergeCell ref="F26:I26"/>
     <mergeCell ref="J21:N21"/>
     <mergeCell ref="S29:T29"/>
+    <mergeCell ref="J51:N51"/>
     <mergeCell ref="U27:Z27"/>
     <mergeCell ref="G48:I48"/>
     <mergeCell ref="O50:R50"/>
     <mergeCell ref="C29:E29"/>
     <mergeCell ref="U30:Z30"/>
-    <mergeCell ref="V47:Z47"/>
     <mergeCell ref="J23:N23"/>
     <mergeCell ref="B41:F41"/>
     <mergeCell ref="S31:T31"/>
@@ -10193,7 +9959,7 @@
       <c r="X2" s="15" t="n"/>
       <c r="Y2" s="17" t="inlineStr">
         <is>
-          <t>2026/07/13</t>
+          <t>2026/07/14</t>
         </is>
       </c>
       <c r="Z2" s="18" t="n"/>
@@ -10234,7 +10000,7 @@
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="B6" s="42" t="inlineStr">
+      <c r="B6" s="44" t="inlineStr">
         <is>
           <t>■10.1 異常分類</t>
         </is>
@@ -10490,7 +10256,7 @@
       <c r="E13" s="35" t="n"/>
       <c r="F13" s="36" t="inlineStr">
         <is>
-          <t>Host停止要求またはプロセス終了確認を完了できない。</t>
+          <t>デバイスコネクタ停止要求またはプロセス終了確認を完了できない。</t>
         </is>
       </c>
       <c r="G13" s="34" t="n"/>
@@ -10523,7 +10289,7 @@
       <c r="Z13" s="37" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="B15" s="42" t="inlineStr">
+      <c r="B15" s="44" t="inlineStr">
         <is>
           <t>■10.2 エラー処理方針</t>
         </is>
@@ -10539,7 +10305,7 @@
     <row r="18" ht="18" customHeight="1">
       <c r="C18" s="24" t="inlineStr">
         <is>
-          <t>② 既存互換を維持するため、失敗応答にも可能な範囲で結果コード（ResultCode）と戻り値（ReturnValue）を含める。</t>
+          <t>② 既存デバイス資源の結果契約を維持するため、失敗応答にも可能な範囲で結果コード（ResultCode）と戻り値（ReturnValue）を含める。</t>
         </is>
       </c>
     </row>
@@ -10565,7 +10331,7 @@
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="B22" s="42" t="inlineStr">
+      <c r="B22" s="44" t="inlineStr">
         <is>
           <t>■10.3 エラー処理一覧</t>
         </is>
@@ -10763,7 +10529,7 @@
       <c r="E27" s="29" t="n"/>
       <c r="F27" s="16" t="inlineStr">
         <is>
-          <t>JSONまたは既存互換形式が不正。</t>
+          <t>JSON形式が不正。</t>
         </is>
       </c>
       <c r="G27" s="28" t="n"/>
@@ -10771,7 +10537,7 @@
       <c r="I27" s="29" t="n"/>
       <c r="J27" s="16" t="inlineStr">
         <is>
-          <t>形式解析例外。</t>
+          <t>JSON解析例外。</t>
         </is>
       </c>
       <c r="K27" s="28" t="n"/>
@@ -11147,7 +10913,7 @@
       <c r="S33" s="29" t="n"/>
       <c r="T33" s="16" t="inlineStr">
         <is>
-          <t>個別デバイス実装のログ。</t>
+          <t>ホスト内部実装のログ。</t>
         </is>
       </c>
       <c r="U33" s="28" t="n"/>
@@ -11412,7 +11178,7 @@
       <c r="E38" s="29" t="n"/>
       <c r="F38" s="32" t="inlineStr">
         <is>
-          <t>Host停止要求失敗、応答タイムアウト、または所有プロセスが10秒以内に終了しない。</t>
+          <t>デバイスコネクタ停止要求失敗、応答タイムアウト、または所有プロセスが10秒以内に終了しない。</t>
         </is>
       </c>
       <c r="G38" s="28" t="n"/>
@@ -11427,7 +11193,7 @@
       <c r="L38" s="29" t="n"/>
       <c r="M38" s="32" t="inlineStr">
         <is>
-          <t>Host停止要求を受信できた場合は通常の停止処理を継続する。</t>
+          <t>デバイスコネクタ停止要求を受信できた場合は通常の停止処理を継続する。</t>
         </is>
       </c>
       <c r="N38" s="28" t="n"/>
@@ -11456,7 +11222,7 @@
       <c r="Y38" s="28" t="n"/>
       <c r="Z38" s="30" t="n"/>
     </row>
-    <row r="39" ht="54" customHeight="1">
+    <row r="39" ht="72" customHeight="1">
       <c r="B39" s="27" t="inlineStr">
         <is>
           <t>15</t>
@@ -11494,7 +11260,7 @@
       <c r="P39" s="29" t="n"/>
       <c r="Q39" s="16" t="inlineStr">
         <is>
-          <t>Host停止要求の受付応答は書込済みのため変更しない。</t>
+          <t>デバイスコネクタ停止要求の受付応答は書込済みのため変更しない。</t>
         </is>
       </c>
       <c r="R39" s="28" t="n"/>
@@ -11752,7 +11518,7 @@
       <c r="Z43" s="37" t="n"/>
     </row>
     <row r="45" ht="18" customHeight="1">
-      <c r="B45" s="42" t="inlineStr">
+      <c r="B45" s="44" t="inlineStr">
         <is>
           <t>■10.4 ログ出力方針</t>
         </is>
@@ -11787,7 +11553,7 @@
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
-      <c r="B51" s="42" t="inlineStr">
+      <c r="B51" s="44" t="inlineStr">
         <is>
           <t>■10.5 ログ出力一覧</t>
         </is>
@@ -11989,7 +11755,7 @@
       </c>
       <c r="C57" s="32" t="inlineStr">
         <is>
-          <t>Host停止要求失敗</t>
+          <t>デバイスコネクタ停止要求失敗</t>
         </is>
       </c>
       <c r="D57" s="28" t="n"/>
@@ -12380,7 +12146,7 @@
       <c r="I65" s="29" t="n"/>
       <c r="J65" s="32" t="inlineStr">
         <is>
-          <t>個別デバイス実装</t>
+          <t>ホスト内部実装</t>
         </is>
       </c>
       <c r="K65" s="28" t="n"/>
@@ -13060,7 +12826,7 @@
       <c r="X2" s="15" t="n"/>
       <c r="Y2" s="17" t="inlineStr">
         <is>
-          <t>2026/07/13</t>
+          <t>2026/07/14</t>
         </is>
       </c>
       <c r="Z2" s="18" t="n"/>
@@ -13744,7 +13510,7 @@
       <c r="Q17" s="29" t="n"/>
       <c r="R17" s="16" t="inlineStr">
         <is>
-          <t>プロセス存在・稼働確認、起動、Host停止要求、所有プロセス終了監視、強制終了。</t>
+          <t>プロセス存在・稼働確認、起動、デバイスコネクタ停止要求、所有プロセス終了監視、強制終了。</t>
         </is>
       </c>
       <c r="S17" s="28" t="n"/>
@@ -13760,7 +13526,7 @@
       <c r="Y17" s="28" t="n"/>
       <c r="Z17" s="30" t="n"/>
     </row>
-    <row r="18" ht="54" customHeight="1">
+    <row r="18" ht="36" customHeight="1">
       <c r="B18" s="31" t="inlineStr">
         <is>
           <t>12</t>
@@ -13789,7 +13555,7 @@
       <c r="K18" s="29" t="n"/>
       <c r="L18" s="32" t="inlineStr">
         <is>
-          <t>NamedPipeCommandMapper、LegacyMessageParser</t>
+          <t>NamedPipeCommandMapper</t>
         </is>
       </c>
       <c r="M18" s="28" t="n"/>
@@ -13799,7 +13565,7 @@
       <c r="Q18" s="29" t="n"/>
       <c r="R18" s="32" t="inlineStr">
         <is>
-          <t>JSON要求と既存互換形式の内部コマンド変換、および処理結果のJSON応答変換。</t>
+          <t>JSON要求の内部コマンド変換、および処理結果のJSON応答変換。</t>
         </is>
       </c>
       <c r="S18" s="28" t="n"/>
@@ -14019,7 +13785,7 @@
       <c r="Q22" s="29" t="n"/>
       <c r="R22" s="32" t="inlineStr">
         <is>
-          <t>二重起動防止、デバイスコネクタ本体の生成・開始、通常時の非表示実行、デバッグ画面。</t>
+          <t>二重起動防止、既存デバイス資源を管理する単一プロセスの生成・開始、通常時のバックグラウンド実行、デバッグ画面。</t>
         </is>
       </c>
       <c r="S22" s="28" t="n"/>
@@ -14074,7 +13840,7 @@
       <c r="Q23" s="35" t="n"/>
       <c r="R23" s="36" t="inlineStr">
         <is>
-          <t>アプリとは独立した保守操作としてHost停止要求を送信する。</t>
+          <t>アプリとは独立した保守操作としてデバイスコネクタ停止要求を送信する。</t>
         </is>
       </c>
       <c r="S23" s="34" t="n"/>
@@ -14235,7 +14001,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Z19"/>
+  <dimension ref="A1:Z20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -14369,7 +14135,7 @@
       <c r="X2" s="15" t="n"/>
       <c r="Y2" s="17" t="inlineStr">
         <is>
-          <t>2026/07/13</t>
+          <t>2026/07/14</t>
         </is>
       </c>
       <c r="Z2" s="18" t="n"/>
@@ -14456,22 +14222,22 @@
       <c r="Y6" s="5" t="n"/>
       <c r="Z6" s="9" t="n"/>
     </row>
-    <row r="7" ht="36" customHeight="1">
+    <row r="7" ht="54" customHeight="1">
       <c r="B7" s="27" t="inlineStr">
         <is>
-          <t>0.3.2</t>
+          <t>0.3.3</t>
         </is>
       </c>
       <c r="C7" s="29" t="n"/>
       <c r="D7" s="16" t="inlineStr">
         <is>
-          <t>2026/07/13</t>
+          <t>2026/07/14</t>
         </is>
       </c>
       <c r="E7" s="29" t="n"/>
       <c r="F7" s="16" t="inlineStr">
         <is>
-          <t>補足コメントの色指定と透過率の記載を分離し、淡い黄色の背景、黄土色の枠線、および濃い灰色の文字で表示する規約を明確化。</t>
+          <t>MAUIアプリと既存のOPOS、OCX、ActiveX、および既存DLLの実行環境差異を別プロセス化の理由として明確化。デバイスコネクタの実行形態、将来機器の対応方針、および名称を整理し、旧通信方式に関する記載を削除。</t>
         </is>
       </c>
       <c r="G7" s="28" t="n"/>
@@ -14506,7 +14272,7 @@
     <row r="8" ht="36" customHeight="1">
       <c r="B8" s="31" t="inlineStr">
         <is>
-          <t>0.3.1</t>
+          <t>0.3.2</t>
         </is>
       </c>
       <c r="C8" s="29" t="n"/>
@@ -14518,7 +14284,7 @@
       <c r="E8" s="29" t="n"/>
       <c r="F8" s="32" t="inlineStr">
         <is>
-          <t>図の関係について、矢印の向きと色・線種の役割を分離し、主処理、コマンド通信、実機制御、非同期イベント、設定参照、および異常経路の表示規約を明確化。</t>
+          <t>補足コメントの色指定と透過率の記載を分離し、淡い黄色の背景、黄土色の枠線、および濃い灰色の文字で表示する規約を明確化。</t>
         </is>
       </c>
       <c r="G8" s="28" t="n"/>
@@ -14553,19 +14319,19 @@
     <row r="9" ht="36" customHeight="1">
       <c r="B9" s="27" t="inlineStr">
         <is>
-          <t>0.3.0</t>
+          <t>0.3.1</t>
         </is>
       </c>
       <c r="C9" s="29" t="n"/>
       <c r="D9" s="16" t="inlineStr">
         <is>
-          <t>2026/07/12</t>
+          <t>2026/07/13</t>
         </is>
       </c>
       <c r="E9" s="29" t="n"/>
       <c r="F9" s="16" t="inlineStr">
         <is>
-          <t>システム全体、責務グループ、構成要素、機能の順に理解できる構成へ再設計。3つの図と本文の役割を整理し、重複していた処理説明を各設計章へ集約。</t>
+          <t>図の関係について、矢印の向きと色・線種の役割を分離し、主処理、コマンド通信、実機制御、非同期イベント、設定参照、および異常経路の表示規約を明確化。</t>
         </is>
       </c>
       <c r="G9" s="28" t="n"/>
@@ -14600,19 +14366,19 @@
     <row r="10" ht="36" customHeight="1">
       <c r="B10" s="31" t="inlineStr">
         <is>
-          <t>0.2.29</t>
+          <t>0.3.0</t>
         </is>
       </c>
       <c r="C10" s="29" t="n"/>
       <c r="D10" s="32" t="inlineStr">
         <is>
-          <t>2026/07/11</t>
+          <t>2026/07/12</t>
         </is>
       </c>
       <c r="E10" s="29" t="n"/>
       <c r="F10" s="32" t="inlineStr">
         <is>
-          <t>対象デバイスを対象範囲へ統合し、単独のデバイス別設計を廃止。機能詳細の手順表示と各一覧の番号付けを整理。</t>
+          <t>システム全体、責務グループ、構成要素、機能の順に理解できる構成へ再設計。3つの図と本文の役割を整理し、重複していた処理説明を各設計章へ集約。</t>
         </is>
       </c>
       <c r="G10" s="28" t="n"/>
@@ -14647,7 +14413,7 @@
     <row r="11" ht="36" customHeight="1">
       <c r="B11" s="27" t="inlineStr">
         <is>
-          <t>0.2.28</t>
+          <t>0.2.29</t>
         </is>
       </c>
       <c r="C11" s="29" t="n"/>
@@ -14659,7 +14425,7 @@
       <c r="E11" s="29" t="n"/>
       <c r="F11" s="16" t="inlineStr">
         <is>
-          <t>通常運用フローと重複していたライフサイクル設計を統合し、管理責務および保守・デバッグ時の扱いを通常運用説明へ集約。</t>
+          <t>対象デバイスを対象範囲へ統合し、単独のデバイス別設計を廃止。機能詳細の手順表示と各一覧の番号付けを整理。</t>
         </is>
       </c>
       <c r="G11" s="28" t="n"/>
@@ -14691,10 +14457,10 @@
       <c r="Y11" s="28" t="n"/>
       <c r="Z11" s="30" t="n"/>
     </row>
-    <row r="12" ht="24" customHeight="1">
+    <row r="12" ht="36" customHeight="1">
       <c r="B12" s="31" t="inlineStr">
         <is>
-          <t>0.2.27</t>
+          <t>0.2.28</t>
         </is>
       </c>
       <c r="C12" s="29" t="n"/>
@@ -14706,7 +14472,7 @@
       <c r="E12" s="29" t="n"/>
       <c r="F12" s="32" t="inlineStr">
         <is>
-          <t>理解しにくい構成要素だけに表示する補足コメントの表示規約を汎用へ追加。</t>
+          <t>通常運用フローと重複していたライフサイクル設計を統合し、管理責務および保守・デバッグ時の扱いを通常運用説明へ集約。</t>
         </is>
       </c>
       <c r="G12" s="28" t="n"/>
@@ -14738,10 +14504,10 @@
       <c r="Y12" s="28" t="n"/>
       <c r="Z12" s="30" t="n"/>
     </row>
-    <row r="13" ht="36" customHeight="1">
+    <row r="13" ht="24" customHeight="1">
       <c r="B13" s="27" t="inlineStr">
         <is>
-          <t>0.2.26</t>
+          <t>0.2.27</t>
         </is>
       </c>
       <c r="C13" s="29" t="n"/>
@@ -14753,7 +14519,7 @@
       <c r="E13" s="29" t="n"/>
       <c r="F13" s="16" t="inlineStr">
         <is>
-          <t>デバイス操作要求処理とライフサイクルを通常運用フローへ統合し、起動・操作・終了および主要異常経路を1図で確認できる構成へ変更。</t>
+          <t>理解しにくい構成要素だけに表示する補足コメントの表示規約を汎用へ追加。</t>
         </is>
       </c>
       <c r="G13" s="28" t="n"/>
@@ -14788,7 +14554,7 @@
     <row r="14" ht="36" customHeight="1">
       <c r="B14" s="31" t="inlineStr">
         <is>
-          <t>0.2.25</t>
+          <t>0.2.26</t>
         </is>
       </c>
       <c r="C14" s="29" t="n"/>
@@ -14800,7 +14566,7 @@
       <c r="E14" s="29" t="n"/>
       <c r="F14" s="32" t="inlineStr">
         <is>
-          <t>通信再試行、再送禁止、イベント再接続、異常種別、および稼働確認の時間条件を各処理図へ反映。</t>
+          <t>デバイス操作要求処理とライフサイクルを通常運用フローへ統合し、起動・操作・終了および主要異常経路を1図で確認できる構成へ変更。</t>
         </is>
       </c>
       <c r="G14" s="28" t="n"/>
@@ -14832,10 +14598,10 @@
       <c r="Y14" s="28" t="n"/>
       <c r="Z14" s="30" t="n"/>
     </row>
-    <row r="15" ht="54" customHeight="1">
+    <row r="15" ht="36" customHeight="1">
       <c r="B15" s="27" t="inlineStr">
         <is>
-          <t>0.2.24</t>
+          <t>0.2.25</t>
         </is>
       </c>
       <c r="C15" s="29" t="n"/>
@@ -14847,7 +14613,7 @@
       <c r="E15" s="29" t="n"/>
       <c r="F15" s="16" t="inlineStr">
         <is>
-          <t>プロセス起動準備確認、所有プロセスの停止、非同期イベント受信、通信再試行、設定読込、エラー処理、およびログを設計方針として確定。全体構成とライフサイクルを更新。</t>
+          <t>通信再試行、再送禁止、イベント再接続、異常種別、および稼働確認の時間条件を各処理図へ反映。</t>
         </is>
       </c>
       <c r="G15" s="28" t="n"/>
@@ -14879,10 +14645,10 @@
       <c r="Y15" s="28" t="n"/>
       <c r="Z15" s="30" t="n"/>
     </row>
-    <row r="16" ht="36" customHeight="1">
+    <row r="16" ht="54" customHeight="1">
       <c r="B16" s="31" t="inlineStr">
         <is>
-          <t>0.2.23</t>
+          <t>0.2.24</t>
         </is>
       </c>
       <c r="C16" s="29" t="n"/>
@@ -14894,7 +14660,7 @@
       <c r="E16" s="29" t="n"/>
       <c r="F16" s="32" t="inlineStr">
         <is>
-          <t>同期応答経路とプロセス終了確認を明確化し、デバイス操作失敗と通信失敗を分離。通常の停止制御と対象外デバイス記載をエラー一覧から整理。</t>
+          <t>プロセス起動準備確認、所有プロセスの停止、非同期イベント受信、通信再試行、設定読込、エラー処理、およびログを設計方針として確定。全体構成とライフサイクルを更新。</t>
         </is>
       </c>
       <c r="G16" s="28" t="n"/>
@@ -14929,19 +14695,19 @@
     <row r="17" ht="36" customHeight="1">
       <c r="B17" s="27" t="inlineStr">
         <is>
-          <t>0.2.21</t>
+          <t>0.2.23</t>
         </is>
       </c>
       <c r="C17" s="29" t="n"/>
       <c r="D17" s="16" t="inlineStr">
         <is>
-          <t>2026/07/10</t>
+          <t>2026/07/11</t>
         </is>
       </c>
       <c r="E17" s="29" t="n"/>
       <c r="F17" s="16" t="inlineStr">
         <is>
-          <t>全体構成を、3つの責務領域と主経路を示す全体概要図、および詳細構成図の2段構成へ変更。</t>
+          <t>同期応答経路とプロセス終了確認を明確化し、デバイス操作失敗と通信失敗を分離。通常の停止制御と対象外デバイス記載をエラー一覧から整理。</t>
         </is>
       </c>
       <c r="G17" s="28" t="n"/>
@@ -14973,10 +14739,10 @@
       <c r="Y17" s="28" t="n"/>
       <c r="Z17" s="30" t="n"/>
     </row>
-    <row r="18" ht="24" customHeight="1">
+    <row r="18" ht="36" customHeight="1">
       <c r="B18" s="31" t="inlineStr">
         <is>
-          <t>0.2.16</t>
+          <t>0.2.21</t>
         </is>
       </c>
       <c r="C18" s="29" t="n"/>
@@ -14988,7 +14754,7 @@
       <c r="E18" s="29" t="n"/>
       <c r="F18" s="32" t="inlineStr">
         <is>
-          <t>本文と図の論理名称を日本語へ統一し、物理識別子の記載箇所を整理。</t>
+          <t>全体構成を、3つの責務領域と主経路を示す全体概要図、および詳細構成図の2段構成へ変更。</t>
         </is>
       </c>
       <c r="G18" s="28" t="n"/>
@@ -15021,54 +14787,102 @@
       <c r="Z18" s="30" t="n"/>
     </row>
     <row r="19" ht="24" customHeight="1">
-      <c r="B19" s="33" t="inlineStr">
+      <c r="B19" s="27" t="inlineStr">
+        <is>
+          <t>0.2.16</t>
+        </is>
+      </c>
+      <c r="C19" s="29" t="n"/>
+      <c r="D19" s="16" t="inlineStr">
+        <is>
+          <t>2026/07/10</t>
+        </is>
+      </c>
+      <c r="E19" s="29" t="n"/>
+      <c r="F19" s="16" t="inlineStr">
+        <is>
+          <t>本文と図の論理名称を日本語へ統一し、物理識別子の記載箇所を整理。</t>
+        </is>
+      </c>
+      <c r="G19" s="28" t="n"/>
+      <c r="H19" s="28" t="n"/>
+      <c r="I19" s="28" t="n"/>
+      <c r="J19" s="28" t="n"/>
+      <c r="K19" s="28" t="n"/>
+      <c r="L19" s="28" t="n"/>
+      <c r="M19" s="28" t="n"/>
+      <c r="N19" s="28" t="n"/>
+      <c r="O19" s="28" t="n"/>
+      <c r="P19" s="28" t="n"/>
+      <c r="Q19" s="28" t="n"/>
+      <c r="R19" s="29" t="n"/>
+      <c r="S19" s="16" t="inlineStr">
+        <is>
+          <t>VTI サム</t>
+        </is>
+      </c>
+      <c r="T19" s="28" t="n"/>
+      <c r="U19" s="28" t="n"/>
+      <c r="V19" s="29" t="n"/>
+      <c r="W19" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X19" s="28" t="n"/>
+      <c r="Y19" s="28" t="n"/>
+      <c r="Z19" s="30" t="n"/>
+    </row>
+    <row r="20" ht="24" customHeight="1">
+      <c r="B20" s="38" t="inlineStr">
         <is>
           <t>0.2.8</t>
         </is>
       </c>
-      <c r="C19" s="35" t="n"/>
-      <c r="D19" s="36" t="inlineStr">
+      <c r="C20" s="35" t="n"/>
+      <c r="D20" s="39" t="inlineStr">
         <is>
           <t>2026/07/08</t>
         </is>
       </c>
-      <c r="E19" s="35" t="n"/>
-      <c r="F19" s="36" t="inlineStr">
+      <c r="E20" s="35" t="n"/>
+      <c r="F20" s="39" t="inlineStr">
         <is>
           <t>デバイスコネクタの基本設計書として新規作成。</t>
         </is>
       </c>
-      <c r="G19" s="34" t="n"/>
-      <c r="H19" s="34" t="n"/>
-      <c r="I19" s="34" t="n"/>
-      <c r="J19" s="34" t="n"/>
-      <c r="K19" s="34" t="n"/>
-      <c r="L19" s="34" t="n"/>
-      <c r="M19" s="34" t="n"/>
-      <c r="N19" s="34" t="n"/>
-      <c r="O19" s="34" t="n"/>
-      <c r="P19" s="34" t="n"/>
-      <c r="Q19" s="34" t="n"/>
-      <c r="R19" s="35" t="n"/>
-      <c r="S19" s="36" t="inlineStr">
+      <c r="G20" s="34" t="n"/>
+      <c r="H20" s="34" t="n"/>
+      <c r="I20" s="34" t="n"/>
+      <c r="J20" s="34" t="n"/>
+      <c r="K20" s="34" t="n"/>
+      <c r="L20" s="34" t="n"/>
+      <c r="M20" s="34" t="n"/>
+      <c r="N20" s="34" t="n"/>
+      <c r="O20" s="34" t="n"/>
+      <c r="P20" s="34" t="n"/>
+      <c r="Q20" s="34" t="n"/>
+      <c r="R20" s="35" t="n"/>
+      <c r="S20" s="39" t="inlineStr">
         <is>
           <t>VTI サム</t>
         </is>
       </c>
-      <c r="T19" s="34" t="n"/>
-      <c r="U19" s="34" t="n"/>
-      <c r="V19" s="35" t="n"/>
-      <c r="W19" s="36" t="inlineStr">
+      <c r="T20" s="34" t="n"/>
+      <c r="U20" s="34" t="n"/>
+      <c r="V20" s="35" t="n"/>
+      <c r="W20" s="39" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="X19" s="34" t="n"/>
-      <c r="Y19" s="34" t="n"/>
-      <c r="Z19" s="37" t="n"/>
+      <c r="X20" s="34" t="n"/>
+      <c r="Y20" s="34" t="n"/>
+      <c r="Z20" s="37" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="84">
+  <mergeCells count="89">
+    <mergeCell ref="D20:E20"/>
     <mergeCell ref="W9:Z9"/>
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="D6:E6"/>
@@ -15091,6 +14905,7 @@
     <mergeCell ref="D10:E10"/>
     <mergeCell ref="F13:R13"/>
     <mergeCell ref="D19:E19"/>
+    <mergeCell ref="S20:V20"/>
     <mergeCell ref="B18:C18"/>
     <mergeCell ref="W14:Z14"/>
     <mergeCell ref="H2:Q3"/>
@@ -15103,6 +14918,7 @@
     <mergeCell ref="F6:R6"/>
     <mergeCell ref="A1:D3"/>
     <mergeCell ref="D9:E9"/>
+    <mergeCell ref="F20:R20"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="D15:E15"/>
@@ -15132,6 +14948,7 @@
     <mergeCell ref="T2:V3"/>
     <mergeCell ref="F18:R18"/>
     <mergeCell ref="S13:V13"/>
+    <mergeCell ref="B20:C20"/>
     <mergeCell ref="F8:R8"/>
     <mergeCell ref="D14:E14"/>
     <mergeCell ref="W7:Z7"/>
@@ -15151,6 +14968,7 @@
     <mergeCell ref="S11:V11"/>
     <mergeCell ref="F12:R12"/>
     <mergeCell ref="D18:E18"/>
+    <mergeCell ref="W20:Z20"/>
     <mergeCell ref="D8:E8"/>
     <mergeCell ref="W12:Z12"/>
   </mergeCells>
@@ -15308,7 +15126,7 @@
       <c r="X2" s="15" t="n"/>
       <c r="Y2" s="17" t="inlineStr">
         <is>
-          <t>2026/07/13</t>
+          <t>2026/07/14</t>
         </is>
       </c>
       <c r="Z2" s="18" t="n"/>
@@ -15342,7 +15160,7 @@
       <c r="Z3" s="23" t="n"/>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="B6" s="38" t="n"/>
+      <c r="B6" s="40" t="n"/>
       <c r="C6" s="2" t="n"/>
       <c r="D6" s="2" t="n"/>
       <c r="E6" s="2" t="n"/>
@@ -15353,7 +15171,7 @@
       <c r="J6" s="2" t="n"/>
       <c r="K6" s="2" t="n"/>
       <c r="L6" s="2" t="n"/>
-      <c r="M6" s="38" t="n"/>
+      <c r="M6" s="40" t="n"/>
       <c r="N6" s="2" t="n"/>
       <c r="O6" s="2" t="n"/>
       <c r="P6" s="2" t="n"/>
@@ -15366,11 +15184,11 @@
       <c r="W6" s="2" t="n"/>
       <c r="X6" s="2" t="n"/>
       <c r="Y6" s="2" t="n"/>
-      <c r="Z6" s="39" t="n"/>
+      <c r="Z6" s="41" t="n"/>
     </row>
     <row r="7" ht="24" customHeight="1">
       <c r="B7" s="10" t="n"/>
-      <c r="C7" s="40" t="inlineStr">
+      <c r="C7" s="42" t="inlineStr">
         <is>
           <t>1． 表紙（00_表紙）</t>
         </is>
@@ -15388,11 +15206,11 @@
       <c r="W7" s="11" t="n"/>
       <c r="X7" s="11" t="n"/>
       <c r="Y7" s="11" t="n"/>
-      <c r="Z7" s="41" t="n"/>
+      <c r="Z7" s="43" t="n"/>
     </row>
     <row r="8" ht="24" customHeight="1">
       <c r="B8" s="10" t="n"/>
-      <c r="C8" s="40" t="inlineStr">
+      <c r="C8" s="42" t="inlineStr">
         <is>
           <t>2． 改訂履歴（01_改訂履歴）</t>
         </is>
@@ -15410,11 +15228,11 @@
       <c r="W8" s="11" t="n"/>
       <c r="X8" s="11" t="n"/>
       <c r="Y8" s="11" t="n"/>
-      <c r="Z8" s="41" t="n"/>
+      <c r="Z8" s="43" t="n"/>
     </row>
     <row r="9" ht="24" customHeight="1">
       <c r="B9" s="10" t="n"/>
-      <c r="C9" s="40" t="inlineStr">
+      <c r="C9" s="42" t="inlineStr">
         <is>
           <t>3． 概要（02_概要）</t>
         </is>
@@ -15432,11 +15250,11 @@
       <c r="W9" s="11" t="n"/>
       <c r="X9" s="11" t="n"/>
       <c r="Y9" s="11" t="n"/>
-      <c r="Z9" s="41" t="n"/>
+      <c r="Z9" s="43" t="n"/>
     </row>
     <row r="10" ht="24" customHeight="1">
       <c r="B10" s="10" t="n"/>
-      <c r="C10" s="40" t="inlineStr">
+      <c r="C10" s="42" t="inlineStr">
         <is>
           <t>4． 対象範囲（03_対象範囲）</t>
         </is>
@@ -15454,11 +15272,11 @@
       <c r="W10" s="11" t="n"/>
       <c r="X10" s="11" t="n"/>
       <c r="Y10" s="11" t="n"/>
-      <c r="Z10" s="41" t="n"/>
+      <c r="Z10" s="43" t="n"/>
     </row>
     <row r="11" ht="24" customHeight="1">
       <c r="B11" s="10" t="n"/>
-      <c r="C11" s="40" t="inlineStr">
+      <c r="C11" s="42" t="inlineStr">
         <is>
           <t>5． 関連資料（04_関連資料）</t>
         </is>
@@ -15476,11 +15294,11 @@
       <c r="W11" s="11" t="n"/>
       <c r="X11" s="11" t="n"/>
       <c r="Y11" s="11" t="n"/>
-      <c r="Z11" s="41" t="n"/>
+      <c r="Z11" s="43" t="n"/>
     </row>
     <row r="12" ht="24" customHeight="1">
       <c r="B12" s="10" t="n"/>
-      <c r="C12" s="40" t="inlineStr">
+      <c r="C12" s="42" t="inlineStr">
         <is>
           <t>6． システム・論理構成図（05_全体構成_01）</t>
         </is>
@@ -15498,11 +15316,11 @@
       <c r="W12" s="11" t="n"/>
       <c r="X12" s="11" t="n"/>
       <c r="Y12" s="11" t="n"/>
-      <c r="Z12" s="41" t="n"/>
+      <c r="Z12" s="43" t="n"/>
     </row>
     <row r="13" ht="24" customHeight="1">
       <c r="B13" s="10" t="n"/>
-      <c r="C13" s="40" t="inlineStr">
+      <c r="C13" s="42" t="inlineStr">
         <is>
           <t>7． 責務階層・構成要素（05_全体構成_02）</t>
         </is>
@@ -15520,11 +15338,11 @@
       <c r="W13" s="11" t="n"/>
       <c r="X13" s="11" t="n"/>
       <c r="Y13" s="11" t="n"/>
-      <c r="Z13" s="41" t="n"/>
+      <c r="Z13" s="43" t="n"/>
     </row>
     <row r="14" ht="24" customHeight="1">
       <c r="B14" s="10" t="n"/>
-      <c r="C14" s="40" t="inlineStr">
+      <c r="C14" s="42" t="inlineStr">
         <is>
           <t>8． 運用シナリオ図（06_運用シナリオ_01）</t>
         </is>
@@ -15542,11 +15360,11 @@
       <c r="W14" s="11" t="n"/>
       <c r="X14" s="11" t="n"/>
       <c r="Y14" s="11" t="n"/>
-      <c r="Z14" s="41" t="n"/>
+      <c r="Z14" s="43" t="n"/>
     </row>
     <row r="15" ht="24" customHeight="1">
       <c r="B15" s="10" t="n"/>
-      <c r="C15" s="40" t="inlineStr">
+      <c r="C15" s="42" t="inlineStr">
         <is>
           <t>9． 運用シナリオ説明（06_運用シナリオ_02）</t>
         </is>
@@ -15564,11 +15382,11 @@
       <c r="W15" s="11" t="n"/>
       <c r="X15" s="11" t="n"/>
       <c r="Y15" s="11" t="n"/>
-      <c r="Z15" s="41" t="n"/>
+      <c r="Z15" s="43" t="n"/>
     </row>
     <row r="16" ht="24" customHeight="1">
       <c r="B16" s="10" t="n"/>
-      <c r="C16" s="40" t="inlineStr">
+      <c r="C16" s="42" t="inlineStr">
         <is>
           <t>10． 機能設計（07_機能設計）</t>
         </is>
@@ -15586,11 +15404,11 @@
       <c r="W16" s="11" t="n"/>
       <c r="X16" s="11" t="n"/>
       <c r="Y16" s="11" t="n"/>
-      <c r="Z16" s="41" t="n"/>
+      <c r="Z16" s="43" t="n"/>
     </row>
     <row r="17" ht="24" customHeight="1">
       <c r="B17" s="10" t="n"/>
-      <c r="C17" s="40" t="inlineStr">
+      <c r="C17" s="42" t="inlineStr">
         <is>
           <t>11． 通信・データ設計（08_通信・データ設計）</t>
         </is>
@@ -15608,11 +15426,11 @@
       <c r="W17" s="11" t="n"/>
       <c r="X17" s="11" t="n"/>
       <c r="Y17" s="11" t="n"/>
-      <c r="Z17" s="41" t="n"/>
+      <c r="Z17" s="43" t="n"/>
     </row>
     <row r="18" ht="24" customHeight="1">
       <c r="B18" s="10" t="n"/>
-      <c r="C18" s="40" t="inlineStr">
+      <c r="C18" s="42" t="inlineStr">
         <is>
           <t>12． 設定・デバイス設計（09_設定・デバイス設計）</t>
         </is>
@@ -15630,11 +15448,11 @@
       <c r="W18" s="11" t="n"/>
       <c r="X18" s="11" t="n"/>
       <c r="Y18" s="11" t="n"/>
-      <c r="Z18" s="41" t="n"/>
+      <c r="Z18" s="43" t="n"/>
     </row>
     <row r="19" ht="24" customHeight="1">
       <c r="B19" s="10" t="n"/>
-      <c r="C19" s="40" t="inlineStr">
+      <c r="C19" s="42" t="inlineStr">
         <is>
           <t>13． 異常・運用設計（10_異常・運用設計）</t>
         </is>
@@ -15652,11 +15470,11 @@
       <c r="W19" s="11" t="n"/>
       <c r="X19" s="11" t="n"/>
       <c r="Y19" s="11" t="n"/>
-      <c r="Z19" s="41" t="n"/>
+      <c r="Z19" s="43" t="n"/>
     </row>
     <row r="20" ht="24" customHeight="1">
       <c r="B20" s="10" t="n"/>
-      <c r="C20" s="40" t="inlineStr">
+      <c r="C20" s="42" t="inlineStr">
         <is>
           <t>14． 実装対応（11_実装対応）</t>
         </is>
@@ -15674,7 +15492,7 @@
       <c r="W20" s="11" t="n"/>
       <c r="X20" s="11" t="n"/>
       <c r="Y20" s="11" t="n"/>
-      <c r="Z20" s="41" t="n"/>
+      <c r="Z20" s="43" t="n"/>
     </row>
     <row r="21" ht="24" customHeight="1">
       <c r="B21" s="10" t="n"/>
@@ -15701,7 +15519,7 @@
       <c r="W21" s="11" t="n"/>
       <c r="X21" s="11" t="n"/>
       <c r="Y21" s="11" t="n"/>
-      <c r="Z21" s="41" t="n"/>
+      <c r="Z21" s="43" t="n"/>
     </row>
     <row r="22" ht="24" customHeight="1">
       <c r="B22" s="10" t="n"/>
@@ -15728,7 +15546,7 @@
       <c r="W22" s="11" t="n"/>
       <c r="X22" s="11" t="n"/>
       <c r="Y22" s="11" t="n"/>
-      <c r="Z22" s="41" t="n"/>
+      <c r="Z22" s="43" t="n"/>
     </row>
     <row r="23" ht="24" customHeight="1">
       <c r="B23" s="10" t="n"/>
@@ -15755,7 +15573,7 @@
       <c r="W23" s="11" t="n"/>
       <c r="X23" s="11" t="n"/>
       <c r="Y23" s="11" t="n"/>
-      <c r="Z23" s="41" t="n"/>
+      <c r="Z23" s="43" t="n"/>
     </row>
     <row r="24" ht="24" customHeight="1">
       <c r="B24" s="10" t="n"/>
@@ -15782,7 +15600,7 @@
       <c r="W24" s="11" t="n"/>
       <c r="X24" s="11" t="n"/>
       <c r="Y24" s="11" t="n"/>
-      <c r="Z24" s="41" t="n"/>
+      <c r="Z24" s="43" t="n"/>
     </row>
     <row r="25" ht="24" customHeight="1">
       <c r="B25" s="10" t="n"/>
@@ -15809,7 +15627,7 @@
       <c r="W25" s="11" t="n"/>
       <c r="X25" s="11" t="n"/>
       <c r="Y25" s="11" t="n"/>
-      <c r="Z25" s="41" t="n"/>
+      <c r="Z25" s="43" t="n"/>
     </row>
     <row r="26" ht="24" customHeight="1">
       <c r="B26" s="10" t="n"/>
@@ -15836,7 +15654,7 @@
       <c r="W26" s="11" t="n"/>
       <c r="X26" s="11" t="n"/>
       <c r="Y26" s="11" t="n"/>
-      <c r="Z26" s="41" t="n"/>
+      <c r="Z26" s="43" t="n"/>
     </row>
     <row r="27" ht="24" customHeight="1">
       <c r="B27" s="10" t="n"/>
@@ -15863,7 +15681,7 @@
       <c r="W27" s="11" t="n"/>
       <c r="X27" s="11" t="n"/>
       <c r="Y27" s="11" t="n"/>
-      <c r="Z27" s="41" t="n"/>
+      <c r="Z27" s="43" t="n"/>
     </row>
     <row r="28" ht="24" customHeight="1">
       <c r="B28" s="10" t="n"/>
@@ -15890,7 +15708,7 @@
       <c r="W28" s="11" t="n"/>
       <c r="X28" s="11" t="n"/>
       <c r="Y28" s="11" t="n"/>
-      <c r="Z28" s="41" t="n"/>
+      <c r="Z28" s="43" t="n"/>
     </row>
     <row r="29" ht="24" customHeight="1">
       <c r="B29" s="10" t="n"/>
@@ -15917,7 +15735,7 @@
       <c r="W29" s="11" t="n"/>
       <c r="X29" s="11" t="n"/>
       <c r="Y29" s="11" t="n"/>
-      <c r="Z29" s="41" t="n"/>
+      <c r="Z29" s="43" t="n"/>
     </row>
     <row r="30" ht="24" customHeight="1">
       <c r="B30" s="10" t="n"/>
@@ -15944,7 +15762,7 @@
       <c r="W30" s="11" t="n"/>
       <c r="X30" s="11" t="n"/>
       <c r="Y30" s="11" t="n"/>
-      <c r="Z30" s="41" t="n"/>
+      <c r="Z30" s="43" t="n"/>
     </row>
     <row r="31" ht="24" customHeight="1">
       <c r="B31" s="10" t="n"/>
@@ -15971,7 +15789,7 @@
       <c r="W31" s="11" t="n"/>
       <c r="X31" s="11" t="n"/>
       <c r="Y31" s="11" t="n"/>
-      <c r="Z31" s="41" t="n"/>
+      <c r="Z31" s="43" t="n"/>
     </row>
     <row r="32" ht="24" customHeight="1">
       <c r="B32" s="19" t="n"/>
@@ -16050,7 +15868,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Z40"/>
+  <dimension ref="A1:Z42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -16184,7 +16002,7 @@
       <c r="X2" s="15" t="n"/>
       <c r="Y2" s="17" t="inlineStr">
         <is>
-          <t>2026/07/13</t>
+          <t>2026/07/14</t>
         </is>
       </c>
       <c r="Z2" s="18" t="n"/>
@@ -16225,7 +16043,7 @@
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="B6" s="42" t="inlineStr">
+      <c r="B6" s="44" t="inlineStr">
         <is>
           <t>■2.1 設計目的と結論</t>
         </is>
@@ -16234,115 +16052,83 @@
     <row r="8" ht="28" customHeight="1">
       <c r="B8" s="24" t="inlineStr">
         <is>
-          <t>タブレットPOS端末アプリから周辺機器の実装方式を分離し、機器ごとの既存制御資源を共通の通信契約で利用できる構成とする。そのため、周辺機器を制御するデバイスコネクタをタブレットPOS端末アプリとは別プロセスとして配置する。</t>
+          <t>タブレットPOS端末アプリは.NET MAUIで動作するため、既存デバイスが使用するOPOS、OCX、ActiveX、および既存DLLをアプリプロセス内で直接実行しない。これらの既存デバイス資源を必要なWindows実行環境内で継続利用するため、デバイスコネクタをタブレットPOS端末アプリとは別プロセスとして配置する。</t>
         </is>
       </c>
     </row>
     <row r="9" ht="42" customHeight="1">
       <c r="B9" s="24" t="inlineStr">
         <is>
-          <t>アプリケーション層は業務上必要なデバイス操作をデバイス制御層へ依頼する。デバイス制御層は要求と結果をアプリ内の形式へ変換し、名前付きパイプを介してデバイスコネクタと通信する。デバイスコネクタは要求順序の保証、対象デバイスの選択、既存資源を利用した実機制御、および非同期イベント配信を担当する。この境界により、アプリケーション層はデバイスコネクタ内部や個別デバイス実装を直接呼び出さない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="B10" s="42" t="inlineStr">
+          <t>アプリケーション層は業務上必要なデバイス操作をデバイス制御層へ依頼する。デバイス制御層は要求と結果をアプリ内の形式へ変換し、名前付きパイプを介してデバイスコネクタと通信する。デバイスコネクタは要求順序の保証、対象デバイスの選択、既存デバイス資源の呼出し、および非同期イベント配信を担当する。この境界により、アプリケーション層はOPOS、OCX、ActiveX、既存DLL、またはデバイスコネクタ内部実装を直接呼び出さない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1">
+      <c r="B10" s="24" t="inlineStr">
+        <is>
+          <t>デバイスコネクタは、現行POSで使用している既存デバイスを継続利用するための互換境界とする。今後追加する機器は、既存デバイス資源を必要とする場合を除き、端末アプリから直接制御する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="B11" s="44" t="inlineStr">
         <is>
           <t>■2.2 システム内の位置付け</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="B12" s="25" t="inlineStr">
+    <row r="13" ht="20" customHeight="1">
+      <c r="B13" s="25" t="inlineStr">
         <is>
           <t>責務領域</t>
         </is>
       </c>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="6" t="n"/>
-      <c r="G12" s="26" t="inlineStr">
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="26" t="inlineStr">
         <is>
           <t>担当する内容</t>
         </is>
       </c>
-      <c r="H12" s="5" t="n"/>
-      <c r="I12" s="5" t="n"/>
-      <c r="J12" s="5" t="n"/>
-      <c r="K12" s="5" t="n"/>
-      <c r="L12" s="5" t="n"/>
-      <c r="M12" s="5" t="n"/>
-      <c r="N12" s="5" t="n"/>
-      <c r="O12" s="5" t="n"/>
-      <c r="P12" s="6" t="n"/>
-      <c r="Q12" s="26" t="inlineStr">
+      <c r="H13" s="5" t="n"/>
+      <c r="I13" s="5" t="n"/>
+      <c r="J13" s="5" t="n"/>
+      <c r="K13" s="5" t="n"/>
+      <c r="L13" s="5" t="n"/>
+      <c r="M13" s="5" t="n"/>
+      <c r="N13" s="5" t="n"/>
+      <c r="O13" s="5" t="n"/>
+      <c r="P13" s="6" t="n"/>
+      <c r="Q13" s="26" t="inlineStr">
         <is>
           <t>担当しない内容</t>
         </is>
       </c>
-      <c r="R12" s="5" t="n"/>
-      <c r="S12" s="5" t="n"/>
-      <c r="T12" s="5" t="n"/>
-      <c r="U12" s="5" t="n"/>
-      <c r="V12" s="5" t="n"/>
-      <c r="W12" s="5" t="n"/>
-      <c r="X12" s="5" t="n"/>
-      <c r="Y12" s="5" t="n"/>
-      <c r="Z12" s="9" t="n"/>
-    </row>
-    <row r="13" ht="36" customHeight="1">
-      <c r="B13" s="27" t="inlineStr">
+      <c r="R13" s="5" t="n"/>
+      <c r="S13" s="5" t="n"/>
+      <c r="T13" s="5" t="n"/>
+      <c r="U13" s="5" t="n"/>
+      <c r="V13" s="5" t="n"/>
+      <c r="W13" s="5" t="n"/>
+      <c r="X13" s="5" t="n"/>
+      <c r="Y13" s="5" t="n"/>
+      <c r="Z13" s="9" t="n"/>
+    </row>
+    <row r="14" ht="36" customHeight="1">
+      <c r="B14" s="27" t="inlineStr">
         <is>
           <t>タブレットPOS端末アプリ</t>
-        </is>
-      </c>
-      <c r="C13" s="28" t="n"/>
-      <c r="D13" s="28" t="n"/>
-      <c r="E13" s="28" t="n"/>
-      <c r="F13" s="29" t="n"/>
-      <c r="G13" s="16" t="inlineStr">
-        <is>
-          <t>画面・業務判断、デバイス操作の依頼、処理結果の利用、デバイスコネクタプロセスの起動・停止管理。</t>
-        </is>
-      </c>
-      <c r="H13" s="28" t="n"/>
-      <c r="I13" s="28" t="n"/>
-      <c r="J13" s="28" t="n"/>
-      <c r="K13" s="28" t="n"/>
-      <c r="L13" s="28" t="n"/>
-      <c r="M13" s="28" t="n"/>
-      <c r="N13" s="28" t="n"/>
-      <c r="O13" s="28" t="n"/>
-      <c r="P13" s="29" t="n"/>
-      <c r="Q13" s="16" t="inlineStr">
-        <is>
-          <t>個別デバイスの実機制御、デバイスコネクタ内部処理の直接呼出し。</t>
-        </is>
-      </c>
-      <c r="R13" s="28" t="n"/>
-      <c r="S13" s="28" t="n"/>
-      <c r="T13" s="28" t="n"/>
-      <c r="U13" s="28" t="n"/>
-      <c r="V13" s="28" t="n"/>
-      <c r="W13" s="28" t="n"/>
-      <c r="X13" s="28" t="n"/>
-      <c r="Y13" s="28" t="n"/>
-      <c r="Z13" s="30" t="n"/>
-    </row>
-    <row r="14" ht="36" customHeight="1">
-      <c r="B14" s="31" t="inlineStr">
-        <is>
-          <t>デバイスコネクタ</t>
         </is>
       </c>
       <c r="C14" s="28" t="n"/>
       <c r="D14" s="28" t="n"/>
       <c r="E14" s="28" t="n"/>
       <c r="F14" s="29" t="n"/>
-      <c r="G14" s="32" t="inlineStr">
-        <is>
-          <t>プロセス間通信、要求順序制御、コマンド処理、デバイス管理、実機制御、非同期イベント配信。</t>
+      <c r="G14" s="16" t="inlineStr">
+        <is>
+          <t>画面・業務判断、デバイス操作の依頼、処理結果の利用、デバイスコネクタプロセスの起動・停止管理。</t>
         </is>
       </c>
       <c r="H14" s="28" t="n"/>
@@ -16354,9 +16140,9 @@
       <c r="N14" s="28" t="n"/>
       <c r="O14" s="28" t="n"/>
       <c r="P14" s="29" t="n"/>
-      <c r="Q14" s="32" t="inlineStr">
-        <is>
-          <t>画面表示、業務継続可否、ユーザー向けメッセージの決定。</t>
+      <c r="Q14" s="16" t="inlineStr">
+        <is>
+          <t>OPOS、OCX、ActiveX、既存DLL、およびデバイスコネクタ内部処理の直接呼出し。</t>
         </is>
       </c>
       <c r="R14" s="28" t="n"/>
@@ -16369,139 +16155,139 @@
       <c r="Y14" s="28" t="n"/>
       <c r="Z14" s="30" t="n"/>
     </row>
-    <row r="15" ht="36" customHeight="1">
-      <c r="B15" s="33" t="inlineStr">
+    <row r="15" ht="54" customHeight="1">
+      <c r="B15" s="31" t="inlineStr">
+        <is>
+          <t>デバイスコネクタ</t>
+        </is>
+      </c>
+      <c r="C15" s="28" t="n"/>
+      <c r="D15" s="28" t="n"/>
+      <c r="E15" s="28" t="n"/>
+      <c r="F15" s="29" t="n"/>
+      <c r="G15" s="32" t="inlineStr">
+        <is>
+          <t>プロセス間通信、要求順序制御、コマンド処理、デバイス管理、既存デバイス資源の呼出し、実機制御、非同期イベント配信。通常時は画面を表示せず、バックグラウンドで動作する。</t>
+        </is>
+      </c>
+      <c r="H15" s="28" t="n"/>
+      <c r="I15" s="28" t="n"/>
+      <c r="J15" s="28" t="n"/>
+      <c r="K15" s="28" t="n"/>
+      <c r="L15" s="28" t="n"/>
+      <c r="M15" s="28" t="n"/>
+      <c r="N15" s="28" t="n"/>
+      <c r="O15" s="28" t="n"/>
+      <c r="P15" s="29" t="n"/>
+      <c r="Q15" s="32" t="inlineStr">
+        <is>
+          <t>業務画面の表示、業務継続可否、ユーザー向けメッセージの決定。デバッグ用画面は保守・デバッグ時だけ表示する。</t>
+        </is>
+      </c>
+      <c r="R15" s="28" t="n"/>
+      <c r="S15" s="28" t="n"/>
+      <c r="T15" s="28" t="n"/>
+      <c r="U15" s="28" t="n"/>
+      <c r="V15" s="28" t="n"/>
+      <c r="W15" s="28" t="n"/>
+      <c r="X15" s="28" t="n"/>
+      <c r="Y15" s="28" t="n"/>
+      <c r="Z15" s="30" t="n"/>
+    </row>
+    <row r="16" ht="36" customHeight="1">
+      <c r="B16" s="33" t="inlineStr">
         <is>
           <t>周辺機器</t>
         </is>
       </c>
-      <c r="C15" s="34" t="n"/>
-      <c r="D15" s="34" t="n"/>
-      <c r="E15" s="34" t="n"/>
-      <c r="F15" s="35" t="n"/>
-      <c r="G15" s="36" t="inlineStr">
+      <c r="C16" s="34" t="n"/>
+      <c r="D16" s="34" t="n"/>
+      <c r="E16" s="34" t="n"/>
+      <c r="F16" s="35" t="n"/>
+      <c r="G16" s="36" t="inlineStr">
         <is>
           <t>釣銭、ドロア開放、カスタマーディスプレイ表示などの実処理。</t>
         </is>
       </c>
-      <c r="H15" s="34" t="n"/>
-      <c r="I15" s="34" t="n"/>
-      <c r="J15" s="34" t="n"/>
-      <c r="K15" s="34" t="n"/>
-      <c r="L15" s="34" t="n"/>
-      <c r="M15" s="34" t="n"/>
-      <c r="N15" s="34" t="n"/>
-      <c r="O15" s="34" t="n"/>
-      <c r="P15" s="35" t="n"/>
-      <c r="Q15" s="36" t="inlineStr">
+      <c r="H16" s="34" t="n"/>
+      <c r="I16" s="34" t="n"/>
+      <c r="J16" s="34" t="n"/>
+      <c r="K16" s="34" t="n"/>
+      <c r="L16" s="34" t="n"/>
+      <c r="M16" s="34" t="n"/>
+      <c r="N16" s="34" t="n"/>
+      <c r="O16" s="34" t="n"/>
+      <c r="P16" s="35" t="n"/>
+      <c r="Q16" s="36" t="inlineStr">
         <is>
           <t>アプリケーション層との直接通信。</t>
         </is>
       </c>
-      <c r="R15" s="34" t="n"/>
-      <c r="S15" s="34" t="n"/>
-      <c r="T15" s="34" t="n"/>
-      <c r="U15" s="34" t="n"/>
-      <c r="V15" s="34" t="n"/>
-      <c r="W15" s="34" t="n"/>
-      <c r="X15" s="34" t="n"/>
-      <c r="Y15" s="34" t="n"/>
-      <c r="Z15" s="37" t="n"/>
-    </row>
-    <row r="17" ht="18" customHeight="1">
-      <c r="B17" s="42" t="inlineStr">
+      <c r="R16" s="34" t="n"/>
+      <c r="S16" s="34" t="n"/>
+      <c r="T16" s="34" t="n"/>
+      <c r="U16" s="34" t="n"/>
+      <c r="V16" s="34" t="n"/>
+      <c r="W16" s="34" t="n"/>
+      <c r="X16" s="34" t="n"/>
+      <c r="Y16" s="34" t="n"/>
+      <c r="Z16" s="37" t="n"/>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="B18" s="44" t="inlineStr">
         <is>
           <t>■2.3 基本設計原則</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="20" customHeight="1">
-      <c r="B19" s="25" t="inlineStr">
+    <row r="20" ht="20" customHeight="1">
+      <c r="B20" s="25" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="C19" s="26" t="inlineStr">
+      <c r="C20" s="26" t="inlineStr">
         <is>
           <t>原則</t>
         </is>
       </c>
-      <c r="D19" s="5" t="n"/>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="5" t="n"/>
-      <c r="G19" s="5" t="n"/>
-      <c r="H19" s="6" t="n"/>
-      <c r="I19" s="26" t="inlineStr">
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="5" t="n"/>
+      <c r="H20" s="6" t="n"/>
+      <c r="I20" s="26" t="inlineStr">
         <is>
           <t>設計内容</t>
         </is>
       </c>
-      <c r="J19" s="5" t="n"/>
-      <c r="K19" s="5" t="n"/>
-      <c r="L19" s="5" t="n"/>
-      <c r="M19" s="5" t="n"/>
-      <c r="N19" s="5" t="n"/>
-      <c r="O19" s="5" t="n"/>
-      <c r="P19" s="5" t="n"/>
-      <c r="Q19" s="5" t="n"/>
-      <c r="R19" s="5" t="n"/>
-      <c r="S19" s="5" t="n"/>
-      <c r="T19" s="5" t="n"/>
-      <c r="U19" s="5" t="n"/>
-      <c r="V19" s="5" t="n"/>
-      <c r="W19" s="5" t="n"/>
-      <c r="X19" s="5" t="n"/>
-      <c r="Y19" s="5" t="n"/>
-      <c r="Z19" s="9" t="n"/>
-    </row>
-    <row r="20" ht="24" customHeight="1">
-      <c r="B20" s="27" t="inlineStr">
+      <c r="J20" s="5" t="n"/>
+      <c r="K20" s="5" t="n"/>
+      <c r="L20" s="5" t="n"/>
+      <c r="M20" s="5" t="n"/>
+      <c r="N20" s="5" t="n"/>
+      <c r="O20" s="5" t="n"/>
+      <c r="P20" s="5" t="n"/>
+      <c r="Q20" s="5" t="n"/>
+      <c r="R20" s="5" t="n"/>
+      <c r="S20" s="5" t="n"/>
+      <c r="T20" s="5" t="n"/>
+      <c r="U20" s="5" t="n"/>
+      <c r="V20" s="5" t="n"/>
+      <c r="W20" s="5" t="n"/>
+      <c r="X20" s="5" t="n"/>
+      <c r="Y20" s="5" t="n"/>
+      <c r="Z20" s="9" t="n"/>
+    </row>
+    <row r="21" ht="24" customHeight="1">
+      <c r="B21" s="27" t="inlineStr">
         <is>
           <t>①</t>
         </is>
       </c>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>責務分離</t>
-        </is>
-      </c>
-      <c r="D20" s="28" t="n"/>
-      <c r="E20" s="28" t="n"/>
-      <c r="F20" s="28" t="n"/>
-      <c r="G20" s="28" t="n"/>
-      <c r="H20" s="29" t="n"/>
-      <c r="I20" s="16" t="inlineStr">
-        <is>
-          <t>業務判断、通信制御、実機制御を分離し、各責務を越えた直接呼出しを行わない。</t>
-        </is>
-      </c>
-      <c r="J20" s="28" t="n"/>
-      <c r="K20" s="28" t="n"/>
-      <c r="L20" s="28" t="n"/>
-      <c r="M20" s="28" t="n"/>
-      <c r="N20" s="28" t="n"/>
-      <c r="O20" s="28" t="n"/>
-      <c r="P20" s="28" t="n"/>
-      <c r="Q20" s="28" t="n"/>
-      <c r="R20" s="28" t="n"/>
-      <c r="S20" s="28" t="n"/>
-      <c r="T20" s="28" t="n"/>
-      <c r="U20" s="28" t="n"/>
-      <c r="V20" s="28" t="n"/>
-      <c r="W20" s="28" t="n"/>
-      <c r="X20" s="28" t="n"/>
-      <c r="Y20" s="28" t="n"/>
-      <c r="Z20" s="30" t="n"/>
-    </row>
-    <row r="21" ht="24" customHeight="1">
-      <c r="B21" s="31" t="inlineStr">
-        <is>
-          <t>②</t>
-        </is>
-      </c>
-      <c r="C21" s="32" t="inlineStr">
-        <is>
-          <t>通信分離</t>
+      <c r="C21" s="16" t="inlineStr">
+        <is>
+          <t>既存デバイス互換</t>
         </is>
       </c>
       <c r="D21" s="28" t="n"/>
@@ -16509,9 +16295,9 @@
       <c r="F21" s="28" t="n"/>
       <c r="G21" s="28" t="n"/>
       <c r="H21" s="29" t="n"/>
-      <c r="I21" s="32" t="inlineStr">
-        <is>
-          <t>コマンド要求と同期応答はコマンド通信用パイプ、デバイス処理結果通知はイベント通知用パイプで扱う。</t>
+      <c r="I21" s="16" t="inlineStr">
+        <is>
+          <t>MAUIアプリから直接利用しないOPOS、OCX、ActiveX、および既存DLLをデバイスコネクタ内部へ閉じ込める。</t>
         </is>
       </c>
       <c r="J21" s="28" t="n"/>
@@ -16533,14 +16319,14 @@
       <c r="Z21" s="30" t="n"/>
     </row>
     <row r="22" ht="24" customHeight="1">
-      <c r="B22" s="27" t="inlineStr">
-        <is>
-          <t>③</t>
-        </is>
-      </c>
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>順序保証</t>
+      <c r="B22" s="31" t="inlineStr">
+        <is>
+          <t>②</t>
+        </is>
+      </c>
+      <c r="C22" s="32" t="inlineStr">
+        <is>
+          <t>責務分離</t>
         </is>
       </c>
       <c r="D22" s="28" t="n"/>
@@ -16548,9 +16334,9 @@
       <c r="F22" s="28" t="n"/>
       <c r="G22" s="28" t="n"/>
       <c r="H22" s="29" t="n"/>
-      <c r="I22" s="16" t="inlineStr">
-        <is>
-          <t>同一デバイスIDの要求は投入順に処理し、異なるデバイスIDの要求は互いに処理を妨げない。</t>
+      <c r="I22" s="32" t="inlineStr">
+        <is>
+          <t>業務判断、通信制御、実機制御を分離し、各責務を越えた直接呼出しを行わない。</t>
         </is>
       </c>
       <c r="J22" s="28" t="n"/>
@@ -16572,14 +16358,14 @@
       <c r="Z22" s="30" t="n"/>
     </row>
     <row r="23" ht="24" customHeight="1">
-      <c r="B23" s="31" t="inlineStr">
-        <is>
-          <t>④</t>
-        </is>
-      </c>
-      <c r="C23" s="32" t="inlineStr">
-        <is>
-          <t>二重実行防止</t>
+      <c r="B23" s="27" t="inlineStr">
+        <is>
+          <t>③</t>
+        </is>
+      </c>
+      <c r="C23" s="16" t="inlineStr">
+        <is>
+          <t>通信分離</t>
         </is>
       </c>
       <c r="D23" s="28" t="n"/>
@@ -16587,9 +16373,9 @@
       <c r="F23" s="28" t="n"/>
       <c r="G23" s="28" t="n"/>
       <c r="H23" s="29" t="n"/>
-      <c r="I23" s="32" t="inlineStr">
-        <is>
-          <t>通信接続の再試行は要求送信前に限定し、送信後に結果を確定できない場合も同一要求を自動再送しない。</t>
+      <c r="I23" s="16" t="inlineStr">
+        <is>
+          <t>コマンド要求と同期応答はコマンド通信用パイプ、デバイス処理結果通知はイベント通知用パイプで扱う。</t>
         </is>
       </c>
       <c r="J23" s="28" t="n"/>
@@ -16611,14 +16397,14 @@
       <c r="Z23" s="30" t="n"/>
     </row>
     <row r="24" ht="24" customHeight="1">
-      <c r="B24" s="27" t="inlineStr">
-        <is>
-          <t>⑤</t>
-        </is>
-      </c>
-      <c r="C24" s="16" t="inlineStr">
-        <is>
-          <t>安全なライフサイクル</t>
+      <c r="B24" s="31" t="inlineStr">
+        <is>
+          <t>④</t>
+        </is>
+      </c>
+      <c r="C24" s="32" t="inlineStr">
+        <is>
+          <t>順序保証</t>
         </is>
       </c>
       <c r="D24" s="28" t="n"/>
@@ -16626,9 +16412,9 @@
       <c r="F24" s="28" t="n"/>
       <c r="G24" s="28" t="n"/>
       <c r="H24" s="29" t="n"/>
-      <c r="I24" s="16" t="inlineStr">
-        <is>
-          <t>アプリケーション層は自ら起動したデバイスコネクタだけを停止対象とし、非所有プロセスを停止しない。</t>
+      <c r="I24" s="32" t="inlineStr">
+        <is>
+          <t>同一デバイスIDの要求は投入順に処理し、異なるデバイスIDの要求は互いに処理を妨げない。</t>
         </is>
       </c>
       <c r="J24" s="28" t="n"/>
@@ -16650,184 +16436,265 @@
       <c r="Z24" s="30" t="n"/>
     </row>
     <row r="25" ht="24" customHeight="1">
-      <c r="B25" s="43" t="inlineStr">
+      <c r="B25" s="27" t="inlineStr">
+        <is>
+          <t>⑤</t>
+        </is>
+      </c>
+      <c r="C25" s="16" t="inlineStr">
+        <is>
+          <t>二重実行防止</t>
+        </is>
+      </c>
+      <c r="D25" s="28" t="n"/>
+      <c r="E25" s="28" t="n"/>
+      <c r="F25" s="28" t="n"/>
+      <c r="G25" s="28" t="n"/>
+      <c r="H25" s="29" t="n"/>
+      <c r="I25" s="16" t="inlineStr">
+        <is>
+          <t>通信接続の再試行は要求送信前に限定し、送信後に結果を確定できない場合も同一要求を自動再送しない。</t>
+        </is>
+      </c>
+      <c r="J25" s="28" t="n"/>
+      <c r="K25" s="28" t="n"/>
+      <c r="L25" s="28" t="n"/>
+      <c r="M25" s="28" t="n"/>
+      <c r="N25" s="28" t="n"/>
+      <c r="O25" s="28" t="n"/>
+      <c r="P25" s="28" t="n"/>
+      <c r="Q25" s="28" t="n"/>
+      <c r="R25" s="28" t="n"/>
+      <c r="S25" s="28" t="n"/>
+      <c r="T25" s="28" t="n"/>
+      <c r="U25" s="28" t="n"/>
+      <c r="V25" s="28" t="n"/>
+      <c r="W25" s="28" t="n"/>
+      <c r="X25" s="28" t="n"/>
+      <c r="Y25" s="28" t="n"/>
+      <c r="Z25" s="30" t="n"/>
+    </row>
+    <row r="26" ht="24" customHeight="1">
+      <c r="B26" s="31" t="inlineStr">
         <is>
           <t>⑥</t>
         </is>
       </c>
-      <c r="C25" s="44" t="inlineStr">
+      <c r="C26" s="32" t="inlineStr">
+        <is>
+          <t>安全なライフサイクル</t>
+        </is>
+      </c>
+      <c r="D26" s="28" t="n"/>
+      <c r="E26" s="28" t="n"/>
+      <c r="F26" s="28" t="n"/>
+      <c r="G26" s="28" t="n"/>
+      <c r="H26" s="29" t="n"/>
+      <c r="I26" s="32" t="inlineStr">
+        <is>
+          <t>アプリケーション層は自ら起動したデバイスコネクタだけを停止対象とし、非所有プロセスを停止しない。</t>
+        </is>
+      </c>
+      <c r="J26" s="28" t="n"/>
+      <c r="K26" s="28" t="n"/>
+      <c r="L26" s="28" t="n"/>
+      <c r="M26" s="28" t="n"/>
+      <c r="N26" s="28" t="n"/>
+      <c r="O26" s="28" t="n"/>
+      <c r="P26" s="28" t="n"/>
+      <c r="Q26" s="28" t="n"/>
+      <c r="R26" s="28" t="n"/>
+      <c r="S26" s="28" t="n"/>
+      <c r="T26" s="28" t="n"/>
+      <c r="U26" s="28" t="n"/>
+      <c r="V26" s="28" t="n"/>
+      <c r="W26" s="28" t="n"/>
+      <c r="X26" s="28" t="n"/>
+      <c r="Y26" s="28" t="n"/>
+      <c r="Z26" s="30" t="n"/>
+    </row>
+    <row r="27" ht="24" customHeight="1">
+      <c r="B27" s="33" t="inlineStr">
+        <is>
+          <t>⑦</t>
+        </is>
+      </c>
+      <c r="C27" s="36" t="inlineStr">
         <is>
           <t>設定責務の分離</t>
         </is>
       </c>
-      <c r="D25" s="34" t="n"/>
-      <c r="E25" s="34" t="n"/>
-      <c r="F25" s="34" t="n"/>
-      <c r="G25" s="34" t="n"/>
-      <c r="H25" s="35" t="n"/>
-      <c r="I25" s="44" t="inlineStr">
-        <is>
-          <t>アプリ側設定は使用する制御方式、デバイスコネクタ側設定は起動するデバイス実装を決定する。</t>
-        </is>
-      </c>
-      <c r="J25" s="34" t="n"/>
-      <c r="K25" s="34" t="n"/>
-      <c r="L25" s="34" t="n"/>
-      <c r="M25" s="34" t="n"/>
-      <c r="N25" s="34" t="n"/>
-      <c r="O25" s="34" t="n"/>
-      <c r="P25" s="34" t="n"/>
-      <c r="Q25" s="34" t="n"/>
-      <c r="R25" s="34" t="n"/>
-      <c r="S25" s="34" t="n"/>
-      <c r="T25" s="34" t="n"/>
-      <c r="U25" s="34" t="n"/>
-      <c r="V25" s="34" t="n"/>
-      <c r="W25" s="34" t="n"/>
-      <c r="X25" s="34" t="n"/>
-      <c r="Y25" s="34" t="n"/>
-      <c r="Z25" s="37" t="n"/>
-    </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="B27" s="42" t="inlineStr">
+      <c r="D27" s="34" t="n"/>
+      <c r="E27" s="34" t="n"/>
+      <c r="F27" s="34" t="n"/>
+      <c r="G27" s="34" t="n"/>
+      <c r="H27" s="35" t="n"/>
+      <c r="I27" s="36" t="inlineStr">
+        <is>
+          <t>アプリ側設定は使用する制御方式、デバイスコネクタ側設定は起動するホスト内部実装を決定する。</t>
+        </is>
+      </c>
+      <c r="J27" s="34" t="n"/>
+      <c r="K27" s="34" t="n"/>
+      <c r="L27" s="34" t="n"/>
+      <c r="M27" s="34" t="n"/>
+      <c r="N27" s="34" t="n"/>
+      <c r="O27" s="34" t="n"/>
+      <c r="P27" s="34" t="n"/>
+      <c r="Q27" s="34" t="n"/>
+      <c r="R27" s="34" t="n"/>
+      <c r="S27" s="34" t="n"/>
+      <c r="T27" s="34" t="n"/>
+      <c r="U27" s="34" t="n"/>
+      <c r="V27" s="34" t="n"/>
+      <c r="W27" s="34" t="n"/>
+      <c r="X27" s="34" t="n"/>
+      <c r="Y27" s="34" t="n"/>
+      <c r="Z27" s="37" t="n"/>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="B29" s="44" t="inlineStr">
         <is>
           <t>■2.4 本書の読み方</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="B29" s="24" t="inlineStr">
+    <row r="31" ht="18" customHeight="1">
+      <c r="B31" s="24" t="inlineStr">
         <is>
           <t>本書は、対象範囲から実装対応までを次の順序で確認する。各章は、前の章で定義した内容を次の観点へ具体化する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="C30" s="24" t="inlineStr">
-        <is>
-          <t>① 03_対象範囲では、設計対象となる責務、対象デバイス、および対象外を確認する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="18" customHeight="1">
-      <c r="C31" s="24" t="inlineStr">
-        <is>
-          <t>② 05_全体構成では、対象範囲を担う責務領域、責務グループ、および論理構成要素の関係を確認する。</t>
         </is>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="C32" s="24" t="inlineStr">
         <is>
-          <t>③ 06_運用シナリオでは、各構成要素が起動、デバイス操作、非同期イベント、および終了でどのように連携するかを確認する。</t>
+          <t>① 03_対象範囲では、設計対象となる責務、対象デバイス、および対象外を確認する。</t>
         </is>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="C33" s="24" t="inlineStr">
         <is>
-          <t>④ 07_機能設計では、全体構成の責務と運用シナリオを実現する機能、および各機能の正常時・異常時の扱いを確認する。</t>
+          <t>② 05_全体構成では、対象範囲を担う責務領域、責務グループ、および論理構成要素の関係を確認する。</t>
         </is>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="C34" s="24" t="inlineStr">
         <is>
-          <t>⑤ 08_通信・データ設計と09_設定・デバイス設計では、機能を実行するための通信契約、データ項目、設定責務、およびデバイス対応を確認する。</t>
+          <t>③ 06_運用シナリオでは、各構成要素が起動、デバイス操作、非同期イベント、および終了でどのように連携するかを確認する。</t>
         </is>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="C35" s="24" t="inlineStr">
         <is>
-          <t>⑥ 10_異常・運用設計では、各処理で発生する異常の分類、復旧方法、およびログ出力を確認する。</t>
+          <t>④ 07_機能設計では、全体構成の責務と運用シナリオを実現する機能、および各機能の正常時・異常時の扱いを確認する。</t>
         </is>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="C36" s="24" t="inlineStr">
         <is>
+          <t>⑤ 08_通信・データ設計と09_設定・デバイス設計では、機能を実行するための通信契約、データ項目、設定責務、およびデバイス対応を確認する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="C37" s="24" t="inlineStr">
+        <is>
+          <t>⑥ 10_異常・運用設計では、各処理で発生する異常の分類、復旧方法、およびログ出力を確認する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="C38" s="24" t="inlineStr">
+        <is>
           <t>⑦ 11_実装対応では、論理構成要素と機能が実装上のクラスおよび関連仕様へどのように対応するかを確認する。</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="18" customHeight="1">
-      <c r="B37" s="24" t="inlineStr">
+    <row r="39" ht="18" customHeight="1">
+      <c r="B39" s="24" t="inlineStr">
         <is>
           <t>レビューでは、対象範囲、責務、運用シナリオ、機能、通信・設定、異常時の扱い、および実装対応が一つの流れとして矛盾していないことを確認する。</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="18" customHeight="1">
-      <c r="B38" s="42" t="inlineStr">
+    <row r="40" ht="18" customHeight="1">
+      <c r="B40" s="44" t="inlineStr">
         <is>
           <t>■2.5 レビュー判断</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="28" customHeight="1">
-      <c r="B40" s="24" t="inlineStr">
+    <row r="42" ht="28" customHeight="1">
+      <c r="B42" s="24" t="inlineStr">
         <is>
           <t>責務境界、運用シナリオ、通信契約、設定責務、異常時の継続・停止条件、および実装対応が相互に矛盾していないことを確認し、デバイスコネクタ基本設計としての妥当性を判断する。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="57">
+  <mergeCells count="60">
     <mergeCell ref="G14:P14"/>
     <mergeCell ref="C25:H25"/>
-    <mergeCell ref="B38:Z38"/>
+    <mergeCell ref="C26:H26"/>
     <mergeCell ref="C35:Z35"/>
     <mergeCell ref="B10:Z10"/>
+    <mergeCell ref="B16:F16"/>
     <mergeCell ref="C22:H22"/>
     <mergeCell ref="I25:Z25"/>
-    <mergeCell ref="B37:Z37"/>
     <mergeCell ref="B40:Z40"/>
     <mergeCell ref="B9:Z9"/>
     <mergeCell ref="Q15:Z15"/>
     <mergeCell ref="I22:Z22"/>
     <mergeCell ref="W2:X3"/>
-    <mergeCell ref="C31:Z31"/>
     <mergeCell ref="B6:Z6"/>
+    <mergeCell ref="G16:P16"/>
     <mergeCell ref="C21:H21"/>
     <mergeCell ref="H2:Q3"/>
-    <mergeCell ref="B12:F12"/>
     <mergeCell ref="T1:V1"/>
     <mergeCell ref="I21:Z21"/>
     <mergeCell ref="I24:Z24"/>
     <mergeCell ref="B5:Z5"/>
+    <mergeCell ref="C27:H27"/>
     <mergeCell ref="Q13:Z13"/>
     <mergeCell ref="W1:X1"/>
-    <mergeCell ref="G12:P12"/>
     <mergeCell ref="C23:H23"/>
     <mergeCell ref="Y1:Z1"/>
     <mergeCell ref="R2:S3"/>
-    <mergeCell ref="Q12:Z12"/>
+    <mergeCell ref="Q16:Z16"/>
     <mergeCell ref="B14:F14"/>
     <mergeCell ref="C36:Z36"/>
     <mergeCell ref="H1:Q1"/>
     <mergeCell ref="I23:Z23"/>
     <mergeCell ref="B13:F13"/>
-    <mergeCell ref="C19:H19"/>
     <mergeCell ref="I20:Z20"/>
     <mergeCell ref="A1:D3"/>
     <mergeCell ref="C32:Z32"/>
-    <mergeCell ref="I19:Z19"/>
-    <mergeCell ref="B27:Z27"/>
+    <mergeCell ref="C38:Z38"/>
+    <mergeCell ref="B31:Z31"/>
+    <mergeCell ref="C37:Z37"/>
+    <mergeCell ref="B18:Z18"/>
     <mergeCell ref="Q14:Z14"/>
     <mergeCell ref="B29:Z29"/>
+    <mergeCell ref="B39:Z39"/>
+    <mergeCell ref="B11:Z11"/>
     <mergeCell ref="T2:V3"/>
     <mergeCell ref="G13:P13"/>
     <mergeCell ref="C24:H24"/>
     <mergeCell ref="E2:G3"/>
-    <mergeCell ref="C30:Z30"/>
     <mergeCell ref="C34:Z34"/>
+    <mergeCell ref="B42:Z42"/>
     <mergeCell ref="B15:F15"/>
     <mergeCell ref="Y2:Z3"/>
-    <mergeCell ref="B17:Z17"/>
+    <mergeCell ref="I27:Z27"/>
     <mergeCell ref="C33:Z33"/>
     <mergeCell ref="B8:Z8"/>
     <mergeCell ref="G15:P15"/>
+    <mergeCell ref="I26:Z26"/>
     <mergeCell ref="R1:S1"/>
     <mergeCell ref="E1:G1"/>
     <mergeCell ref="C20:H20"/>
@@ -16852,7 +16719,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Z29"/>
+  <dimension ref="A1:Z34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -16986,7 +16853,7 @@
       <c r="X2" s="15" t="n"/>
       <c r="Y2" s="17" t="inlineStr">
         <is>
-          <t>2026/07/13</t>
+          <t>2026/07/14</t>
         </is>
       </c>
       <c r="Z2" s="18" t="n"/>
@@ -17027,7 +16894,7 @@
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="B6" s="42" t="inlineStr">
+      <c r="B6" s="44" t="inlineStr">
         <is>
           <t>■3.1 対象</t>
         </is>
@@ -17069,116 +16936,80 @@
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="B13" s="42" t="inlineStr">
+      <c r="C13" s="24" t="inlineStr">
+        <is>
+          <t>⑥ 既存デバイス資源を一つのデバイスコネクタプロセスで管理し、通常時はバックグラウンドで動作させる実行形態。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="B14" s="44" t="inlineStr">
         <is>
           <t>■3.2 対象デバイス</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="28" customHeight="1">
-      <c r="B15" s="24" t="inlineStr">
+    <row r="16" ht="28" customHeight="1">
+      <c r="B16" s="24" t="inlineStr">
         <is>
           <t>初期対象は、RT-300釣銭機、SHARPキャッシュドロア、SHARPカスタマーディスプレイの3種類とする。アプリ側設定とデバイスコネクタ側設定は、次のデバイスIDで対応付ける。</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="B16" s="45" t="inlineStr">
+    <row r="17" ht="18" customHeight="1">
+      <c r="B17" s="45" t="inlineStr">
         <is>
           <t>■3.2.1 デバイスID対応</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="B18" s="25" t="inlineStr">
+    <row r="19" ht="20" customHeight="1">
+      <c r="B19" s="25" t="inlineStr">
         <is>
           <t>アプリ側有効デバイス区分</t>
         </is>
       </c>
-      <c r="C18" s="5" t="n"/>
-      <c r="D18" s="5" t="n"/>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="5" t="n"/>
-      <c r="G18" s="6" t="n"/>
-      <c r="H18" s="26" t="inlineStr">
+      <c r="C19" s="5" t="n"/>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="6" t="n"/>
+      <c r="H19" s="26" t="inlineStr">
         <is>
           <t>アプリ側設定ID</t>
         </is>
       </c>
-      <c r="I18" s="5" t="n"/>
-      <c r="J18" s="5" t="n"/>
-      <c r="K18" s="5" t="n"/>
-      <c r="L18" s="5" t="n"/>
-      <c r="M18" s="5" t="n"/>
-      <c r="N18" s="6" t="n"/>
-      <c r="O18" s="26" t="inlineStr">
+      <c r="I19" s="5" t="n"/>
+      <c r="J19" s="5" t="n"/>
+      <c r="K19" s="5" t="n"/>
+      <c r="L19" s="5" t="n"/>
+      <c r="M19" s="5" t="n"/>
+      <c r="N19" s="6" t="n"/>
+      <c r="O19" s="26" t="inlineStr">
         <is>
           <t>デバイスコネクタ要求のデバイスID（DeviceId）</t>
         </is>
       </c>
-      <c r="P18" s="5" t="n"/>
-      <c r="Q18" s="5" t="n"/>
-      <c r="R18" s="5" t="n"/>
-      <c r="S18" s="5" t="n"/>
-      <c r="T18" s="5" t="n"/>
-      <c r="U18" s="6" t="n"/>
-      <c r="V18" s="26" t="inlineStr">
+      <c r="P19" s="5" t="n"/>
+      <c r="Q19" s="5" t="n"/>
+      <c r="R19" s="5" t="n"/>
+      <c r="S19" s="5" t="n"/>
+      <c r="T19" s="5" t="n"/>
+      <c r="U19" s="6" t="n"/>
+      <c r="V19" s="26" t="inlineStr">
         <is>
           <t>デバイスコネクタ側設定例</t>
         </is>
       </c>
-      <c r="W18" s="5" t="n"/>
-      <c r="X18" s="5" t="n"/>
-      <c r="Y18" s="5" t="n"/>
-      <c r="Z18" s="9" t="n"/>
-    </row>
-    <row r="19" ht="24" customHeight="1">
-      <c r="B19" s="27" t="inlineStr">
+      <c r="W19" s="5" t="n"/>
+      <c r="X19" s="5" t="n"/>
+      <c r="Y19" s="5" t="n"/>
+      <c r="Z19" s="9" t="n"/>
+    </row>
+    <row r="20" ht="24" customHeight="1">
+      <c r="B20" s="27" t="inlineStr">
         <is>
           <t>local_cashchanger</t>
-        </is>
-      </c>
-      <c r="C19" s="28" t="n"/>
-      <c r="D19" s="28" t="n"/>
-      <c r="E19" s="28" t="n"/>
-      <c r="F19" s="28" t="n"/>
-      <c r="G19" s="29" t="n"/>
-      <c r="H19" s="46" t="inlineStr">
-        <is>
-          <t>cash_changer_glory_rt300_windows</t>
-        </is>
-      </c>
-      <c r="I19" s="28" t="n"/>
-      <c r="J19" s="28" t="n"/>
-      <c r="K19" s="28" t="n"/>
-      <c r="L19" s="28" t="n"/>
-      <c r="M19" s="28" t="n"/>
-      <c r="N19" s="29" t="n"/>
-      <c r="O19" s="16" t="inlineStr">
-        <is>
-          <t>釣銭機（CashChanger）</t>
-        </is>
-      </c>
-      <c r="P19" s="28" t="n"/>
-      <c r="Q19" s="28" t="n"/>
-      <c r="R19" s="28" t="n"/>
-      <c r="S19" s="28" t="n"/>
-      <c r="T19" s="28" t="n"/>
-      <c r="U19" s="29" t="n"/>
-      <c r="V19" s="16" t="inlineStr">
-        <is>
-          <t>CashChanger / CashChanger1</t>
-        </is>
-      </c>
-      <c r="W19" s="28" t="n"/>
-      <c r="X19" s="28" t="n"/>
-      <c r="Y19" s="28" t="n"/>
-      <c r="Z19" s="30" t="n"/>
-    </row>
-    <row r="20" ht="24" customHeight="1">
-      <c r="B20" s="31" t="inlineStr">
-        <is>
-          <t>local_drawer</t>
         </is>
       </c>
       <c r="C20" s="28" t="n"/>
@@ -17186,9 +17017,9 @@
       <c r="E20" s="28" t="n"/>
       <c r="F20" s="28" t="n"/>
       <c r="G20" s="29" t="n"/>
-      <c r="H20" s="47" t="inlineStr">
-        <is>
-          <t>drawer_external_windows</t>
+      <c r="H20" s="46" t="inlineStr">
+        <is>
+          <t>cash_changer_glory_rt300_windows</t>
         </is>
       </c>
       <c r="I20" s="28" t="n"/>
@@ -17197,9 +17028,9 @@
       <c r="L20" s="28" t="n"/>
       <c r="M20" s="28" t="n"/>
       <c r="N20" s="29" t="n"/>
-      <c r="O20" s="32" t="inlineStr">
-        <is>
-          <t>キャッシュドロア（CashDrawer）</t>
+      <c r="O20" s="16" t="inlineStr">
+        <is>
+          <t>釣銭機（CashChanger）</t>
         </is>
       </c>
       <c r="P20" s="28" t="n"/>
@@ -17208,9 +17039,9 @@
       <c r="S20" s="28" t="n"/>
       <c r="T20" s="28" t="n"/>
       <c r="U20" s="29" t="n"/>
-      <c r="V20" s="32" t="inlineStr">
-        <is>
-          <t>CashDrawer / CashDrawer1</t>
+      <c r="V20" s="16" t="inlineStr">
+        <is>
+          <t>CashChanger / CashChanger1</t>
         </is>
       </c>
       <c r="W20" s="28" t="n"/>
@@ -17218,106 +17049,171 @@
       <c r="Y20" s="28" t="n"/>
       <c r="Z20" s="30" t="n"/>
     </row>
-    <row r="21" ht="36" customHeight="1">
-      <c r="B21" s="33" t="inlineStr">
+    <row r="21" ht="24" customHeight="1">
+      <c r="B21" s="31" t="inlineStr">
+        <is>
+          <t>local_drawer</t>
+        </is>
+      </c>
+      <c r="C21" s="28" t="n"/>
+      <c r="D21" s="28" t="n"/>
+      <c r="E21" s="28" t="n"/>
+      <c r="F21" s="28" t="n"/>
+      <c r="G21" s="29" t="n"/>
+      <c r="H21" s="47" t="inlineStr">
+        <is>
+          <t>drawer_external_windows</t>
+        </is>
+      </c>
+      <c r="I21" s="28" t="n"/>
+      <c r="J21" s="28" t="n"/>
+      <c r="K21" s="28" t="n"/>
+      <c r="L21" s="28" t="n"/>
+      <c r="M21" s="28" t="n"/>
+      <c r="N21" s="29" t="n"/>
+      <c r="O21" s="32" t="inlineStr">
+        <is>
+          <t>キャッシュドロア（CashDrawer）</t>
+        </is>
+      </c>
+      <c r="P21" s="28" t="n"/>
+      <c r="Q21" s="28" t="n"/>
+      <c r="R21" s="28" t="n"/>
+      <c r="S21" s="28" t="n"/>
+      <c r="T21" s="28" t="n"/>
+      <c r="U21" s="29" t="n"/>
+      <c r="V21" s="32" t="inlineStr">
+        <is>
+          <t>CashDrawer / CashDrawer1</t>
+        </is>
+      </c>
+      <c r="W21" s="28" t="n"/>
+      <c r="X21" s="28" t="n"/>
+      <c r="Y21" s="28" t="n"/>
+      <c r="Z21" s="30" t="n"/>
+    </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="B22" s="33" t="inlineStr">
         <is>
           <t>local_display</t>
         </is>
       </c>
-      <c r="C21" s="34" t="n"/>
-      <c r="D21" s="34" t="n"/>
-      <c r="E21" s="34" t="n"/>
-      <c r="F21" s="34" t="n"/>
-      <c r="G21" s="35" t="n"/>
-      <c r="H21" s="48" t="inlineStr">
+      <c r="C22" s="34" t="n"/>
+      <c r="D22" s="34" t="n"/>
+      <c r="E22" s="34" t="n"/>
+      <c r="F22" s="34" t="n"/>
+      <c r="G22" s="35" t="n"/>
+      <c r="H22" s="48" t="inlineStr">
         <is>
           <t>customer_display_sharp_windows</t>
         </is>
       </c>
-      <c r="I21" s="34" t="n"/>
-      <c r="J21" s="34" t="n"/>
-      <c r="K21" s="34" t="n"/>
-      <c r="L21" s="34" t="n"/>
-      <c r="M21" s="34" t="n"/>
-      <c r="N21" s="35" t="n"/>
-      <c r="O21" s="36" t="inlineStr">
+      <c r="I22" s="34" t="n"/>
+      <c r="J22" s="34" t="n"/>
+      <c r="K22" s="34" t="n"/>
+      <c r="L22" s="34" t="n"/>
+      <c r="M22" s="34" t="n"/>
+      <c r="N22" s="35" t="n"/>
+      <c r="O22" s="36" t="inlineStr">
         <is>
           <t>カスタマーディスプレイ（CustomerDisplay）</t>
         </is>
       </c>
-      <c r="P21" s="34" t="n"/>
-      <c r="Q21" s="34" t="n"/>
-      <c r="R21" s="34" t="n"/>
-      <c r="S21" s="34" t="n"/>
-      <c r="T21" s="34" t="n"/>
-      <c r="U21" s="35" t="n"/>
-      <c r="V21" s="36" t="inlineStr">
+      <c r="P22" s="34" t="n"/>
+      <c r="Q22" s="34" t="n"/>
+      <c r="R22" s="34" t="n"/>
+      <c r="S22" s="34" t="n"/>
+      <c r="T22" s="34" t="n"/>
+      <c r="U22" s="35" t="n"/>
+      <c r="V22" s="36" t="inlineStr">
         <is>
           <t>CustomerDisplay / LineDisplay1</t>
         </is>
       </c>
-      <c r="W21" s="34" t="n"/>
-      <c r="X21" s="34" t="n"/>
-      <c r="Y21" s="34" t="n"/>
-      <c r="Z21" s="37" t="n"/>
-    </row>
-    <row r="23" ht="18" customHeight="1">
-      <c r="B23" s="42" t="inlineStr">
+      <c r="W22" s="34" t="n"/>
+      <c r="X22" s="34" t="n"/>
+      <c r="Y22" s="34" t="n"/>
+      <c r="Z22" s="37" t="n"/>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="B24" s="44" t="inlineStr">
         <is>
           <t>■3.3 対象外</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="C25" s="24" t="inlineStr">
-        <is>
-          <t>① 画面項目、画面遷移、ユーザー向け文言、および業務継続可否の判断は、アプリ側設計で扱う。</t>
         </is>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="C26" s="24" t="inlineStr">
         <is>
-          <t>② デバイス制御内部の直接制御方式は対象外とし、デバイスコネクタ経由で既存デバイス資源を利用する範囲を対象とする。</t>
+          <t>① 画面項目、画面遷移、ユーザー向け文言、および業務継続可否の判断は、アプリ側設計で扱う。</t>
         </is>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="C27" s="24" t="inlineStr">
         <is>
-          <t>③ 個別クラスのprivateメソッド、内部変数、および実装上の詳細分岐は、プログラム仕様書で扱う。</t>
+          <t>② デバイス制御内部の直接制御方式は対象外とし、デバイスコネクタ経由で既存デバイス資源を利用する範囲を対象とする。</t>
         </is>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="C28" s="24" t="inlineStr">
         <is>
+          <t>③ 個別クラスのprivateメソッド、内部変数、および実装上の詳細分岐は、プログラム仕様書で扱う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="C29" s="24" t="inlineStr">
+        <is>
           <t>④ OPOS設定、ドライバー導入、および店舗での実機設定は、運用手順書または導入手順書で扱う。</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="28" customHeight="1">
-      <c r="C29" s="24" t="inlineStr">
+    <row r="30" ht="28" customHeight="1">
+      <c r="C30" s="24" t="inlineStr">
         <is>
           <t>⑤ プリンター、スキャナー、決済端末などの将来追加機器は初期対象に含めない。設定ファイルに候補として保持する場合も、Windows向けの有効デバイスには選択しない。</t>
         </is>
       </c>
     </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="B31" s="44" t="inlineStr">
+        <is>
+          <t>■3.4 将来機器の対応方針</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="28" customHeight="1">
+      <c r="B33" s="24" t="inlineStr">
+        <is>
+          <t>今後追加する機器は、既存のOPOS、OCX、ActiveX、または既存DLLを利用する必要がある場合を除き、iPadと同様に端末アプリから直接制御する。デバイスコネクタは、現行POSで使用している既存デバイスを継続利用する場合に限定して使用する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="B34" s="24" t="inlineStr">
+        <is>
+          <t>デバイスコネクタ経由で制御する既存デバイスの使用が終了した後は、デバイスコネクタを不要な資材として整理できる構成とする。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="45">
+  <mergeCells count="49">
     <mergeCell ref="C26:Z26"/>
     <mergeCell ref="H19:N19"/>
     <mergeCell ref="V21:Z21"/>
     <mergeCell ref="C29:Z29"/>
+    <mergeCell ref="H22:N22"/>
+    <mergeCell ref="B34:Z34"/>
     <mergeCell ref="C10:Z10"/>
-    <mergeCell ref="C25:Z25"/>
     <mergeCell ref="W2:X3"/>
     <mergeCell ref="B6:Z6"/>
-    <mergeCell ref="H18:N18"/>
     <mergeCell ref="C9:Z9"/>
-    <mergeCell ref="B15:Z15"/>
+    <mergeCell ref="B33:Z33"/>
     <mergeCell ref="B19:G19"/>
     <mergeCell ref="H2:Q3"/>
+    <mergeCell ref="B24:Z24"/>
     <mergeCell ref="T1:V1"/>
     <mergeCell ref="V20:Z20"/>
     <mergeCell ref="C12:Z12"/>
@@ -17332,22 +17228,25 @@
     <mergeCell ref="O19:U19"/>
     <mergeCell ref="H1:Q1"/>
     <mergeCell ref="C8:Z8"/>
-    <mergeCell ref="O18:U18"/>
     <mergeCell ref="B20:G20"/>
-    <mergeCell ref="B21:G21"/>
     <mergeCell ref="B16:Z16"/>
     <mergeCell ref="A1:D3"/>
+    <mergeCell ref="B31:Z31"/>
     <mergeCell ref="C28:Z28"/>
     <mergeCell ref="H21:N21"/>
     <mergeCell ref="O20:U20"/>
+    <mergeCell ref="C13:Z13"/>
     <mergeCell ref="T2:V3"/>
     <mergeCell ref="E2:G3"/>
+    <mergeCell ref="C30:Z30"/>
+    <mergeCell ref="B22:G22"/>
+    <mergeCell ref="B14:Z14"/>
+    <mergeCell ref="O22:U22"/>
     <mergeCell ref="Y2:Z3"/>
-    <mergeCell ref="B23:Z23"/>
-    <mergeCell ref="V18:Z18"/>
-    <mergeCell ref="B18:G18"/>
+    <mergeCell ref="B17:Z17"/>
+    <mergeCell ref="V22:Z22"/>
     <mergeCell ref="O21:U21"/>
-    <mergeCell ref="B13:Z13"/>
+    <mergeCell ref="B21:G21"/>
     <mergeCell ref="R1:S1"/>
     <mergeCell ref="E1:G1"/>
   </mergeCells>
@@ -17505,7 +17404,7 @@
       <c r="X2" s="15" t="n"/>
       <c r="Y2" s="17" t="inlineStr">
         <is>
-          <t>2026/07/13</t>
+          <t>2026/07/14</t>
         </is>
       </c>
       <c r="Z2" s="18" t="n"/>
@@ -18099,7 +17998,7 @@
       </c>
       <c r="C20" s="34" t="n"/>
       <c r="D20" s="35" t="n"/>
-      <c r="E20" s="44" t="inlineStr">
+      <c r="E20" s="39" t="inlineStr">
         <is>
           <t>カスタマーディスプレイ制御 SHARP</t>
         </is>
@@ -18113,7 +18012,7 @@
       <c r="L20" s="34" t="n"/>
       <c r="M20" s="34" t="n"/>
       <c r="N20" s="35" t="n"/>
-      <c r="O20" s="44" t="inlineStr">
+      <c r="O20" s="39" t="inlineStr">
         <is>
           <t>SHARPカスタマーディスプレイのプログラム仕様。</t>
         </is>
@@ -18212,7 +18111,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Z116"/>
+  <dimension ref="A1:Z117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -18346,7 +18245,7 @@
       <c r="X2" s="15" t="n"/>
       <c r="Y2" s="17" t="inlineStr">
         <is>
-          <t>2026/07/13</t>
+          <t>2026/07/14</t>
         </is>
       </c>
       <c r="Z2" s="18" t="n"/>
@@ -18387,7 +18286,7 @@
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="B6" s="42" t="inlineStr">
+      <c r="B6" s="44" t="inlineStr">
         <is>
           <t>■5.1 全体構成</t>
         </is>
@@ -18448,7 +18347,7 @@
       <c r="I12" s="58" t="n"/>
       <c r="J12" s="55" t="inlineStr">
         <is>
-          <t>通信、コマンド実行、デバイス管理、および実機制御を担当する独立プロセスを示す。</t>
+          <t>OPOS、OCX、ActiveX、および既存DLLを利用する既存デバイス制御を担当するWindows別プロセスを示す。</t>
         </is>
       </c>
     </row>
@@ -18833,29 +18732,36 @@
         </is>
       </c>
     </row>
-    <row r="114" ht="18" customHeight="1">
+    <row r="114" ht="28" customHeight="1">
       <c r="B114" s="55" t="inlineStr">
         <is>
-          <t>- タブレットPOS端末アプリとデバイスコネクタは同一Windows端末上の別プロセスであり、要求、応答、およびイベント通知には名前付きパイプを使用する。</t>
+          <t>- タブレットPOS端末アプリはMAUIプロセス、デバイスコネクタは既存デバイス資源を利用するWindows別プロセスとして、同一Windows端末上で動作する。要求、応答、およびイベント通知には名前付きパイプを使用する。</t>
         </is>
       </c>
     </row>
     <row r="115" ht="28" customHeight="1">
       <c r="B115" s="55" t="inlineStr">
         <is>
-          <t>- アプリケーション層はデバイスコネクタ内部を直接呼び出さない。デバイス操作はデバイス制御層を経由し、プロセスの起動・停止はデバイスコネクタプロセス管理が担当する。</t>
+          <t>- アプリケーション層はOPOS、OCX、ActiveX、既存DLL、またはデバイスコネクタ内部実装を直接呼び出さない。デバイス操作はデバイス制御層を経由し、プロセスの起動・停止はデバイスコネクタプロセス管理が担当する。</t>
         </is>
       </c>
     </row>
     <row r="116" ht="18" customHeight="1">
       <c r="B116" s="55" t="inlineStr">
         <is>
+          <t>- デバイスコネクタ側のホスト内部実装は、アプリ側のストラテジークラスではなく、既存デバイス資源を呼び出すための内部構成要素である。</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="18" customHeight="1">
+      <c r="B117" s="55" t="inlineStr">
+        <is>
           <t>- 再試行、タイムアウト、所有プロセス、および異常分岐は静的構成ではなく、06_運用シナリオで示す。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="58">
+  <mergeCells count="59">
     <mergeCell ref="B69:Z69"/>
     <mergeCell ref="J23:Z23"/>
     <mergeCell ref="B10:Z10"/>
@@ -18902,6 +18808,7 @@
     <mergeCell ref="J16:Z16"/>
     <mergeCell ref="J22:Z22"/>
     <mergeCell ref="T2:V3"/>
+    <mergeCell ref="B117:Z117"/>
     <mergeCell ref="E2:G3"/>
     <mergeCell ref="B15:I15"/>
     <mergeCell ref="B111:Z111"/>
@@ -18935,7 +18842,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Z54"/>
+  <dimension ref="A1:Z58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -19069,7 +18976,7 @@
       <c r="X2" s="15" t="n"/>
       <c r="Y2" s="17" t="inlineStr">
         <is>
-          <t>2026/07/13</t>
+          <t>2026/07/14</t>
         </is>
       </c>
       <c r="Z2" s="18" t="n"/>
@@ -19110,7 +19017,7 @@
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="B6" s="42" t="inlineStr">
+      <c r="B6" s="44" t="inlineStr">
         <is>
           <t>■5.2 構成の階層</t>
         </is>
@@ -19273,7 +19180,7 @@
       <c r="Z11" s="37" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="B13" s="42" t="inlineStr">
+      <c r="B13" s="44" t="inlineStr">
         <is>
           <t>■5.3 責務領域と構成要素</t>
         </is>
@@ -19294,42 +19201,42 @@
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="C17" s="95" t="inlineStr">
+      <c r="D17" s="95" t="inlineStr">
         <is>
           <t>①-1 画面・業務処理は、必要なデバイス操作を依頼し、同期結果または非同期イベントを業務処理へ反映する。</t>
         </is>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="C18" s="96" t="inlineStr">
+      <c r="D18" s="96" t="inlineStr">
         <is>
           <t>関連シート: 06_運用シナリオ_02、07_機能設計</t>
         </is>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="C19" s="95" t="inlineStr">
+      <c r="D19" s="95" t="inlineStr">
         <is>
           <t>①-2 アプリライフサイクルは、アプリの起動、再開、停止、および破棄をプロセス管理へ通知する。</t>
         </is>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="C20" s="96" t="inlineStr">
+      <c r="D20" s="96" t="inlineStr">
         <is>
           <t>関連シート: 06_運用シナリオ_02</t>
         </is>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="C21" s="95" t="inlineStr">
+      <c r="D21" s="95" t="inlineStr">
         <is>
           <t>①-3 デバイスコネクタプロセス管理は、存在確認、起動、稼働確認、停止要求、および所有プロセスの終了監視を行う。</t>
         </is>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="C22" s="96" t="inlineStr">
+      <c r="D22" s="96" t="inlineStr">
         <is>
           <t>関連シート: 06_運用シナリオ_02、07_機能設計、10_異常・運用設計</t>
         </is>
@@ -19343,42 +19250,42 @@
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
-      <c r="C24" s="95" t="inlineStr">
+      <c r="D24" s="95" t="inlineStr">
         <is>
           <t>②-1 設定・制御方式選択は、読み込み済み設定から有効デバイスとデバイスコネクタ経由の制御方式を選択する。</t>
         </is>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
-      <c r="C25" s="96" t="inlineStr">
+      <c r="D25" s="96" t="inlineStr">
         <is>
           <t>関連シート: 07_機能設計、09_設定・デバイス設計</t>
         </is>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
-      <c r="C26" s="95" t="inlineStr">
+      <c r="D26" s="95" t="inlineStr">
         <is>
           <t>②-2 コマンド通信は、要求を生成し、コマンド通信用パイプで送信して同期応答を受信する。</t>
         </is>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
-      <c r="C27" s="96" t="inlineStr">
+      <c r="D27" s="96" t="inlineStr">
         <is>
           <t>関連シート: 07_機能設計、08_通信・データ設計</t>
         </is>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
-      <c r="C28" s="95" t="inlineStr">
+      <c r="D28" s="95" t="inlineStr">
         <is>
           <t>②-3 結果・イベント連携は、同期応答と非同期イベントをアプリ内の結果形式へ変換して通知する。</t>
         </is>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
-      <c r="C29" s="96" t="inlineStr">
+      <c r="D29" s="96" t="inlineStr">
         <is>
           <t>関連シート: 07_機能設計、08_通信・データ設計、10_異常・運用設計</t>
         </is>
@@ -19387,7 +19294,7 @@
     <row r="30" ht="18" customHeight="1">
       <c r="B30" s="24" t="inlineStr">
         <is>
-          <t>（2）デバイスコネクタは、アプリから独立したプロセスとして要求制御と実機制御を担当する。</t>
+          <t>（2）デバイスコネクタは、MAUIアプリから直接利用しない既存デバイス資源をWindows別プロセス内に保持し、要求制御と実機制御を担当する。</t>
         </is>
       </c>
     </row>
@@ -19399,42 +19306,42 @@
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
-      <c r="C32" s="95" t="inlineStr">
+      <c r="D32" s="95" t="inlineStr">
         <is>
           <t>①-1 起動・停止管理は、通信サービスとデバイス管理を開始・停止し、稼働状態を管理する。</t>
         </is>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
-      <c r="C33" s="96" t="inlineStr">
+      <c r="D33" s="96" t="inlineStr">
         <is>
           <t>関連シート: 06_運用シナリオ_02、07_機能設計、10_異常・運用設計</t>
         </is>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
-      <c r="C34" s="95" t="inlineStr">
+      <c r="D34" s="95" t="inlineStr">
         <is>
           <t>①-2 コマンド受付は、一接続につき一要求を受け付け、同じ接続で同期応答を返す。</t>
         </is>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
-      <c r="C35" s="96" t="inlineStr">
+      <c r="D35" s="96" t="inlineStr">
         <is>
           <t>関連シート: 07_機能設計、08_通信・データ設計</t>
         </is>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
-      <c r="C36" s="95" t="inlineStr">
+      <c r="D36" s="95" t="inlineStr">
         <is>
           <t>①-3 イベント配信は、デバイス処理結果をイベント通知用パイプの接続先へ送信する。</t>
         </is>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
-      <c r="C37" s="96" t="inlineStr">
+      <c r="D37" s="96" t="inlineStr">
         <is>
           <t>関連シート: 07_機能設計、08_通信・データ設計</t>
         </is>
@@ -19448,63 +19355,63 @@
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
-      <c r="C39" s="95" t="inlineStr">
+      <c r="D39" s="95" t="inlineStr">
         <is>
           <t>②-1 デバイスID別順序制御は、同一デバイスIDの要求を投入順に処理する。</t>
         </is>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
-      <c r="C40" s="96" t="inlineStr">
+      <c r="D40" s="96" t="inlineStr">
         <is>
           <t>関連シート: 06_運用シナリオ_02、07_機能設計</t>
         </is>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
-      <c r="C41" s="95" t="inlineStr">
+      <c r="D41" s="95" t="inlineStr">
         <is>
           <t>②-2 要求変換・コマンド制御は、通信形式を内部要求へ変換し、制御要求またはデバイス操作要求として実行する。</t>
         </is>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
-      <c r="C42" s="96" t="inlineStr">
+      <c r="D42" s="96" t="inlineStr">
         <is>
           <t>関連シート: 07_機能設計、08_通信・データ設計、10_異常・運用設計</t>
         </is>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
-      <c r="C43" s="95" t="inlineStr">
+      <c r="D43" s="95" t="inlineStr">
         <is>
           <t>②-3 デバイス管理は、設定に基づくデバイス生成、保持、検索、実行、および停止を管理する。</t>
         </is>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
-      <c r="C44" s="96" t="inlineStr">
+      <c r="D44" s="96" t="inlineStr">
         <is>
           <t>関連シート: 07_機能設計、09_設定・デバイス設計、10_異常・運用設計</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="18" customHeight="1">
+    <row r="45" ht="28" customHeight="1">
       <c r="C45" s="24" t="inlineStr">
         <is>
-          <t>③ デバイスアダプターは、既存デバイス資源の差異をデバイスコネクタ内部へ閉じ込める。</t>
+          <t>③ 既存デバイス資源呼出しは、既存デバイス資源の差異をデバイスコネクタ内部へ閉じ込める。アプリ側のストラテジークラスではなく、既存デバイスを呼び出すためのホスト内部実装として扱う。</t>
         </is>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
-      <c r="C46" s="95" t="inlineStr">
-        <is>
-          <t>③-1 個別デバイス実装は、OPOS、OCX、共有メモリ、要求／応答ファイルなどを利用して実機を制御する。</t>
+      <c r="D46" s="95" t="inlineStr">
+        <is>
+          <t>③-1 ホスト内部実装は、OPOS、OCX、ActiveX、既存DLL、共有メモリ、要求／応答ファイルなどを利用して実機を制御する。</t>
         </is>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
-      <c r="C47" s="96" t="inlineStr">
+      <c r="D47" s="96" t="inlineStr">
         <is>
           <t>関連シート: 09_設定・デバイス設計、11_実装対応</t>
         </is>
@@ -19513,7 +19420,7 @@
     <row r="48" ht="18" customHeight="1">
       <c r="B48" s="24" t="inlineStr">
         <is>
-          <t>（3）周辺機器は、デバイスコネクタの個別デバイス実装から制御される店舗設備である。</t>
+          <t>（3）周辺機器は、デバイスコネクタのホスト内部実装から制御される店舗設備である。</t>
         </is>
       </c>
     </row>
@@ -19559,74 +19466,98 @@
         </is>
       </c>
     </row>
+    <row r="55" ht="18" customHeight="1">
+      <c r="B55" s="44" t="inlineStr">
+        <is>
+          <t>■5.4 デバイスコネクタの実行形態</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="18" customHeight="1">
+      <c r="B57" s="24" t="inlineStr">
+        <is>
+          <t>現行版では、釣銭機、キャッシュドロア、およびカスタマーディスプレイの既存デバイス資源を一つのデバイスコネクタプロセスで管理する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="28" customHeight="1">
+      <c r="B58" s="24" t="inlineStr">
+        <is>
+          <t>通常運用時は画面を表示せず、バックグラウンドで動作する。デバイスコネクタを直接開始・停止する画面は、デバッグ引数（DEBUG）付きで起動した場合だけ表示する。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="68">
-    <mergeCell ref="C26:Z26"/>
-    <mergeCell ref="C29:Z29"/>
-    <mergeCell ref="C35:Z35"/>
-    <mergeCell ref="C20:Z20"/>
+  <mergeCells count="71">
+    <mergeCell ref="D26:Z26"/>
     <mergeCell ref="D9:J9"/>
-    <mergeCell ref="C47:Z47"/>
+    <mergeCell ref="D35:Z35"/>
     <mergeCell ref="C16:Z16"/>
     <mergeCell ref="D8:J8"/>
+    <mergeCell ref="D20:Z20"/>
+    <mergeCell ref="D44:Z44"/>
+    <mergeCell ref="C50:Z50"/>
     <mergeCell ref="C54:Z54"/>
-    <mergeCell ref="C50:Z50"/>
-    <mergeCell ref="C25:Z25"/>
-    <mergeCell ref="C44:Z44"/>
-    <mergeCell ref="C41:Z41"/>
     <mergeCell ref="W2:X3"/>
+    <mergeCell ref="D19:Z19"/>
     <mergeCell ref="C31:Z31"/>
+    <mergeCell ref="D34:Z34"/>
     <mergeCell ref="B6:Z6"/>
-    <mergeCell ref="C22:Z22"/>
     <mergeCell ref="B30:Z30"/>
-    <mergeCell ref="C40:Z40"/>
     <mergeCell ref="B15:Z15"/>
+    <mergeCell ref="D46:Z46"/>
     <mergeCell ref="H2:Q3"/>
     <mergeCell ref="K10:Z10"/>
+    <mergeCell ref="D22:Z22"/>
+    <mergeCell ref="D40:Z40"/>
     <mergeCell ref="T1:V1"/>
-    <mergeCell ref="C21:Z21"/>
+    <mergeCell ref="B55:Z55"/>
     <mergeCell ref="B11:C11"/>
-    <mergeCell ref="C43:Z43"/>
     <mergeCell ref="B5:Z5"/>
-    <mergeCell ref="C46:Z46"/>
     <mergeCell ref="C51:Z51"/>
+    <mergeCell ref="D36:Z36"/>
     <mergeCell ref="W1:X1"/>
     <mergeCell ref="Y1:Z1"/>
     <mergeCell ref="R2:S3"/>
-    <mergeCell ref="C27:Z27"/>
+    <mergeCell ref="D21:Z21"/>
     <mergeCell ref="D10:J10"/>
-    <mergeCell ref="C36:Z36"/>
     <mergeCell ref="R1:S1"/>
     <mergeCell ref="B8:C8"/>
     <mergeCell ref="H1:Q1"/>
     <mergeCell ref="C23:Z23"/>
-    <mergeCell ref="C39:Z39"/>
+    <mergeCell ref="D27:Z27"/>
     <mergeCell ref="C52:Z52"/>
-    <mergeCell ref="C17:Z17"/>
+    <mergeCell ref="D32:Z32"/>
     <mergeCell ref="K9:Z9"/>
+    <mergeCell ref="D41:Z41"/>
     <mergeCell ref="A1:D3"/>
+    <mergeCell ref="D17:Z17"/>
     <mergeCell ref="C45:Z45"/>
-    <mergeCell ref="C32:Z32"/>
     <mergeCell ref="C38:Z38"/>
     <mergeCell ref="B10:C10"/>
-    <mergeCell ref="C28:Z28"/>
-    <mergeCell ref="C19:Z19"/>
-    <mergeCell ref="C37:Z37"/>
+    <mergeCell ref="D47:Z47"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="K11:Z11"/>
     <mergeCell ref="D11:J11"/>
+    <mergeCell ref="D43:Z43"/>
     <mergeCell ref="C53:Z53"/>
+    <mergeCell ref="D37:Z37"/>
     <mergeCell ref="B48:Z48"/>
-    <mergeCell ref="C18:Z18"/>
+    <mergeCell ref="B58:Z58"/>
+    <mergeCell ref="D28:Z28"/>
     <mergeCell ref="T2:V3"/>
+    <mergeCell ref="D18:Z18"/>
+    <mergeCell ref="E2:G3"/>
     <mergeCell ref="C49:Z49"/>
-    <mergeCell ref="E2:G3"/>
-    <mergeCell ref="C34:Z34"/>
-    <mergeCell ref="C24:Z24"/>
-    <mergeCell ref="C42:Z42"/>
+    <mergeCell ref="D39:Z39"/>
+    <mergeCell ref="D25:Z25"/>
     <mergeCell ref="Y2:Z3"/>
-    <mergeCell ref="C33:Z33"/>
+    <mergeCell ref="B57:Z57"/>
+    <mergeCell ref="D24:Z24"/>
+    <mergeCell ref="D33:Z33"/>
     <mergeCell ref="B13:Z13"/>
+    <mergeCell ref="D29:Z29"/>
+    <mergeCell ref="D42:Z42"/>
     <mergeCell ref="K8:Z8"/>
     <mergeCell ref="E1:G1"/>
   </mergeCells>
@@ -19784,7 +19715,7 @@
       <c r="X2" s="15" t="n"/>
       <c r="Y2" s="17" t="inlineStr">
         <is>
-          <t>2026/07/13</t>
+          <t>2026/07/14</t>
         </is>
       </c>
       <c r="Z2" s="18" t="n"/>
@@ -19825,7 +19756,7 @@
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="B6" s="42" t="inlineStr">
+      <c r="B6" s="44" t="inlineStr">
         <is>
           <t>■6.1 運用シナリオ図</t>
         </is>
